--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="817" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{552976D4-2A31-4C53-96A3-A94B93BAEA3C}"/>
+  <xr:revisionPtr revIDLastSave="930" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99E26759-0DB2-43A6-93FD-358521979CE6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-1545" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="115">
   <si>
     <t>Boneco</t>
   </si>
@@ -369,6 +369,21 @@
   </si>
   <si>
     <t>Claudinei</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Patinho</t>
+  </si>
+  <si>
+    <t>cristiano</t>
+  </si>
+  <si>
+    <t>Carioca</t>
+  </si>
+  <si>
+    <t>Roney</t>
   </si>
 </sst>
 </file>
@@ -695,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O205"/>
+  <dimension ref="A1:O227"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -7899,6 +7914,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>110</v>
+      </c>
+      <c r="C206">
+        <v>9</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+      <c r="F206">
+        <v>2</v>
+      </c>
+      <c r="G206">
+        <v>1</v>
+      </c>
+      <c r="H206">
+        <v>1</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>34</v>
+      </c>
+      <c r="C207">
+        <v>9</v>
+      </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="F207">
+        <v>3</v>
+      </c>
+      <c r="G207">
+        <v>1</v>
+      </c>
+      <c r="H207">
+        <v>1</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>63</v>
+      </c>
+      <c r="C208">
+        <v>9</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208">
+        <v>4</v>
+      </c>
+      <c r="G208">
+        <v>1</v>
+      </c>
+      <c r="H208">
+        <v>1</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>24</v>
+      </c>
+      <c r="C209">
+        <v>9</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>1</v>
+      </c>
+      <c r="F209">
+        <v>4</v>
+      </c>
+      <c r="G209">
+        <v>1</v>
+      </c>
+      <c r="H209">
+        <v>1</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>1</v>
+      </c>
+      <c r="C210">
+        <v>9</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>1</v>
+      </c>
+      <c r="F210">
+        <v>5</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+      <c r="H210">
+        <v>1</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>59</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>3</v>
+      </c>
+      <c r="E211">
+        <v>3</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211">
+        <v>1</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>29</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>3</v>
+      </c>
+      <c r="E212">
+        <v>3</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>1</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>111</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>3</v>
+      </c>
+      <c r="E213">
+        <v>3</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+      <c r="G213">
+        <v>1</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>43</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>3</v>
+      </c>
+      <c r="E214">
+        <v>3</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214">
+        <v>1</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>3</v>
+      </c>
+      <c r="E215">
+        <v>3</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>50</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>6</v>
+      </c>
+      <c r="F216">
+        <v>0</v>
+      </c>
+      <c r="G216">
+        <v>1</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>112</v>
+      </c>
+      <c r="C217">
+        <v>1</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>6</v>
+      </c>
+      <c r="F217">
+        <v>0</v>
+      </c>
+      <c r="G217">
+        <v>1</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>6</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>6</v>
+      </c>
+      <c r="F218">
+        <v>2</v>
+      </c>
+      <c r="G218">
+        <v>1</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>57</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>6</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>1</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>30</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>6</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220">
+        <v>1</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>4</v>
+      </c>
+      <c r="C221">
+        <v>2</v>
+      </c>
+      <c r="D221">
+        <v>2</v>
+      </c>
+      <c r="E221">
+        <v>2</v>
+      </c>
+      <c r="F221">
+        <v>2</v>
+      </c>
+      <c r="G221">
+        <v>1</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>0</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>5</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="D222">
+        <v>2</v>
+      </c>
+      <c r="E222">
+        <v>2</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>1</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>113</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+      <c r="D223">
+        <v>2</v>
+      </c>
+      <c r="E223">
+        <v>2</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223">
+        <v>1</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>41</v>
+      </c>
+      <c r="C224">
+        <v>2</v>
+      </c>
+      <c r="D224">
+        <v>2</v>
+      </c>
+      <c r="E224">
+        <v>2</v>
+      </c>
+      <c r="F224">
+        <v>1</v>
+      </c>
+      <c r="G224">
+        <v>1</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>2</v>
+      </c>
+      <c r="D225">
+        <v>2</v>
+      </c>
+      <c r="E225">
+        <v>2</v>
+      </c>
+      <c r="F225">
+        <v>0</v>
+      </c>
+      <c r="G225">
+        <v>1</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>114</v>
+      </c>
+      <c r="C226">
+        <v>8</v>
+      </c>
+      <c r="D226">
+        <v>4</v>
+      </c>
+      <c r="E226">
+        <v>3</v>
+      </c>
+      <c r="F226">
+        <v>0</v>
+      </c>
+      <c r="G226">
+        <v>1</v>
+      </c>
+      <c r="H226">
+        <v>1</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>45</v>
+      </c>
+      <c r="C227">
+        <v>3</v>
+      </c>
+      <c r="D227">
+        <v>4</v>
+      </c>
+      <c r="E227">
+        <v>8</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="G227">
+        <v>1</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>0</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="930" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99E26759-0DB2-43A6-93FD-358521979CE6}"/>
+  <xr:revisionPtr revIDLastSave="1044" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2428FEB7-0B20-4F64-8E50-9812013AEC2A}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-1545" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="116">
   <si>
     <t>Boneco</t>
   </si>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>Roney</t>
+  </si>
+  <si>
+    <t>Davidson</t>
   </si>
 </sst>
 </file>
@@ -710,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O227"/>
+  <dimension ref="A1:O249"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -8684,6 +8687,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>5</v>
+      </c>
+      <c r="C228">
+        <v>2</v>
+      </c>
+      <c r="D228">
+        <v>3</v>
+      </c>
+      <c r="E228">
+        <v>2</v>
+      </c>
+      <c r="F228">
+        <v>2</v>
+      </c>
+      <c r="G228">
+        <v>1</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>32</v>
+      </c>
+      <c r="C229">
+        <v>2</v>
+      </c>
+      <c r="D229">
+        <v>3</v>
+      </c>
+      <c r="E229">
+        <v>2</v>
+      </c>
+      <c r="F229">
+        <v>0</v>
+      </c>
+      <c r="G229">
+        <v>1</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>59</v>
+      </c>
+      <c r="C230">
+        <v>2</v>
+      </c>
+      <c r="D230">
+        <v>3</v>
+      </c>
+      <c r="E230">
+        <v>2</v>
+      </c>
+      <c r="F230">
+        <v>2</v>
+      </c>
+      <c r="G230">
+        <v>1</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>28</v>
+      </c>
+      <c r="C231">
+        <v>2</v>
+      </c>
+      <c r="D231">
+        <v>3</v>
+      </c>
+      <c r="E231">
+        <v>2</v>
+      </c>
+      <c r="F231">
+        <v>0</v>
+      </c>
+      <c r="G231">
+        <v>1</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>6</v>
+      </c>
+      <c r="C232">
+        <v>2</v>
+      </c>
+      <c r="D232">
+        <v>3</v>
+      </c>
+      <c r="E232">
+        <v>2</v>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+      <c r="G232">
+        <v>1</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>27</v>
+      </c>
+      <c r="C233">
+        <v>3</v>
+      </c>
+      <c r="D233">
+        <v>3</v>
+      </c>
+      <c r="E233">
+        <v>2</v>
+      </c>
+      <c r="F233">
+        <v>2</v>
+      </c>
+      <c r="G233">
+        <v>1</v>
+      </c>
+      <c r="H233">
+        <v>1</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>84</v>
+      </c>
+      <c r="C234">
+        <v>3</v>
+      </c>
+      <c r="D234">
+        <v>3</v>
+      </c>
+      <c r="E234">
+        <v>2</v>
+      </c>
+      <c r="F234">
+        <v>3</v>
+      </c>
+      <c r="G234">
+        <v>1</v>
+      </c>
+      <c r="H234">
+        <v>1</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>49</v>
+      </c>
+      <c r="C235">
+        <v>3</v>
+      </c>
+      <c r="D235">
+        <v>3</v>
+      </c>
+      <c r="E235">
+        <v>2</v>
+      </c>
+      <c r="F235">
+        <v>1</v>
+      </c>
+      <c r="G235">
+        <v>1</v>
+      </c>
+      <c r="H235">
+        <v>1</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>30</v>
+      </c>
+      <c r="C236">
+        <v>3</v>
+      </c>
+      <c r="D236">
+        <v>3</v>
+      </c>
+      <c r="E236">
+        <v>2</v>
+      </c>
+      <c r="F236">
+        <v>1</v>
+      </c>
+      <c r="G236">
+        <v>1</v>
+      </c>
+      <c r="H236">
+        <v>1</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>57</v>
+      </c>
+      <c r="C237">
+        <v>3</v>
+      </c>
+      <c r="D237">
+        <v>3</v>
+      </c>
+      <c r="E237">
+        <v>2</v>
+      </c>
+      <c r="F237">
+        <v>3</v>
+      </c>
+      <c r="G237">
+        <v>1</v>
+      </c>
+      <c r="H237">
+        <v>1</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238">
+        <v>2</v>
+      </c>
+      <c r="D238">
+        <v>2</v>
+      </c>
+      <c r="E238">
+        <v>3</v>
+      </c>
+      <c r="F238">
+        <v>1</v>
+      </c>
+      <c r="G238">
+        <v>1</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>1</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>1</v>
+      </c>
+      <c r="C239">
+        <v>2</v>
+      </c>
+      <c r="D239">
+        <v>2</v>
+      </c>
+      <c r="E239">
+        <v>3</v>
+      </c>
+      <c r="F239">
+        <v>1</v>
+      </c>
+      <c r="G239">
+        <v>1</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>0</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>39</v>
+      </c>
+      <c r="C240">
+        <v>2</v>
+      </c>
+      <c r="D240">
+        <v>2</v>
+      </c>
+      <c r="E240">
+        <v>3</v>
+      </c>
+      <c r="F240">
+        <v>3</v>
+      </c>
+      <c r="G240">
+        <v>1</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>2</v>
+      </c>
+      <c r="D241">
+        <v>2</v>
+      </c>
+      <c r="E241">
+        <v>3</v>
+      </c>
+      <c r="F241">
+        <v>1</v>
+      </c>
+      <c r="G241">
+        <v>1</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>115</v>
+      </c>
+      <c r="C242">
+        <v>2</v>
+      </c>
+      <c r="D242">
+        <v>2</v>
+      </c>
+      <c r="E242">
+        <v>3</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+      <c r="G242">
+        <v>1</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>34</v>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+      <c r="D243">
+        <v>2</v>
+      </c>
+      <c r="E243">
+        <v>2</v>
+      </c>
+      <c r="F243">
+        <v>0</v>
+      </c>
+      <c r="G243">
+        <v>1</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>21</v>
+      </c>
+      <c r="C244">
+        <v>2</v>
+      </c>
+      <c r="D244">
+        <v>2</v>
+      </c>
+      <c r="E244">
+        <v>2</v>
+      </c>
+      <c r="F244">
+        <v>3</v>
+      </c>
+      <c r="G244">
+        <v>1</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>0</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>36</v>
+      </c>
+      <c r="C245">
+        <v>2</v>
+      </c>
+      <c r="D245">
+        <v>2</v>
+      </c>
+      <c r="E245">
+        <v>2</v>
+      </c>
+      <c r="F245">
+        <v>1</v>
+      </c>
+      <c r="G245">
+        <v>1</v>
+      </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>24</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+      <c r="D246">
+        <v>2</v>
+      </c>
+      <c r="E246">
+        <v>2</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+      <c r="G246">
+        <v>1</v>
+      </c>
+      <c r="H246">
+        <v>0</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>29</v>
+      </c>
+      <c r="C247">
+        <v>2</v>
+      </c>
+      <c r="D247">
+        <v>2</v>
+      </c>
+      <c r="E247">
+        <v>2</v>
+      </c>
+      <c r="F247">
+        <v>1</v>
+      </c>
+      <c r="G247">
+        <v>1</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247">
+        <v>0</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>0</v>
+      </c>
+      <c r="L247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>25</v>
+      </c>
+      <c r="C248">
+        <v>2</v>
+      </c>
+      <c r="D248">
+        <v>4</v>
+      </c>
+      <c r="E248">
+        <v>4</v>
+      </c>
+      <c r="F248">
+        <v>0</v>
+      </c>
+      <c r="G248">
+        <v>1</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>13</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>45</v>
+      </c>
+      <c r="C249">
+        <v>4</v>
+      </c>
+      <c r="D249">
+        <v>4</v>
+      </c>
+      <c r="E249">
+        <v>2</v>
+      </c>
+      <c r="F249">
+        <v>0</v>
+      </c>
+      <c r="G249">
+        <v>1</v>
+      </c>
+      <c r="H249">
+        <v>1</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>13</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1044" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2428FEB7-0B20-4F64-8E50-9812013AEC2A}"/>
+  <xr:revisionPtr revIDLastSave="1171" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9BA5DCF-70A1-46AC-9646-65B0191A8141}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-1545" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="118">
   <si>
     <t>Boneco</t>
   </si>
@@ -387,6 +387,12 @@
   </si>
   <si>
     <t>Davidson</t>
+  </si>
+  <si>
+    <t>Marcos goleiro</t>
+  </si>
+  <si>
+    <t>Ian</t>
   </si>
 </sst>
 </file>
@@ -713,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O249"/>
+  <dimension ref="A1:O272"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -9389,7 +9395,7 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="C248">
         <v>2</v>
@@ -9454,6 +9460,811 @@
         <v>13</v>
       </c>
       <c r="L249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>25</v>
+      </c>
+      <c r="C250">
+        <v>4</v>
+      </c>
+      <c r="D250">
+        <v>4</v>
+      </c>
+      <c r="E250">
+        <v>2</v>
+      </c>
+      <c r="F250">
+        <v>2</v>
+      </c>
+      <c r="G250">
+        <v>1</v>
+      </c>
+      <c r="H250">
+        <v>1</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>6</v>
+      </c>
+      <c r="C251">
+        <v>4</v>
+      </c>
+      <c r="D251">
+        <v>4</v>
+      </c>
+      <c r="E251">
+        <v>2</v>
+      </c>
+      <c r="F251">
+        <v>2</v>
+      </c>
+      <c r="G251">
+        <v>1</v>
+      </c>
+      <c r="H251">
+        <v>1</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>0</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>3</v>
+      </c>
+      <c r="C252">
+        <v>4</v>
+      </c>
+      <c r="D252">
+        <v>4</v>
+      </c>
+      <c r="E252">
+        <v>2</v>
+      </c>
+      <c r="F252">
+        <v>0</v>
+      </c>
+      <c r="G252">
+        <v>1</v>
+      </c>
+      <c r="H252">
+        <v>1</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>27</v>
+      </c>
+      <c r="C253">
+        <v>4</v>
+      </c>
+      <c r="D253">
+        <v>4</v>
+      </c>
+      <c r="E253">
+        <v>2</v>
+      </c>
+      <c r="F253">
+        <v>3</v>
+      </c>
+      <c r="G253">
+        <v>1</v>
+      </c>
+      <c r="H253">
+        <v>1</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>49</v>
+      </c>
+      <c r="C254">
+        <v>4</v>
+      </c>
+      <c r="D254">
+        <v>4</v>
+      </c>
+      <c r="E254">
+        <v>2</v>
+      </c>
+      <c r="F254">
+        <v>1</v>
+      </c>
+      <c r="G254">
+        <v>1</v>
+      </c>
+      <c r="H254">
+        <v>1</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>0</v>
+      </c>
+      <c r="L254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>34</v>
+      </c>
+      <c r="C255">
+        <v>2</v>
+      </c>
+      <c r="D255">
+        <v>4</v>
+      </c>
+      <c r="E255">
+        <v>2</v>
+      </c>
+      <c r="F255">
+        <v>3</v>
+      </c>
+      <c r="G255">
+        <v>1</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>0</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>28</v>
+      </c>
+      <c r="C256">
+        <v>2</v>
+      </c>
+      <c r="D256">
+        <v>4</v>
+      </c>
+      <c r="E256">
+        <v>2</v>
+      </c>
+      <c r="F256">
+        <v>0</v>
+      </c>
+      <c r="G256">
+        <v>1</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>0</v>
+      </c>
+      <c r="L256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>29</v>
+      </c>
+      <c r="C257">
+        <v>2</v>
+      </c>
+      <c r="D257">
+        <v>4</v>
+      </c>
+      <c r="E257">
+        <v>2</v>
+      </c>
+      <c r="F257">
+        <v>0</v>
+      </c>
+      <c r="G257">
+        <v>1</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>1</v>
+      </c>
+      <c r="C258">
+        <v>2</v>
+      </c>
+      <c r="D258">
+        <v>4</v>
+      </c>
+      <c r="E258">
+        <v>2</v>
+      </c>
+      <c r="F258">
+        <v>2</v>
+      </c>
+      <c r="G258">
+        <v>1</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258">
+        <v>0</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>59</v>
+      </c>
+      <c r="C259">
+        <v>2</v>
+      </c>
+      <c r="D259">
+        <v>4</v>
+      </c>
+      <c r="E259">
+        <v>2</v>
+      </c>
+      <c r="F259">
+        <v>1</v>
+      </c>
+      <c r="G259">
+        <v>1</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>0</v>
+      </c>
+      <c r="K259">
+        <v>0</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>32</v>
+      </c>
+      <c r="C260">
+        <v>3</v>
+      </c>
+      <c r="D260">
+        <v>2</v>
+      </c>
+      <c r="E260">
+        <v>3</v>
+      </c>
+      <c r="F260">
+        <v>1</v>
+      </c>
+      <c r="G260">
+        <v>1</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>57</v>
+      </c>
+      <c r="C261">
+        <v>3</v>
+      </c>
+      <c r="D261">
+        <v>2</v>
+      </c>
+      <c r="E261">
+        <v>3</v>
+      </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
+      <c r="G261">
+        <v>1</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>0</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>30</v>
+      </c>
+      <c r="C262">
+        <v>3</v>
+      </c>
+      <c r="D262">
+        <v>2</v>
+      </c>
+      <c r="E262">
+        <v>3</v>
+      </c>
+      <c r="F262">
+        <v>0</v>
+      </c>
+      <c r="G262">
+        <v>1</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>0</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>23</v>
+      </c>
+      <c r="C263">
+        <v>3</v>
+      </c>
+      <c r="D263">
+        <v>2</v>
+      </c>
+      <c r="E263">
+        <v>3</v>
+      </c>
+      <c r="F263">
+        <v>2</v>
+      </c>
+      <c r="G263">
+        <v>1</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>0</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>4</v>
+      </c>
+      <c r="C264">
+        <v>3</v>
+      </c>
+      <c r="D264">
+        <v>2</v>
+      </c>
+      <c r="E264">
+        <v>3</v>
+      </c>
+      <c r="F264">
+        <v>4</v>
+      </c>
+      <c r="G264">
+        <v>1</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>24</v>
+      </c>
+      <c r="C265">
+        <v>2</v>
+      </c>
+      <c r="D265">
+        <v>2</v>
+      </c>
+      <c r="E265">
+        <v>3</v>
+      </c>
+      <c r="F265">
+        <v>1</v>
+      </c>
+      <c r="G265">
+        <v>1</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+      <c r="I265">
+        <v>1</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265">
+        <v>0</v>
+      </c>
+      <c r="L265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>39</v>
+      </c>
+      <c r="C266">
+        <v>2</v>
+      </c>
+      <c r="D266">
+        <v>2</v>
+      </c>
+      <c r="E266">
+        <v>3</v>
+      </c>
+      <c r="F266">
+        <v>5</v>
+      </c>
+      <c r="G266">
+        <v>1</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+      <c r="I266">
+        <v>1</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266">
+        <v>0</v>
+      </c>
+      <c r="L266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>84</v>
+      </c>
+      <c r="C267">
+        <v>2</v>
+      </c>
+      <c r="D267">
+        <v>2</v>
+      </c>
+      <c r="E267">
+        <v>3</v>
+      </c>
+      <c r="F267">
+        <v>0</v>
+      </c>
+      <c r="G267">
+        <v>1</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>1</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267">
+        <v>0</v>
+      </c>
+      <c r="L267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>20</v>
+      </c>
+      <c r="C268">
+        <v>2</v>
+      </c>
+      <c r="D268">
+        <v>2</v>
+      </c>
+      <c r="E268">
+        <v>3</v>
+      </c>
+      <c r="F268">
+        <v>0</v>
+      </c>
+      <c r="G268">
+        <v>1</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+      <c r="I268">
+        <v>1</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>0</v>
+      </c>
+      <c r="L268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>33</v>
+      </c>
+      <c r="C269">
+        <v>2</v>
+      </c>
+      <c r="D269">
+        <v>2</v>
+      </c>
+      <c r="E269">
+        <v>3</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
+      <c r="G269">
+        <v>1</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+      <c r="I269">
+        <v>1</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269">
+        <v>0</v>
+      </c>
+      <c r="L269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>109</v>
+      </c>
+      <c r="C270">
+        <v>2</v>
+      </c>
+      <c r="D270">
+        <v>2</v>
+      </c>
+      <c r="E270">
+        <v>1</v>
+      </c>
+      <c r="F270">
+        <v>0</v>
+      </c>
+      <c r="G270">
+        <v>1</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>8</v>
+      </c>
+      <c r="L270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>117</v>
+      </c>
+      <c r="C271">
+        <v>4</v>
+      </c>
+      <c r="D271">
+        <v>4</v>
+      </c>
+      <c r="E271">
+        <v>2</v>
+      </c>
+      <c r="F271">
+        <v>0</v>
+      </c>
+      <c r="G271">
+        <v>1</v>
+      </c>
+      <c r="H271">
+        <v>1</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>9</v>
+      </c>
+      <c r="L271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>45</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+      <c r="D272">
+        <v>3</v>
+      </c>
+      <c r="E272">
+        <v>5</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
+      </c>
+      <c r="G272">
+        <v>1</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+      <c r="I272">
+        <v>1</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>11</v>
+      </c>
+      <c r="L272">
         <v>0</v>
       </c>
     </row>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1171" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9BA5DCF-70A1-46AC-9646-65B0191A8141}"/>
+  <xr:revisionPtr revIDLastSave="1284" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEEBBAA1-B5CA-49F5-8806-C741AA6AF58B}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-1545" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="118">
   <si>
     <t>Boneco</t>
   </si>
@@ -719,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O272"/>
+  <dimension ref="A1:O294"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -10268,6 +10268,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>27</v>
+      </c>
+      <c r="C273">
+        <v>3</v>
+      </c>
+      <c r="D273">
+        <v>3</v>
+      </c>
+      <c r="E273">
+        <v>1</v>
+      </c>
+      <c r="F273">
+        <v>2</v>
+      </c>
+      <c r="G273">
+        <v>1</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+      <c r="I273">
+        <v>0</v>
+      </c>
+      <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273">
+        <v>0</v>
+      </c>
+      <c r="L273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>49</v>
+      </c>
+      <c r="C274">
+        <v>3</v>
+      </c>
+      <c r="D274">
+        <v>3</v>
+      </c>
+      <c r="E274">
+        <v>1</v>
+      </c>
+      <c r="F274">
+        <v>0</v>
+      </c>
+      <c r="G274">
+        <v>1</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>0</v>
+      </c>
+      <c r="L274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>28</v>
+      </c>
+      <c r="C275">
+        <v>3</v>
+      </c>
+      <c r="D275">
+        <v>3</v>
+      </c>
+      <c r="E275">
+        <v>1</v>
+      </c>
+      <c r="F275">
+        <v>3</v>
+      </c>
+      <c r="G275">
+        <v>1</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275">
+        <v>0</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275">
+        <v>0</v>
+      </c>
+      <c r="L275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>34</v>
+      </c>
+      <c r="C276">
+        <v>3</v>
+      </c>
+      <c r="D276">
+        <v>3</v>
+      </c>
+      <c r="E276">
+        <v>1</v>
+      </c>
+      <c r="F276">
+        <v>1</v>
+      </c>
+      <c r="G276">
+        <v>1</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>20</v>
+      </c>
+      <c r="C277">
+        <v>3</v>
+      </c>
+      <c r="D277">
+        <v>3</v>
+      </c>
+      <c r="E277">
+        <v>1</v>
+      </c>
+      <c r="F277">
+        <v>0</v>
+      </c>
+      <c r="G277">
+        <v>1</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>0</v>
+      </c>
+      <c r="L277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>5</v>
+      </c>
+      <c r="C278">
+        <v>5</v>
+      </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
+      <c r="E278">
+        <v>3</v>
+      </c>
+      <c r="F278">
+        <v>2</v>
+      </c>
+      <c r="G278">
+        <v>1</v>
+      </c>
+      <c r="H278">
+        <v>1</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>0</v>
+      </c>
+      <c r="L278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>43</v>
+      </c>
+      <c r="C279">
+        <v>5</v>
+      </c>
+      <c r="D279">
+        <v>1</v>
+      </c>
+      <c r="E279">
+        <v>3</v>
+      </c>
+      <c r="F279">
+        <v>1</v>
+      </c>
+      <c r="G279">
+        <v>1</v>
+      </c>
+      <c r="H279">
+        <v>1</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>0</v>
+      </c>
+      <c r="L279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>21</v>
+      </c>
+      <c r="C280">
+        <v>5</v>
+      </c>
+      <c r="D280">
+        <v>1</v>
+      </c>
+      <c r="E280">
+        <v>3</v>
+      </c>
+      <c r="F280">
+        <v>3</v>
+      </c>
+      <c r="G280">
+        <v>1</v>
+      </c>
+      <c r="H280">
+        <v>1</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>0</v>
+      </c>
+      <c r="L280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>4</v>
+      </c>
+      <c r="C281">
+        <v>5</v>
+      </c>
+      <c r="D281">
+        <v>1</v>
+      </c>
+      <c r="E281">
+        <v>3</v>
+      </c>
+      <c r="F281">
+        <v>3</v>
+      </c>
+      <c r="G281">
+        <v>1</v>
+      </c>
+      <c r="H281">
+        <v>1</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>0</v>
+      </c>
+      <c r="L281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>24</v>
+      </c>
+      <c r="C282">
+        <v>5</v>
+      </c>
+      <c r="D282">
+        <v>1</v>
+      </c>
+      <c r="E282">
+        <v>3</v>
+      </c>
+      <c r="F282">
+        <v>2</v>
+      </c>
+      <c r="G282">
+        <v>1</v>
+      </c>
+      <c r="H282">
+        <v>1</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>0</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>1</v>
+      </c>
+      <c r="C283">
+        <v>2</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>5</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+      <c r="G283">
+        <v>1</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>2</v>
+      </c>
+      <c r="C284">
+        <v>2</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>5</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+      <c r="G284">
+        <v>1</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>30</v>
+      </c>
+      <c r="C285">
+        <v>2</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>5</v>
+      </c>
+      <c r="F285">
+        <v>1</v>
+      </c>
+      <c r="G285">
+        <v>1</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>0</v>
+      </c>
+      <c r="L285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>63</v>
+      </c>
+      <c r="C286">
+        <v>2</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>5</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+      <c r="G286">
+        <v>1</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>0</v>
+      </c>
+      <c r="L286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>39</v>
+      </c>
+      <c r="C287">
+        <v>2</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>5</v>
+      </c>
+      <c r="F287">
+        <v>1</v>
+      </c>
+      <c r="G287">
+        <v>1</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
+      </c>
+      <c r="K287">
+        <v>0</v>
+      </c>
+      <c r="L287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>29</v>
+      </c>
+      <c r="C288">
+        <v>2</v>
+      </c>
+      <c r="D288">
+        <v>2</v>
+      </c>
+      <c r="E288">
+        <v>2</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288">
+        <v>1</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>0</v>
+      </c>
+      <c r="L288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>6</v>
+      </c>
+      <c r="C289">
+        <v>2</v>
+      </c>
+      <c r="D289">
+        <v>2</v>
+      </c>
+      <c r="E289">
+        <v>2</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+      <c r="G289">
+        <v>1</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>0</v>
+      </c>
+      <c r="L289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>3</v>
+      </c>
+      <c r="C290">
+        <v>2</v>
+      </c>
+      <c r="D290">
+        <v>2</v>
+      </c>
+      <c r="E290">
+        <v>2</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+      <c r="G290">
+        <v>1</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290">
+        <v>0</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>0</v>
+      </c>
+      <c r="L290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>25</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
+      <c r="G291">
+        <v>1</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291">
+        <v>0</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>0</v>
+      </c>
+      <c r="L291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>32</v>
+      </c>
+      <c r="C292">
+        <v>2</v>
+      </c>
+      <c r="D292">
+        <v>2</v>
+      </c>
+      <c r="E292">
+        <v>2</v>
+      </c>
+      <c r="F292">
+        <v>1</v>
+      </c>
+      <c r="G292">
+        <v>1</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>0</v>
+      </c>
+      <c r="L292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>114</v>
+      </c>
+      <c r="C293">
+        <v>8</v>
+      </c>
+      <c r="D293">
+        <v>3</v>
+      </c>
+      <c r="E293">
+        <v>2</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+      <c r="G293">
+        <v>1</v>
+      </c>
+      <c r="H293">
+        <v>1</v>
+      </c>
+      <c r="I293">
+        <v>0</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>8</v>
+      </c>
+      <c r="L293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>45</v>
+      </c>
+      <c r="C294">
+        <v>2</v>
+      </c>
+      <c r="D294">
+        <v>3</v>
+      </c>
+      <c r="E294">
+        <v>8</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+      <c r="G294">
+        <v>1</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>15</v>
+      </c>
+      <c r="L294">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1284" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEEBBAA1-B5CA-49F5-8806-C741AA6AF58B}"/>
+  <xr:revisionPtr revIDLastSave="1407" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02A59BC-D708-4E83-8C03-7E83B475EF38}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="117">
   <si>
     <t>Boneco</t>
   </si>
@@ -345,9 +345,6 @@
   </si>
   <si>
     <t>Dieguinho</t>
-  </si>
-  <si>
-    <t>mateus</t>
   </si>
   <si>
     <t>Breno</t>
@@ -719,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O294"/>
+  <dimension ref="A1:O317"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -3935,7 +3932,7 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3970,7 +3967,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -4005,7 +4002,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4180,7 +4177,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C99">
         <v>4</v>
@@ -4320,7 +4317,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C103">
         <v>3</v>
@@ -4880,7 +4877,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C119">
         <v>6</v>
@@ -4950,7 +4947,7 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C121">
         <v>3</v>
@@ -5440,7 +5437,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -5510,7 +5507,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C137">
         <v>5</v>
@@ -6910,7 +6907,7 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C177">
         <v>3</v>
@@ -7120,7 +7117,7 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C183">
         <v>3</v>
@@ -7925,7 +7922,7 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C206">
         <v>9</v>
@@ -8170,7 +8167,7 @@
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -8310,7 +8307,7 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -8520,7 +8517,7 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -8625,7 +8622,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C226">
         <v>8</v>
@@ -9185,7 +9182,7 @@
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C242">
         <v>2</v>
@@ -9395,7 +9392,7 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C248">
         <v>2</v>
@@ -10165,7 +10162,7 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C270">
         <v>2</v>
@@ -10200,7 +10197,7 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C271">
         <v>4</v>
@@ -10970,7 +10967,7 @@
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C293">
         <v>8</v>
@@ -11035,6 +11032,811 @@
         <v>15</v>
       </c>
       <c r="L294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>37</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>1</v>
+      </c>
+      <c r="E295">
+        <v>5</v>
+      </c>
+      <c r="F295">
+        <v>0</v>
+      </c>
+      <c r="G295">
+        <v>1</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>0</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>2</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>1</v>
+      </c>
+      <c r="E296">
+        <v>5</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+      <c r="G296">
+        <v>1</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>0</v>
+      </c>
+      <c r="L296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>4</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>1</v>
+      </c>
+      <c r="E297">
+        <v>5</v>
+      </c>
+      <c r="F297">
+        <v>1</v>
+      </c>
+      <c r="G297">
+        <v>1</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>0</v>
+      </c>
+      <c r="L297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>50</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>1</v>
+      </c>
+      <c r="E298">
+        <v>5</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
+      <c r="G298">
+        <v>1</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>0</v>
+      </c>
+      <c r="L298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>28</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>1</v>
+      </c>
+      <c r="E299">
+        <v>5</v>
+      </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
+      <c r="G299">
+        <v>1</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+      <c r="I299">
+        <v>1</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>0</v>
+      </c>
+      <c r="L299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>30</v>
+      </c>
+      <c r="C300">
+        <v>4</v>
+      </c>
+      <c r="D300">
+        <v>3</v>
+      </c>
+      <c r="E300">
+        <v>2</v>
+      </c>
+      <c r="F300">
+        <v>2</v>
+      </c>
+      <c r="G300">
+        <v>1</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>0</v>
+      </c>
+      <c r="L300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>34</v>
+      </c>
+      <c r="C301">
+        <v>4</v>
+      </c>
+      <c r="D301">
+        <v>3</v>
+      </c>
+      <c r="E301">
+        <v>2</v>
+      </c>
+      <c r="F301">
+        <v>4</v>
+      </c>
+      <c r="G301">
+        <v>1</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+      <c r="I301">
+        <v>0</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>0</v>
+      </c>
+      <c r="L301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>57</v>
+      </c>
+      <c r="C302">
+        <v>4</v>
+      </c>
+      <c r="D302">
+        <v>3</v>
+      </c>
+      <c r="E302">
+        <v>2</v>
+      </c>
+      <c r="F302">
+        <v>1</v>
+      </c>
+      <c r="G302">
+        <v>1</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>59</v>
+      </c>
+      <c r="C303">
+        <v>4</v>
+      </c>
+      <c r="D303">
+        <v>3</v>
+      </c>
+      <c r="E303">
+        <v>2</v>
+      </c>
+      <c r="F303">
+        <v>1</v>
+      </c>
+      <c r="G303">
+        <v>1</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+      <c r="I303">
+        <v>0</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>0</v>
+      </c>
+      <c r="L303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>21</v>
+      </c>
+      <c r="C304">
+        <v>4</v>
+      </c>
+      <c r="D304">
+        <v>3</v>
+      </c>
+      <c r="E304">
+        <v>2</v>
+      </c>
+      <c r="F304">
+        <v>2</v>
+      </c>
+      <c r="G304">
+        <v>1</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>0</v>
+      </c>
+      <c r="L304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>20</v>
+      </c>
+      <c r="C305">
+        <v>1</v>
+      </c>
+      <c r="D305">
+        <v>2</v>
+      </c>
+      <c r="E305">
+        <v>4</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+      <c r="G305">
+        <v>1</v>
+      </c>
+      <c r="H305">
+        <v>0</v>
+      </c>
+      <c r="I305">
+        <v>0</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>0</v>
+      </c>
+      <c r="L305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>43</v>
+      </c>
+      <c r="C306">
+        <v>1</v>
+      </c>
+      <c r="D306">
+        <v>2</v>
+      </c>
+      <c r="E306">
+        <v>4</v>
+      </c>
+      <c r="F306">
+        <v>1</v>
+      </c>
+      <c r="G306">
+        <v>1</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
+      <c r="L306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>27</v>
+      </c>
+      <c r="C307">
+        <v>1</v>
+      </c>
+      <c r="D307">
+        <v>2</v>
+      </c>
+      <c r="E307">
+        <v>4</v>
+      </c>
+      <c r="F307">
+        <v>0</v>
+      </c>
+      <c r="G307">
+        <v>1</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>3</v>
+      </c>
+      <c r="C308">
+        <v>1</v>
+      </c>
+      <c r="D308">
+        <v>2</v>
+      </c>
+      <c r="E308">
+        <v>4</v>
+      </c>
+      <c r="F308">
+        <v>0</v>
+      </c>
+      <c r="G308">
+        <v>1</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>1</v>
+      </c>
+      <c r="C309">
+        <v>1</v>
+      </c>
+      <c r="D309">
+        <v>2</v>
+      </c>
+      <c r="E309">
+        <v>4</v>
+      </c>
+      <c r="F309">
+        <v>2</v>
+      </c>
+      <c r="G309">
+        <v>1</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>0</v>
+      </c>
+      <c r="L309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>110</v>
+      </c>
+      <c r="C310">
+        <v>6</v>
+      </c>
+      <c r="D310">
+        <v>4</v>
+      </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
+      <c r="F310">
+        <v>1</v>
+      </c>
+      <c r="G310">
+        <v>1</v>
+      </c>
+      <c r="H310">
+        <v>1</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
+      <c r="L310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>32</v>
+      </c>
+      <c r="C311">
+        <v>6</v>
+      </c>
+      <c r="D311">
+        <v>4</v>
+      </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+      <c r="G311">
+        <v>1</v>
+      </c>
+      <c r="H311">
+        <v>1</v>
+      </c>
+      <c r="I311">
+        <v>0</v>
+      </c>
+      <c r="J311">
+        <v>0</v>
+      </c>
+      <c r="K311">
+        <v>0</v>
+      </c>
+      <c r="L311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>23</v>
+      </c>
+      <c r="C312">
+        <v>6</v>
+      </c>
+      <c r="D312">
+        <v>4</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>1</v>
+      </c>
+      <c r="G312">
+        <v>1</v>
+      </c>
+      <c r="H312">
+        <v>1</v>
+      </c>
+      <c r="I312">
+        <v>0</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+      <c r="K312">
+        <v>0</v>
+      </c>
+      <c r="L312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>5</v>
+      </c>
+      <c r="C313">
+        <v>6</v>
+      </c>
+      <c r="D313">
+        <v>4</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+      <c r="F313">
+        <v>6</v>
+      </c>
+      <c r="G313">
+        <v>1</v>
+      </c>
+      <c r="H313">
+        <v>1</v>
+      </c>
+      <c r="I313">
+        <v>0</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>0</v>
+      </c>
+      <c r="L313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>25</v>
+      </c>
+      <c r="C314">
+        <v>6</v>
+      </c>
+      <c r="D314">
+        <v>4</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
+        <v>2</v>
+      </c>
+      <c r="G314">
+        <v>1</v>
+      </c>
+      <c r="H314">
+        <v>1</v>
+      </c>
+      <c r="I314">
+        <v>0</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>0</v>
+      </c>
+      <c r="L314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>17</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>1</v>
+      </c>
+      <c r="E315">
+        <v>5</v>
+      </c>
+      <c r="F315">
+        <v>1</v>
+      </c>
+      <c r="G315">
+        <v>1</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315">
+        <v>1</v>
+      </c>
+      <c r="J315">
+        <v>0</v>
+      </c>
+      <c r="K315">
+        <v>11</v>
+      </c>
+      <c r="L315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>45</v>
+      </c>
+      <c r="C316">
+        <v>10</v>
+      </c>
+      <c r="D316">
+        <v>3</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>1</v>
+      </c>
+      <c r="G316">
+        <v>1</v>
+      </c>
+      <c r="H316">
+        <v>1</v>
+      </c>
+      <c r="I316">
+        <v>0</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>4</v>
+      </c>
+      <c r="L316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>96</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317">
+        <v>2</v>
+      </c>
+      <c r="E317">
+        <v>5</v>
+      </c>
+      <c r="F317">
+        <v>0</v>
+      </c>
+      <c r="G317">
+        <v>1</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>0</v>
+      </c>
+      <c r="K317">
+        <v>12</v>
+      </c>
+      <c r="L317">
         <v>0</v>
       </c>
     </row>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1407" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02A59BC-D708-4E83-8C03-7E83B475EF38}"/>
+  <xr:revisionPtr revIDLastSave="1541" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A6244A9-3827-4EB7-AF1C-CA479AAF00FF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="119">
   <si>
     <t>Boneco</t>
   </si>
@@ -391,6 +391,12 @@
   <si>
     <t>Ian</t>
   </si>
+  <si>
+    <t>Marlinho</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
 </sst>
 </file>
 
@@ -716,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O317"/>
+  <dimension ref="A1:O340"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -11840,6 +11846,811 @@
         <v>0</v>
       </c>
     </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>30</v>
+      </c>
+      <c r="C318">
+        <v>2</v>
+      </c>
+      <c r="D318">
+        <v>1</v>
+      </c>
+      <c r="E318">
+        <v>4</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
+        <v>1</v>
+      </c>
+      <c r="H318">
+        <v>0</v>
+      </c>
+      <c r="I318">
+        <v>1</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>0</v>
+      </c>
+      <c r="L318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>32</v>
+      </c>
+      <c r="C319">
+        <v>2</v>
+      </c>
+      <c r="D319">
+        <v>1</v>
+      </c>
+      <c r="E319">
+        <v>4</v>
+      </c>
+      <c r="F319">
+        <v>0</v>
+      </c>
+      <c r="G319">
+        <v>1</v>
+      </c>
+      <c r="H319">
+        <v>0</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>0</v>
+      </c>
+      <c r="L319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>5</v>
+      </c>
+      <c r="C320">
+        <v>2</v>
+      </c>
+      <c r="D320">
+        <v>1</v>
+      </c>
+      <c r="E320">
+        <v>4</v>
+      </c>
+      <c r="F320">
+        <v>2</v>
+      </c>
+      <c r="G320">
+        <v>1</v>
+      </c>
+      <c r="H320">
+        <v>0</v>
+      </c>
+      <c r="I320">
+        <v>1</v>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="K320">
+        <v>0</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>84</v>
+      </c>
+      <c r="C321">
+        <v>2</v>
+      </c>
+      <c r="D321">
+        <v>1</v>
+      </c>
+      <c r="E321">
+        <v>4</v>
+      </c>
+      <c r="F321">
+        <v>1</v>
+      </c>
+      <c r="G321">
+        <v>1</v>
+      </c>
+      <c r="H321">
+        <v>0</v>
+      </c>
+      <c r="I321">
+        <v>1</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>0</v>
+      </c>
+      <c r="L321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>59</v>
+      </c>
+      <c r="C322">
+        <v>2</v>
+      </c>
+      <c r="D322">
+        <v>1</v>
+      </c>
+      <c r="E322">
+        <v>4</v>
+      </c>
+      <c r="F322">
+        <v>0</v>
+      </c>
+      <c r="G322">
+        <v>1</v>
+      </c>
+      <c r="H322">
+        <v>0</v>
+      </c>
+      <c r="I322">
+        <v>1</v>
+      </c>
+      <c r="J322">
+        <v>0</v>
+      </c>
+      <c r="K322">
+        <v>0</v>
+      </c>
+      <c r="L322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>2</v>
+      </c>
+      <c r="C323">
+        <v>3</v>
+      </c>
+      <c r="D323">
+        <v>3</v>
+      </c>
+      <c r="E323">
+        <v>2</v>
+      </c>
+      <c r="F323">
+        <v>3</v>
+      </c>
+      <c r="G323">
+        <v>1</v>
+      </c>
+      <c r="H323">
+        <v>1</v>
+      </c>
+      <c r="I323">
+        <v>0</v>
+      </c>
+      <c r="J323">
+        <v>0</v>
+      </c>
+      <c r="K323">
+        <v>0</v>
+      </c>
+      <c r="L323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>110</v>
+      </c>
+      <c r="C324">
+        <v>3</v>
+      </c>
+      <c r="D324">
+        <v>3</v>
+      </c>
+      <c r="E324">
+        <v>2</v>
+      </c>
+      <c r="F324">
+        <v>1</v>
+      </c>
+      <c r="G324">
+        <v>1</v>
+      </c>
+      <c r="H324">
+        <v>1</v>
+      </c>
+      <c r="I324">
+        <v>0</v>
+      </c>
+      <c r="J324">
+        <v>0</v>
+      </c>
+      <c r="K324">
+        <v>0</v>
+      </c>
+      <c r="L324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>29</v>
+      </c>
+      <c r="C325">
+        <v>3</v>
+      </c>
+      <c r="D325">
+        <v>3</v>
+      </c>
+      <c r="E325">
+        <v>2</v>
+      </c>
+      <c r="F325">
+        <v>0</v>
+      </c>
+      <c r="G325">
+        <v>1</v>
+      </c>
+      <c r="H325">
+        <v>1</v>
+      </c>
+      <c r="I325">
+        <v>0</v>
+      </c>
+      <c r="J325">
+        <v>0</v>
+      </c>
+      <c r="K325">
+        <v>0</v>
+      </c>
+      <c r="L325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>24</v>
+      </c>
+      <c r="C326">
+        <v>3</v>
+      </c>
+      <c r="D326">
+        <v>3</v>
+      </c>
+      <c r="E326">
+        <v>2</v>
+      </c>
+      <c r="F326">
+        <v>1</v>
+      </c>
+      <c r="G326">
+        <v>1</v>
+      </c>
+      <c r="H326">
+        <v>1</v>
+      </c>
+      <c r="I326">
+        <v>0</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326">
+        <v>0</v>
+      </c>
+      <c r="L326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>36</v>
+      </c>
+      <c r="C327">
+        <v>3</v>
+      </c>
+      <c r="D327">
+        <v>3</v>
+      </c>
+      <c r="E327">
+        <v>2</v>
+      </c>
+      <c r="F327">
+        <v>1</v>
+      </c>
+      <c r="G327">
+        <v>1</v>
+      </c>
+      <c r="H327">
+        <v>1</v>
+      </c>
+      <c r="I327">
+        <v>0</v>
+      </c>
+      <c r="J327">
+        <v>0</v>
+      </c>
+      <c r="K327">
+        <v>0</v>
+      </c>
+      <c r="L327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>3</v>
+      </c>
+      <c r="C328">
+        <v>3</v>
+      </c>
+      <c r="D328">
+        <v>3</v>
+      </c>
+      <c r="E328">
+        <v>2</v>
+      </c>
+      <c r="F328">
+        <v>1</v>
+      </c>
+      <c r="G328">
+        <v>1</v>
+      </c>
+      <c r="H328">
+        <v>1</v>
+      </c>
+      <c r="I328">
+        <v>0</v>
+      </c>
+      <c r="J328">
+        <v>0</v>
+      </c>
+      <c r="K328">
+        <v>0</v>
+      </c>
+      <c r="L328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>27</v>
+      </c>
+      <c r="C329">
+        <v>3</v>
+      </c>
+      <c r="D329">
+        <v>3</v>
+      </c>
+      <c r="E329">
+        <v>2</v>
+      </c>
+      <c r="F329">
+        <v>2</v>
+      </c>
+      <c r="G329">
+        <v>1</v>
+      </c>
+      <c r="H329">
+        <v>1</v>
+      </c>
+      <c r="I329">
+        <v>0</v>
+      </c>
+      <c r="J329">
+        <v>0</v>
+      </c>
+      <c r="K329">
+        <v>0</v>
+      </c>
+      <c r="L329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>43</v>
+      </c>
+      <c r="C330">
+        <v>3</v>
+      </c>
+      <c r="D330">
+        <v>3</v>
+      </c>
+      <c r="E330">
+        <v>2</v>
+      </c>
+      <c r="F330">
+        <v>2</v>
+      </c>
+      <c r="G330">
+        <v>1</v>
+      </c>
+      <c r="H330">
+        <v>1</v>
+      </c>
+      <c r="I330">
+        <v>0</v>
+      </c>
+      <c r="J330">
+        <v>0</v>
+      </c>
+      <c r="K330">
+        <v>0</v>
+      </c>
+      <c r="L330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>25</v>
+      </c>
+      <c r="C331">
+        <v>3</v>
+      </c>
+      <c r="D331">
+        <v>3</v>
+      </c>
+      <c r="E331">
+        <v>2</v>
+      </c>
+      <c r="F331">
+        <v>1</v>
+      </c>
+      <c r="G331">
+        <v>1</v>
+      </c>
+      <c r="H331">
+        <v>1</v>
+      </c>
+      <c r="I331">
+        <v>0</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>0</v>
+      </c>
+      <c r="L331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>20</v>
+      </c>
+      <c r="C332">
+        <v>3</v>
+      </c>
+      <c r="D332">
+        <v>3</v>
+      </c>
+      <c r="E332">
+        <v>2</v>
+      </c>
+      <c r="F332">
+        <v>0</v>
+      </c>
+      <c r="G332">
+        <v>1</v>
+      </c>
+      <c r="H332">
+        <v>1</v>
+      </c>
+      <c r="I332">
+        <v>0</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332">
+        <v>0</v>
+      </c>
+      <c r="L332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>21</v>
+      </c>
+      <c r="C333">
+        <v>3</v>
+      </c>
+      <c r="D333">
+        <v>1</v>
+      </c>
+      <c r="E333">
+        <v>3</v>
+      </c>
+      <c r="F333">
+        <v>1</v>
+      </c>
+      <c r="G333">
+        <v>1</v>
+      </c>
+      <c r="H333">
+        <v>0</v>
+      </c>
+      <c r="I333">
+        <v>0</v>
+      </c>
+      <c r="J333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>0</v>
+      </c>
+      <c r="L333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>117</v>
+      </c>
+      <c r="C334">
+        <v>3</v>
+      </c>
+      <c r="D334">
+        <v>1</v>
+      </c>
+      <c r="E334">
+        <v>3</v>
+      </c>
+      <c r="F334">
+        <v>2</v>
+      </c>
+      <c r="G334">
+        <v>1</v>
+      </c>
+      <c r="H334">
+        <v>0</v>
+      </c>
+      <c r="I334">
+        <v>0</v>
+      </c>
+      <c r="J334">
+        <v>0</v>
+      </c>
+      <c r="K334">
+        <v>0</v>
+      </c>
+      <c r="L334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>1</v>
+      </c>
+      <c r="C335">
+        <v>3</v>
+      </c>
+      <c r="D335">
+        <v>1</v>
+      </c>
+      <c r="E335">
+        <v>3</v>
+      </c>
+      <c r="F335">
+        <v>2</v>
+      </c>
+      <c r="G335">
+        <v>1</v>
+      </c>
+      <c r="H335">
+        <v>0</v>
+      </c>
+      <c r="I335">
+        <v>0</v>
+      </c>
+      <c r="J335">
+        <v>0</v>
+      </c>
+      <c r="K335">
+        <v>0</v>
+      </c>
+      <c r="L335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>4</v>
+      </c>
+      <c r="C336">
+        <v>3</v>
+      </c>
+      <c r="D336">
+        <v>1</v>
+      </c>
+      <c r="E336">
+        <v>3</v>
+      </c>
+      <c r="F336">
+        <v>1</v>
+      </c>
+      <c r="G336">
+        <v>1</v>
+      </c>
+      <c r="H336">
+        <v>0</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
+      </c>
+      <c r="K336">
+        <v>0</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>6</v>
+      </c>
+      <c r="C337">
+        <v>3</v>
+      </c>
+      <c r="D337">
+        <v>1</v>
+      </c>
+      <c r="E337">
+        <v>3</v>
+      </c>
+      <c r="F337">
+        <v>0</v>
+      </c>
+      <c r="G337">
+        <v>1</v>
+      </c>
+      <c r="H337">
+        <v>0</v>
+      </c>
+      <c r="I337">
+        <v>0</v>
+      </c>
+      <c r="J337">
+        <v>0</v>
+      </c>
+      <c r="K337">
+        <v>0</v>
+      </c>
+      <c r="L337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>108</v>
+      </c>
+      <c r="C338">
+        <v>4</v>
+      </c>
+      <c r="D338">
+        <v>2</v>
+      </c>
+      <c r="E338">
+        <v>3</v>
+      </c>
+      <c r="F338">
+        <v>0</v>
+      </c>
+      <c r="G338">
+        <v>1</v>
+      </c>
+      <c r="H338">
+        <v>1</v>
+      </c>
+      <c r="I338">
+        <v>0</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338">
+        <v>5</v>
+      </c>
+      <c r="L338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>96</v>
+      </c>
+      <c r="C339">
+        <v>4</v>
+      </c>
+      <c r="D339">
+        <v>2</v>
+      </c>
+      <c r="E339">
+        <v>4</v>
+      </c>
+      <c r="F339">
+        <v>0</v>
+      </c>
+      <c r="G339">
+        <v>1</v>
+      </c>
+      <c r="H339">
+        <v>0</v>
+      </c>
+      <c r="I339">
+        <v>0</v>
+      </c>
+      <c r="J339">
+        <v>0</v>
+      </c>
+      <c r="K339">
+        <v>5</v>
+      </c>
+      <c r="L339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>118</v>
+      </c>
+      <c r="C340">
+        <v>2</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>3</v>
+      </c>
+      <c r="F340">
+        <v>0</v>
+      </c>
+      <c r="G340">
+        <v>1</v>
+      </c>
+      <c r="H340">
+        <v>0</v>
+      </c>
+      <c r="I340">
+        <v>1</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340">
+        <v>0</v>
+      </c>
+      <c r="L340">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1541" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A6244A9-3827-4EB7-AF1C-CA479AAF00FF}"/>
+  <xr:revisionPtr revIDLastSave="1544" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A158EEA0-91E8-47BB-96E7-9709B0CC7C4B}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12420,7 +12420,7 @@
         <v>3</v>
       </c>
       <c r="F334">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -12455,7 +12455,7 @@
         <v>3</v>
       </c>
       <c r="F335">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G335">
         <v>1</v>
@@ -12490,7 +12490,7 @@
         <v>3</v>
       </c>
       <c r="F336">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G336">
         <v>1</v>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1544" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A158EEA0-91E8-47BB-96E7-9709B0CC7C4B}"/>
+  <xr:revisionPtr revIDLastSave="1671" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{348EFD65-52BE-442A-B516-9C276BF4555E}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="124">
   <si>
     <t>Boneco</t>
   </si>
@@ -397,6 +397,21 @@
   <si>
     <t>Gabriel</t>
   </si>
+  <si>
+    <t>Luan</t>
+  </si>
+  <si>
+    <t>Luciano</t>
+  </si>
+  <si>
+    <t>Hudson</t>
+  </si>
+  <si>
+    <t>david</t>
+  </si>
+  <si>
+    <t>joão</t>
+  </si>
 </sst>
 </file>
 
@@ -722,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O340"/>
+  <dimension ref="A1:O363"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -12651,6 +12666,811 @@
         <v>0</v>
       </c>
     </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>119</v>
+      </c>
+      <c r="C341">
+        <v>4</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>5</v>
+      </c>
+      <c r="F341">
+        <v>3</v>
+      </c>
+      <c r="G341">
+        <v>1</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+      <c r="I341">
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>0</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>29</v>
+      </c>
+      <c r="C342">
+        <v>4</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>5</v>
+      </c>
+      <c r="F342">
+        <v>0</v>
+      </c>
+      <c r="G342">
+        <v>1</v>
+      </c>
+      <c r="H342">
+        <v>0</v>
+      </c>
+      <c r="I342">
+        <v>0</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342">
+        <v>0</v>
+      </c>
+      <c r="L342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>30</v>
+      </c>
+      <c r="C343">
+        <v>4</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>5</v>
+      </c>
+      <c r="F343">
+        <v>1</v>
+      </c>
+      <c r="G343">
+        <v>1</v>
+      </c>
+      <c r="H343">
+        <v>0</v>
+      </c>
+      <c r="I343">
+        <v>0</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343">
+        <v>0</v>
+      </c>
+      <c r="L343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>84</v>
+      </c>
+      <c r="C344">
+        <v>4</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>5</v>
+      </c>
+      <c r="F344">
+        <v>0</v>
+      </c>
+      <c r="G344">
+        <v>1</v>
+      </c>
+      <c r="H344">
+        <v>0</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>0</v>
+      </c>
+      <c r="K344">
+        <v>0</v>
+      </c>
+      <c r="L344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>25</v>
+      </c>
+      <c r="C345">
+        <v>4</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>5</v>
+      </c>
+      <c r="F345">
+        <v>2</v>
+      </c>
+      <c r="G345">
+        <v>1</v>
+      </c>
+      <c r="H345">
+        <v>0</v>
+      </c>
+      <c r="I345">
+        <v>0</v>
+      </c>
+      <c r="J345">
+        <v>0</v>
+      </c>
+      <c r="K345">
+        <v>0</v>
+      </c>
+      <c r="L345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>120</v>
+      </c>
+      <c r="C346">
+        <v>4</v>
+      </c>
+      <c r="D346">
+        <v>3</v>
+      </c>
+      <c r="E346">
+        <v>1</v>
+      </c>
+      <c r="F346">
+        <v>1</v>
+      </c>
+      <c r="G346">
+        <v>1</v>
+      </c>
+      <c r="H346">
+        <v>1</v>
+      </c>
+      <c r="I346">
+        <v>0</v>
+      </c>
+      <c r="J346">
+        <v>0</v>
+      </c>
+      <c r="K346">
+        <v>0</v>
+      </c>
+      <c r="L346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>20</v>
+      </c>
+      <c r="C347">
+        <v>4</v>
+      </c>
+      <c r="D347">
+        <v>3</v>
+      </c>
+      <c r="E347">
+        <v>1</v>
+      </c>
+      <c r="F347">
+        <v>0</v>
+      </c>
+      <c r="G347">
+        <v>1</v>
+      </c>
+      <c r="H347">
+        <v>1</v>
+      </c>
+      <c r="I347">
+        <v>0</v>
+      </c>
+      <c r="J347">
+        <v>0</v>
+      </c>
+      <c r="K347">
+        <v>0</v>
+      </c>
+      <c r="L347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>3</v>
+      </c>
+      <c r="C348">
+        <v>4</v>
+      </c>
+      <c r="D348">
+        <v>3</v>
+      </c>
+      <c r="E348">
+        <v>1</v>
+      </c>
+      <c r="F348">
+        <v>1</v>
+      </c>
+      <c r="G348">
+        <v>1</v>
+      </c>
+      <c r="H348">
+        <v>1</v>
+      </c>
+      <c r="I348">
+        <v>0</v>
+      </c>
+      <c r="J348">
+        <v>0</v>
+      </c>
+      <c r="K348">
+        <v>0</v>
+      </c>
+      <c r="L348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>34</v>
+      </c>
+      <c r="C349">
+        <v>4</v>
+      </c>
+      <c r="D349">
+        <v>3</v>
+      </c>
+      <c r="E349">
+        <v>1</v>
+      </c>
+      <c r="F349">
+        <v>3</v>
+      </c>
+      <c r="G349">
+        <v>1</v>
+      </c>
+      <c r="H349">
+        <v>1</v>
+      </c>
+      <c r="I349">
+        <v>0</v>
+      </c>
+      <c r="J349">
+        <v>0</v>
+      </c>
+      <c r="K349">
+        <v>0</v>
+      </c>
+      <c r="L349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>36</v>
+      </c>
+      <c r="C350">
+        <v>4</v>
+      </c>
+      <c r="D350">
+        <v>3</v>
+      </c>
+      <c r="E350">
+        <v>1</v>
+      </c>
+      <c r="F350">
+        <v>5</v>
+      </c>
+      <c r="G350">
+        <v>1</v>
+      </c>
+      <c r="H350">
+        <v>1</v>
+      </c>
+      <c r="I350">
+        <v>0</v>
+      </c>
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350">
+        <v>0</v>
+      </c>
+      <c r="L350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>27</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+      <c r="D351">
+        <v>3</v>
+      </c>
+      <c r="E351">
+        <v>3</v>
+      </c>
+      <c r="F351">
+        <v>2</v>
+      </c>
+      <c r="G351">
+        <v>1</v>
+      </c>
+      <c r="H351">
+        <v>0</v>
+      </c>
+      <c r="I351">
+        <v>1</v>
+      </c>
+      <c r="J351">
+        <v>0</v>
+      </c>
+      <c r="K351">
+        <v>0</v>
+      </c>
+      <c r="L351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>4</v>
+      </c>
+      <c r="C352">
+        <v>1</v>
+      </c>
+      <c r="D352">
+        <v>3</v>
+      </c>
+      <c r="E352">
+        <v>3</v>
+      </c>
+      <c r="F352">
+        <v>1</v>
+      </c>
+      <c r="G352">
+        <v>1</v>
+      </c>
+      <c r="H352">
+        <v>0</v>
+      </c>
+      <c r="I352">
+        <v>1</v>
+      </c>
+      <c r="J352">
+        <v>0</v>
+      </c>
+      <c r="K352">
+        <v>0</v>
+      </c>
+      <c r="L352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>32</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+      <c r="D353">
+        <v>3</v>
+      </c>
+      <c r="E353">
+        <v>3</v>
+      </c>
+      <c r="F353">
+        <v>2</v>
+      </c>
+      <c r="G353">
+        <v>1</v>
+      </c>
+      <c r="H353">
+        <v>0</v>
+      </c>
+      <c r="I353">
+        <v>1</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353">
+        <v>0</v>
+      </c>
+      <c r="L353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>28</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+      <c r="D354">
+        <v>3</v>
+      </c>
+      <c r="E354">
+        <v>3</v>
+      </c>
+      <c r="F354">
+        <v>0</v>
+      </c>
+      <c r="G354">
+        <v>1</v>
+      </c>
+      <c r="H354">
+        <v>0</v>
+      </c>
+      <c r="I354">
+        <v>1</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354">
+        <v>0</v>
+      </c>
+      <c r="L354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>121</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+      <c r="D355">
+        <v>3</v>
+      </c>
+      <c r="E355">
+        <v>3</v>
+      </c>
+      <c r="F355">
+        <v>0</v>
+      </c>
+      <c r="G355">
+        <v>1</v>
+      </c>
+      <c r="H355">
+        <v>0</v>
+      </c>
+      <c r="I355">
+        <v>1</v>
+      </c>
+      <c r="J355">
+        <v>0</v>
+      </c>
+      <c r="K355">
+        <v>0</v>
+      </c>
+      <c r="L355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>122</v>
+      </c>
+      <c r="C356">
+        <v>3</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>4</v>
+      </c>
+      <c r="F356">
+        <v>1</v>
+      </c>
+      <c r="G356">
+        <v>1</v>
+      </c>
+      <c r="H356">
+        <v>0</v>
+      </c>
+      <c r="I356">
+        <v>0</v>
+      </c>
+      <c r="J356">
+        <v>0</v>
+      </c>
+      <c r="K356">
+        <v>0</v>
+      </c>
+      <c r="L356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>6</v>
+      </c>
+      <c r="C357">
+        <v>3</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>4</v>
+      </c>
+      <c r="F357">
+        <v>0</v>
+      </c>
+      <c r="G357">
+        <v>1</v>
+      </c>
+      <c r="H357">
+        <v>0</v>
+      </c>
+      <c r="I357">
+        <v>0</v>
+      </c>
+      <c r="J357">
+        <v>0</v>
+      </c>
+      <c r="K357">
+        <v>0</v>
+      </c>
+      <c r="L357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>57</v>
+      </c>
+      <c r="C358">
+        <v>3</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>4</v>
+      </c>
+      <c r="F358">
+        <v>1</v>
+      </c>
+      <c r="G358">
+        <v>1</v>
+      </c>
+      <c r="H358">
+        <v>0</v>
+      </c>
+      <c r="I358">
+        <v>0</v>
+      </c>
+      <c r="J358">
+        <v>0</v>
+      </c>
+      <c r="K358">
+        <v>0</v>
+      </c>
+      <c r="L358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>110</v>
+      </c>
+      <c r="C359">
+        <v>3</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>4</v>
+      </c>
+      <c r="F359">
+        <v>0</v>
+      </c>
+      <c r="G359">
+        <v>1</v>
+      </c>
+      <c r="H359">
+        <v>0</v>
+      </c>
+      <c r="I359">
+        <v>0</v>
+      </c>
+      <c r="J359">
+        <v>0</v>
+      </c>
+      <c r="K359">
+        <v>0</v>
+      </c>
+      <c r="L359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>21</v>
+      </c>
+      <c r="C360">
+        <v>3</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>4</v>
+      </c>
+      <c r="F360">
+        <v>4</v>
+      </c>
+      <c r="G360">
+        <v>1</v>
+      </c>
+      <c r="H360">
+        <v>0</v>
+      </c>
+      <c r="I360">
+        <v>0</v>
+      </c>
+      <c r="J360">
+        <v>0</v>
+      </c>
+      <c r="K360">
+        <v>0</v>
+      </c>
+      <c r="L360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>25</v>
+      </c>
+      <c r="C361">
+        <v>3</v>
+      </c>
+      <c r="D361">
+        <v>1</v>
+      </c>
+      <c r="E361">
+        <v>4</v>
+      </c>
+      <c r="F361">
+        <v>0</v>
+      </c>
+      <c r="G361">
+        <v>1</v>
+      </c>
+      <c r="H361">
+        <v>0</v>
+      </c>
+      <c r="I361">
+        <v>1</v>
+      </c>
+      <c r="J361">
+        <v>0</v>
+      </c>
+      <c r="K361">
+        <v>9</v>
+      </c>
+      <c r="L361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>45</v>
+      </c>
+      <c r="C362">
+        <v>4</v>
+      </c>
+      <c r="D362">
+        <v>1</v>
+      </c>
+      <c r="E362">
+        <v>4</v>
+      </c>
+      <c r="F362">
+        <v>0</v>
+      </c>
+      <c r="G362">
+        <v>1</v>
+      </c>
+      <c r="H362">
+        <v>0</v>
+      </c>
+      <c r="I362">
+        <v>0</v>
+      </c>
+      <c r="J362">
+        <v>0</v>
+      </c>
+      <c r="K362">
+        <v>9</v>
+      </c>
+      <c r="L362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>123</v>
+      </c>
+      <c r="C363">
+        <v>4</v>
+      </c>
+      <c r="D363">
+        <v>2</v>
+      </c>
+      <c r="E363">
+        <v>3</v>
+      </c>
+      <c r="F363">
+        <v>0</v>
+      </c>
+      <c r="G363">
+        <v>1</v>
+      </c>
+      <c r="H363">
+        <v>1</v>
+      </c>
+      <c r="I363">
+        <v>0</v>
+      </c>
+      <c r="J363">
+        <v>0</v>
+      </c>
+      <c r="K363">
+        <v>3</v>
+      </c>
+      <c r="L363">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1671" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{348EFD65-52BE-442A-B516-9C276BF4555E}"/>
+  <xr:revisionPtr revIDLastSave="1673" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8182383-098E-466E-A1F1-8443A01373F1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="123">
   <si>
     <t>Boneco</t>
   </si>
@@ -407,9 +407,6 @@
     <t>Hudson</t>
   </si>
   <si>
-    <t>david</t>
-  </si>
-  <si>
     <t>joão</t>
   </si>
 </sst>
@@ -737,7 +734,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O363"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:O456"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -781,7 +779,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -816,7 +814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -851,7 +849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -886,7 +884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -921,7 +919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -956,7 +954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -991,7 +989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1026,7 +1024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1061,7 +1059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1096,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1131,7 +1129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1166,7 +1164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1201,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1236,7 +1234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1271,7 +1269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1306,7 +1304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1341,7 +1339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1376,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1411,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1481,7 +1479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -1516,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -1551,7 +1549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -1586,7 +1584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1622,7 +1620,7 @@
       </c>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -1658,7 +1656,7 @@
       </c>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1694,7 +1692,7 @@
       </c>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -1730,7 +1728,7 @@
       </c>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1764,7 @@
       </c>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -1802,7 +1800,7 @@
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1838,7 +1836,7 @@
       </c>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -1874,7 +1872,7 @@
       </c>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -1910,7 +1908,7 @@
       </c>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -1946,7 +1944,7 @@
       </c>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -1982,7 +1980,7 @@
       </c>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -2018,7 +2016,7 @@
       </c>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>47</v>
       </c>
@@ -2054,7 +2052,7 @@
       </c>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -2090,7 +2088,7 @@
       </c>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>49</v>
       </c>
@@ -2126,7 +2124,7 @@
       </c>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -2162,7 +2160,7 @@
       </c>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2198,7 +2196,7 @@
       </c>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -2234,7 +2232,7 @@
       </c>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -2270,7 +2268,7 @@
       </c>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>54</v>
       </c>
@@ -2306,7 +2304,7 @@
       </c>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>55</v>
       </c>
@@ -2341,7 +2339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -2376,7 +2374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>57</v>
       </c>
@@ -2411,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>58</v>
       </c>
@@ -2446,7 +2444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -2481,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -2516,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -2551,7 +2549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -2586,7 +2584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -2621,7 +2619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>64</v>
       </c>
@@ -2656,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -2691,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -2726,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>67</v>
       </c>
@@ -2761,7 +2759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -2796,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -2831,7 +2829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -2866,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>71</v>
       </c>
@@ -2901,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>72</v>
       </c>
@@ -2936,7 +2934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>73</v>
       </c>
@@ -2971,7 +2969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -3006,7 +3004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -3041,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -3076,7 +3074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>77</v>
       </c>
@@ -3111,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -3146,7 +3144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -3181,7 +3179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -3216,7 +3214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -3251,7 +3249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>82</v>
       </c>
@@ -3286,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -3321,7 +3319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -3356,7 +3354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -3391,7 +3389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -3426,7 +3424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -3461,7 +3459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -3496,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>89</v>
       </c>
@@ -3531,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -3566,7 +3564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -3601,7 +3599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -3636,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -3671,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -3706,7 +3704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>95</v>
       </c>
@@ -3741,7 +3739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>96</v>
       </c>
@@ -3776,7 +3774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -3811,7 +3809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>98</v>
       </c>
@@ -3846,7 +3844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -3881,7 +3879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>100</v>
       </c>
@@ -3916,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>101</v>
       </c>
@@ -3951,7 +3949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -3986,7 +3984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>102</v>
       </c>
@@ -4021,7 +4019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>103</v>
       </c>
@@ -4056,7 +4054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>63</v>
       </c>
@@ -4091,7 +4089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>59</v>
       </c>
@@ -4126,7 +4124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -4161,7 +4159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>36</v>
       </c>
@@ -4196,7 +4194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>104</v>
       </c>
@@ -4231,7 +4229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>37</v>
       </c>
@@ -4266,7 +4264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>35</v>
       </c>
@@ -4301,7 +4299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>1</v>
       </c>
@@ -4336,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -4371,7 +4369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -4406,7 +4404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>79</v>
       </c>
@@ -4441,7 +4439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>39</v>
       </c>
@@ -4476,7 +4474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>28</v>
       </c>
@@ -4511,7 +4509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>7</v>
       </c>
@@ -4546,7 +4544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -4581,7 +4579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -4616,7 +4614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>0</v>
       </c>
@@ -4651,7 +4649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>3</v>
       </c>
@@ -4686,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>23</v>
       </c>
@@ -4721,7 +4719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>2</v>
       </c>
@@ -4756,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>36</v>
       </c>
@@ -4791,7 +4789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>21</v>
       </c>
@@ -4826,7 +4824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>2</v>
       </c>
@@ -4861,7 +4859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>59</v>
       </c>
@@ -4896,7 +4894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>106</v>
       </c>
@@ -4931,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>27</v>
       </c>
@@ -4966,7 +4964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>107</v>
       </c>
@@ -5001,7 +4999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>1</v>
       </c>
@@ -5036,7 +5034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>34</v>
       </c>
@@ -5071,7 +5069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>23</v>
       </c>
@@ -5106,7 +5104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -5141,7 +5139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -5176,7 +5174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>29</v>
       </c>
@@ -5211,7 +5209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>38</v>
       </c>
@@ -5246,7 +5244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>37</v>
       </c>
@@ -5281,7 +5279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>30</v>
       </c>
@@ -5316,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -5351,7 +5349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>25</v>
       </c>
@@ -5386,7 +5384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -5421,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>28</v>
       </c>
@@ -5456,7 +5454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>108</v>
       </c>
@@ -5491,7 +5489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>45</v>
       </c>
@@ -5526,7 +5524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>108</v>
       </c>
@@ -5561,7 +5559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>45</v>
       </c>
@@ -5596,7 +5594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>41</v>
       </c>
@@ -5631,7 +5629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>27</v>
       </c>
@@ -5666,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>57</v>
       </c>
@@ -5736,7 +5734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>6</v>
       </c>
@@ -5771,7 +5769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>50</v>
       </c>
@@ -5806,7 +5804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -5841,7 +5839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -5876,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>1</v>
       </c>
@@ -5911,7 +5909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>36</v>
       </c>
@@ -5946,7 +5944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>28</v>
       </c>
@@ -5981,7 +5979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>3</v>
       </c>
@@ -6016,7 +6014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>34</v>
       </c>
@@ -6051,7 +6049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>29</v>
       </c>
@@ -6086,7 +6084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -6121,7 +6119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -6156,7 +6154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -6191,7 +6189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>23</v>
       </c>
@@ -6226,7 +6224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>84</v>
       </c>
@@ -6261,7 +6259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>30</v>
       </c>
@@ -6296,7 +6294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>55</v>
       </c>
@@ -6331,7 +6329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>97</v>
       </c>
@@ -6366,7 +6364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -6401,7 +6399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>6</v>
       </c>
@@ -6436,7 +6434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>84</v>
       </c>
@@ -6471,7 +6469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>57</v>
       </c>
@@ -6506,7 +6504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>3</v>
       </c>
@@ -6541,7 +6539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>87</v>
       </c>
@@ -6576,7 +6574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>25</v>
       </c>
@@ -6611,7 +6609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -6646,7 +6644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>79</v>
       </c>
@@ -6681,7 +6679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>34</v>
       </c>
@@ -6716,7 +6714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>23</v>
       </c>
@@ -6751,7 +6749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>30</v>
       </c>
@@ -6786,7 +6784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>28</v>
       </c>
@@ -6821,7 +6819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>2</v>
       </c>
@@ -6856,7 +6854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>36</v>
       </c>
@@ -6926,7 +6924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>106</v>
       </c>
@@ -6961,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -6996,7 +6994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>27</v>
       </c>
@@ -7031,7 +7029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>59</v>
       </c>
@@ -7066,7 +7064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>55</v>
       </c>
@@ -7101,7 +7099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>47</v>
       </c>
@@ -7136,7 +7134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>108</v>
       </c>
@@ -7171,7 +7169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>43</v>
       </c>
@@ -7206,7 +7204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>36</v>
       </c>
@@ -7241,7 +7239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>1</v>
       </c>
@@ -7276,7 +7274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>5</v>
       </c>
@@ -7311,7 +7309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -7346,7 +7344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>57</v>
       </c>
@@ -7416,7 +7414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>34</v>
       </c>
@@ -7451,7 +7449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -7486,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>21</v>
       </c>
@@ -7521,7 +7519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>29</v>
       </c>
@@ -7556,7 +7554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>41</v>
       </c>
@@ -7591,7 +7589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>30</v>
       </c>
@@ -7626,7 +7624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -7661,7 +7659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>23</v>
       </c>
@@ -7696,7 +7694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>27</v>
       </c>
@@ -7731,7 +7729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>28</v>
       </c>
@@ -7766,7 +7764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>2</v>
       </c>
@@ -7801,7 +7799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>20</v>
       </c>
@@ -7836,7 +7834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -7871,7 +7869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>45</v>
       </c>
@@ -7906,7 +7904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>97</v>
       </c>
@@ -7941,7 +7939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>109</v>
       </c>
@@ -7976,7 +7974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>34</v>
       </c>
@@ -8011,7 +8009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>63</v>
       </c>
@@ -8081,7 +8079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -8116,7 +8114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>59</v>
       </c>
@@ -8151,7 +8149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>29</v>
       </c>
@@ -8186,7 +8184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>110</v>
       </c>
@@ -8221,7 +8219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>43</v>
       </c>
@@ -8256,7 +8254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>3</v>
       </c>
@@ -8291,7 +8289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>50</v>
       </c>
@@ -8326,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>111</v>
       </c>
@@ -8361,7 +8359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -8396,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>57</v>
       </c>
@@ -8431,7 +8429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>30</v>
       </c>
@@ -8466,7 +8464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -8501,7 +8499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>5</v>
       </c>
@@ -8536,7 +8534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>112</v>
       </c>
@@ -8571,7 +8569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>41</v>
       </c>
@@ -8606,7 +8604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>0</v>
       </c>
@@ -8641,7 +8639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>113</v>
       </c>
@@ -8676,7 +8674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>45</v>
       </c>
@@ -8711,7 +8709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -8746,7 +8744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>32</v>
       </c>
@@ -8781,7 +8779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>59</v>
       </c>
@@ -8816,7 +8814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>28</v>
       </c>
@@ -8851,7 +8849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>6</v>
       </c>
@@ -8886,7 +8884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>27</v>
       </c>
@@ -8921,7 +8919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>84</v>
       </c>
@@ -8956,7 +8954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>49</v>
       </c>
@@ -8991,7 +8989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>30</v>
       </c>
@@ -9026,7 +9024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>57</v>
       </c>
@@ -9061,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>3</v>
       </c>
@@ -9096,7 +9094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>1</v>
       </c>
@@ -9131,7 +9129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>39</v>
       </c>
@@ -9166,7 +9164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>0</v>
       </c>
@@ -9236,7 +9234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>34</v>
       </c>
@@ -9271,7 +9269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>21</v>
       </c>
@@ -9306,7 +9304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>36</v>
       </c>
@@ -9376,7 +9374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>29</v>
       </c>
@@ -9411,7 +9409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>115</v>
       </c>
@@ -9446,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>45</v>
       </c>
@@ -9481,7 +9479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>25</v>
       </c>
@@ -9516,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -9551,7 +9549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>3</v>
       </c>
@@ -9586,7 +9584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>27</v>
       </c>
@@ -9621,7 +9619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>49</v>
       </c>
@@ -9656,7 +9654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>34</v>
       </c>
@@ -9691,7 +9689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>28</v>
       </c>
@@ -9726,7 +9724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>29</v>
       </c>
@@ -9761,7 +9759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>1</v>
       </c>
@@ -9796,7 +9794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>59</v>
       </c>
@@ -9831,7 +9829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>32</v>
       </c>
@@ -9866,7 +9864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>57</v>
       </c>
@@ -9901,7 +9899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>30</v>
       </c>
@@ -9936,7 +9934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>23</v>
       </c>
@@ -9971,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>4</v>
       </c>
@@ -10041,7 +10039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>39</v>
       </c>
@@ -10076,7 +10074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>84</v>
       </c>
@@ -10111,7 +10109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>20</v>
       </c>
@@ -10146,7 +10144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>33</v>
       </c>
@@ -10181,7 +10179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>108</v>
       </c>
@@ -10216,7 +10214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>116</v>
       </c>
@@ -10251,7 +10249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>45</v>
       </c>
@@ -10286,7 +10284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>27</v>
       </c>
@@ -10321,7 +10319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>49</v>
       </c>
@@ -10356,7 +10354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>28</v>
       </c>
@@ -10391,7 +10389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>34</v>
       </c>
@@ -10426,7 +10424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>20</v>
       </c>
@@ -10461,7 +10459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>5</v>
       </c>
@@ -10496,7 +10494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>43</v>
       </c>
@@ -10531,7 +10529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>21</v>
       </c>
@@ -10566,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>4</v>
       </c>
@@ -10636,7 +10634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>1</v>
       </c>
@@ -10671,7 +10669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>2</v>
       </c>
@@ -10706,7 +10704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>30</v>
       </c>
@@ -10741,7 +10739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>63</v>
       </c>
@@ -10776,7 +10774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>39</v>
       </c>
@@ -10811,7 +10809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>29</v>
       </c>
@@ -10846,7 +10844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>6</v>
       </c>
@@ -10881,7 +10879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>3</v>
       </c>
@@ -10916,7 +10914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>25</v>
       </c>
@@ -10951,7 +10949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>32</v>
       </c>
@@ -10986,7 +10984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>113</v>
       </c>
@@ -11021,7 +11019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>45</v>
       </c>
@@ -11056,7 +11054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>37</v>
       </c>
@@ -11091,7 +11089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>2</v>
       </c>
@@ -11126,7 +11124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>4</v>
       </c>
@@ -11161,7 +11159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>50</v>
       </c>
@@ -11196,7 +11194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>28</v>
       </c>
@@ -11231,7 +11229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>30</v>
       </c>
@@ -11266,7 +11264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>34</v>
       </c>
@@ -11301,7 +11299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>57</v>
       </c>
@@ -11336,7 +11334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>59</v>
       </c>
@@ -11371,7 +11369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>21</v>
       </c>
@@ -11406,7 +11404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>20</v>
       </c>
@@ -11441,7 +11439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>43</v>
       </c>
@@ -11476,7 +11474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>27</v>
       </c>
@@ -11511,7 +11509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>3</v>
       </c>
@@ -11546,7 +11544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>1</v>
       </c>
@@ -11581,7 +11579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>110</v>
       </c>
@@ -11616,7 +11614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>32</v>
       </c>
@@ -11651,7 +11649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>23</v>
       </c>
@@ -11686,7 +11684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>5</v>
       </c>
@@ -11721,7 +11719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>25</v>
       </c>
@@ -11756,7 +11754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>17</v>
       </c>
@@ -11791,7 +11789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>45</v>
       </c>
@@ -11826,7 +11824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>96</v>
       </c>
@@ -11861,7 +11859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>30</v>
       </c>
@@ -11896,7 +11894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>32</v>
       </c>
@@ -11931,7 +11929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>5</v>
       </c>
@@ -11966,7 +11964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>84</v>
       </c>
@@ -12001,7 +11999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>59</v>
       </c>
@@ -12036,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>2</v>
       </c>
@@ -12071,7 +12069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>110</v>
       </c>
@@ -12106,7 +12104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>29</v>
       </c>
@@ -12176,7 +12174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>36</v>
       </c>
@@ -12211,7 +12209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>3</v>
       </c>
@@ -12246,7 +12244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>27</v>
       </c>
@@ -12281,7 +12279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>43</v>
       </c>
@@ -12316,7 +12314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>25</v>
       </c>
@@ -12351,7 +12349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>20</v>
       </c>
@@ -12386,7 +12384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>21</v>
       </c>
@@ -12421,7 +12419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>117</v>
       </c>
@@ -12456,7 +12454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>1</v>
       </c>
@@ -12491,7 +12489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>4</v>
       </c>
@@ -12526,7 +12524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>6</v>
       </c>
@@ -12561,7 +12559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>108</v>
       </c>
@@ -12596,7 +12594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>96</v>
       </c>
@@ -12631,7 +12629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>118</v>
       </c>
@@ -12666,7 +12664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>119</v>
       </c>
@@ -12701,7 +12699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>29</v>
       </c>
@@ -12736,7 +12734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>30</v>
       </c>
@@ -12771,7 +12769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>84</v>
       </c>
@@ -12806,7 +12804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>25</v>
       </c>
@@ -12841,7 +12839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>120</v>
       </c>
@@ -12876,7 +12874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>20</v>
       </c>
@@ -12911,7 +12909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>3</v>
       </c>
@@ -12946,7 +12944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>34</v>
       </c>
@@ -12981,7 +12979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>36</v>
       </c>
@@ -13016,7 +13014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>27</v>
       </c>
@@ -13051,7 +13049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>4</v>
       </c>
@@ -13086,7 +13084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>32</v>
       </c>
@@ -13121,7 +13119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>28</v>
       </c>
@@ -13156,7 +13154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>121</v>
       </c>
@@ -13193,7 +13191,7 @@
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="C356">
         <v>3</v>
@@ -13226,7 +13224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>6</v>
       </c>
@@ -13261,7 +13259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>57</v>
       </c>
@@ -13296,7 +13294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>110</v>
       </c>
@@ -13331,7 +13329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>21</v>
       </c>
@@ -13366,7 +13364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>25</v>
       </c>
@@ -13401,7 +13399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>45</v>
       </c>
@@ -13436,9 +13434,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C363">
         <v>4</v>
@@ -13471,8 +13469,108 @@
         <v>0</v>
       </c>
     </row>
+    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="365" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="368" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="369" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="370" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="371" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="372" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="373" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="374" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="375" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="376" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="377" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="378" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="379" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="380" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="381" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="382" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="383" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="384" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="385" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="386" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="387" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="388" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="389" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="390" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="391" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="392" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="393" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="394" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="395" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="396" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="397" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="398" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="399" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="400" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="401" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="402" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="403" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="404" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="405" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="406" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="407" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="408" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="409" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="410" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="411" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="412" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="413" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="414" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="415" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="416" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="417" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="418" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="419" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="420" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="421" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="422" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="423" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="424" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="425" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="426" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="427" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="428" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="429" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="430" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="431" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="432" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="433" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="434" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="435" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="436" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="437" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="438" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="439" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="440" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="441" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="442" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="443" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="444" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="445" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="446" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="447" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="448" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="449" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="450" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="451" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="452" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="453" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="454" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="455" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="456" hidden="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="David"/>
+        <filter val="Davidson"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1673" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8182383-098E-466E-A1F1-8443A01373F1}"/>
+  <xr:revisionPtr revIDLastSave="1799" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1A24EF-D718-4355-9A32-5745A238FECA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="123">
   <si>
     <t>Boneco</t>
   </si>
@@ -407,7 +407,7 @@
     <t>Hudson</t>
   </si>
   <si>
-    <t>joão</t>
+    <t>Luiz</t>
   </si>
 </sst>
 </file>
@@ -734,8 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O456"/>
+  <dimension ref="A1:O386"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -779,7 +778,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -814,7 +813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -849,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -884,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -919,7 +918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -954,7 +953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -989,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1024,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1059,7 +1058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1094,7 +1093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1129,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1164,7 +1163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1199,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1234,7 +1233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1269,7 +1268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1304,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1339,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1374,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1409,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1479,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -1514,7 +1513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -1549,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -1584,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1620,7 +1619,7 @@
       </c>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -1656,7 +1655,7 @@
       </c>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1692,7 +1691,7 @@
       </c>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -1728,7 +1727,7 @@
       </c>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1764,7 +1763,7 @@
       </c>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -1800,7 +1799,7 @@
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1836,7 +1835,7 @@
       </c>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -1872,7 +1871,7 @@
       </c>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -1908,7 +1907,7 @@
       </c>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -1944,7 +1943,7 @@
       </c>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -1980,7 +1979,7 @@
       </c>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -2016,7 +2015,7 @@
       </c>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>47</v>
       </c>
@@ -2052,7 +2051,7 @@
       </c>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -2088,7 +2087,7 @@
       </c>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>49</v>
       </c>
@@ -2124,7 +2123,7 @@
       </c>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -2160,7 +2159,7 @@
       </c>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2196,7 +2195,7 @@
       </c>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -2232,7 +2231,7 @@
       </c>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -2268,7 +2267,7 @@
       </c>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>54</v>
       </c>
@@ -2304,7 +2303,7 @@
       </c>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>55</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -2374,7 +2373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>57</v>
       </c>
@@ -2409,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>58</v>
       </c>
@@ -2444,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -2479,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -2514,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -2549,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -2584,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -2619,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>64</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -2689,7 +2688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -2724,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>67</v>
       </c>
@@ -2759,7 +2758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -2794,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -2829,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -2864,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>71</v>
       </c>
@@ -2899,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>72</v>
       </c>
@@ -2934,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>73</v>
       </c>
@@ -2969,7 +2968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -3004,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -3039,7 +3038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -3074,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>77</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -3144,7 +3143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -3179,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -3214,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -3249,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>82</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -3319,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -3354,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -3389,7 +3388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -3424,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -3459,7 +3458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>89</v>
       </c>
@@ -3529,7 +3528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -3564,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -3599,7 +3598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -3634,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -3669,7 +3668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -3704,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>95</v>
       </c>
@@ -3739,7 +3738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>96</v>
       </c>
@@ -3774,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -3809,7 +3808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>98</v>
       </c>
@@ -3844,7 +3843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -3879,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>100</v>
       </c>
@@ -3914,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>101</v>
       </c>
@@ -3949,7 +3948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -3984,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>102</v>
       </c>
@@ -4019,7 +4018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>103</v>
       </c>
@@ -4054,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>63</v>
       </c>
@@ -4089,7 +4088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>59</v>
       </c>
@@ -4124,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -4159,7 +4158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>36</v>
       </c>
@@ -4194,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>104</v>
       </c>
@@ -4229,7 +4228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>37</v>
       </c>
@@ -4264,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>35</v>
       </c>
@@ -4299,7 +4298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>1</v>
       </c>
@@ -4334,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -4369,7 +4368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -4404,7 +4403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>79</v>
       </c>
@@ -4439,7 +4438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>39</v>
       </c>
@@ -4474,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>28</v>
       </c>
@@ -4509,7 +4508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>7</v>
       </c>
@@ -4544,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -4579,7 +4578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -4614,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>0</v>
       </c>
@@ -4649,7 +4648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>3</v>
       </c>
@@ -4684,7 +4683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>23</v>
       </c>
@@ -4719,7 +4718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>2</v>
       </c>
@@ -4754,7 +4753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>36</v>
       </c>
@@ -4789,7 +4788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>21</v>
       </c>
@@ -4824,7 +4823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>2</v>
       </c>
@@ -4859,7 +4858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>59</v>
       </c>
@@ -4894,7 +4893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>106</v>
       </c>
@@ -4929,7 +4928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>27</v>
       </c>
@@ -4964,7 +4963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>107</v>
       </c>
@@ -4999,7 +4998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>1</v>
       </c>
@@ -5034,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>34</v>
       </c>
@@ -5069,7 +5068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>23</v>
       </c>
@@ -5104,7 +5103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -5139,7 +5138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -5174,7 +5173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>29</v>
       </c>
@@ -5209,7 +5208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>38</v>
       </c>
@@ -5244,7 +5243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>37</v>
       </c>
@@ -5279,7 +5278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>30</v>
       </c>
@@ -5314,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -5349,7 +5348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>25</v>
       </c>
@@ -5384,7 +5383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -5419,7 +5418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>28</v>
       </c>
@@ -5454,7 +5453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>108</v>
       </c>
@@ -5489,7 +5488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>45</v>
       </c>
@@ -5524,7 +5523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>108</v>
       </c>
@@ -5559,7 +5558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>45</v>
       </c>
@@ -5594,7 +5593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>41</v>
       </c>
@@ -5629,7 +5628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>27</v>
       </c>
@@ -5664,7 +5663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>57</v>
       </c>
@@ -5734,7 +5733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>6</v>
       </c>
@@ -5769,7 +5768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>50</v>
       </c>
@@ -5804,7 +5803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -5839,7 +5838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -5874,7 +5873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>1</v>
       </c>
@@ -5909,7 +5908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>36</v>
       </c>
@@ -5944,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>28</v>
       </c>
@@ -5979,7 +5978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>3</v>
       </c>
@@ -6014,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>34</v>
       </c>
@@ -6049,7 +6048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>29</v>
       </c>
@@ -6084,7 +6083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -6119,7 +6118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -6154,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -6189,7 +6188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>23</v>
       </c>
@@ -6224,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>84</v>
       </c>
@@ -6259,7 +6258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>30</v>
       </c>
@@ -6294,7 +6293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>55</v>
       </c>
@@ -6329,7 +6328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>97</v>
       </c>
@@ -6364,7 +6363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -6399,7 +6398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>6</v>
       </c>
@@ -6434,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>84</v>
       </c>
@@ -6469,7 +6468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>57</v>
       </c>
@@ -6504,7 +6503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>3</v>
       </c>
@@ -6539,7 +6538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>87</v>
       </c>
@@ -6574,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>25</v>
       </c>
@@ -6609,7 +6608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -6644,7 +6643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>79</v>
       </c>
@@ -6679,7 +6678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>34</v>
       </c>
@@ -6714,7 +6713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>23</v>
       </c>
@@ -6749,7 +6748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>30</v>
       </c>
@@ -6784,7 +6783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>28</v>
       </c>
@@ -6819,7 +6818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>2</v>
       </c>
@@ -6854,7 +6853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>36</v>
       </c>
@@ -6924,7 +6923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>106</v>
       </c>
@@ -6959,7 +6958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -6994,7 +6993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>27</v>
       </c>
@@ -7029,7 +7028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>59</v>
       </c>
@@ -7064,7 +7063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>55</v>
       </c>
@@ -7099,7 +7098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>47</v>
       </c>
@@ -7134,7 +7133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>108</v>
       </c>
@@ -7169,7 +7168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>43</v>
       </c>
@@ -7204,7 +7203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>36</v>
       </c>
@@ -7239,7 +7238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>1</v>
       </c>
@@ -7274,7 +7273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>5</v>
       </c>
@@ -7309,7 +7308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -7344,7 +7343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>57</v>
       </c>
@@ -7414,7 +7413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>34</v>
       </c>
@@ -7449,7 +7448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -7484,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>21</v>
       </c>
@@ -7519,7 +7518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>29</v>
       </c>
@@ -7554,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>41</v>
       </c>
@@ -7589,7 +7588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>30</v>
       </c>
@@ -7624,7 +7623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -7659,7 +7658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>23</v>
       </c>
@@ -7694,7 +7693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>27</v>
       </c>
@@ -7729,7 +7728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>28</v>
       </c>
@@ -7764,7 +7763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>2</v>
       </c>
@@ -7799,7 +7798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>20</v>
       </c>
@@ -7834,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -7869,7 +7868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>45</v>
       </c>
@@ -7904,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>97</v>
       </c>
@@ -7939,7 +7938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>109</v>
       </c>
@@ -7974,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>34</v>
       </c>
@@ -8009,7 +8008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>63</v>
       </c>
@@ -8079,7 +8078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -8114,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>59</v>
       </c>
@@ -8149,7 +8148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>29</v>
       </c>
@@ -8184,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>110</v>
       </c>
@@ -8219,7 +8218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>43</v>
       </c>
@@ -8254,7 +8253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>3</v>
       </c>
@@ -8289,7 +8288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>50</v>
       </c>
@@ -8324,7 +8323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>111</v>
       </c>
@@ -8359,7 +8358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -8394,7 +8393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>57</v>
       </c>
@@ -8429,7 +8428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>30</v>
       </c>
@@ -8464,7 +8463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -8499,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>5</v>
       </c>
@@ -8534,7 +8533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>112</v>
       </c>
@@ -8569,7 +8568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>41</v>
       </c>
@@ -8604,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>0</v>
       </c>
@@ -8639,7 +8638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>113</v>
       </c>
@@ -8674,7 +8673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>45</v>
       </c>
@@ -8709,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -8744,7 +8743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>32</v>
       </c>
@@ -8779,7 +8778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>59</v>
       </c>
@@ -8814,7 +8813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>28</v>
       </c>
@@ -8849,7 +8848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>6</v>
       </c>
@@ -8884,7 +8883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>27</v>
       </c>
@@ -8919,7 +8918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>84</v>
       </c>
@@ -8954,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>49</v>
       </c>
@@ -8989,7 +8988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>30</v>
       </c>
@@ -9024,7 +9023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>57</v>
       </c>
@@ -9059,7 +9058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>3</v>
       </c>
@@ -9094,7 +9093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>1</v>
       </c>
@@ -9129,7 +9128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>39</v>
       </c>
@@ -9164,7 +9163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>0</v>
       </c>
@@ -9234,7 +9233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>34</v>
       </c>
@@ -9269,7 +9268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>21</v>
       </c>
@@ -9304,7 +9303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>36</v>
       </c>
@@ -9374,7 +9373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>29</v>
       </c>
@@ -9409,7 +9408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>115</v>
       </c>
@@ -9444,7 +9443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>45</v>
       </c>
@@ -9479,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>25</v>
       </c>
@@ -9514,7 +9513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -9549,7 +9548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>3</v>
       </c>
@@ -9584,7 +9583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>27</v>
       </c>
@@ -9619,7 +9618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>49</v>
       </c>
@@ -9654,7 +9653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>34</v>
       </c>
@@ -9689,7 +9688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>28</v>
       </c>
@@ -9724,7 +9723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>29</v>
       </c>
@@ -9759,7 +9758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>1</v>
       </c>
@@ -9794,7 +9793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>59</v>
       </c>
@@ -9829,7 +9828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>32</v>
       </c>
@@ -9864,7 +9863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>57</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>30</v>
       </c>
@@ -9934,7 +9933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>23</v>
       </c>
@@ -9969,7 +9968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>4</v>
       </c>
@@ -10039,7 +10038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>39</v>
       </c>
@@ -10074,7 +10073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>84</v>
       </c>
@@ -10109,7 +10108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>20</v>
       </c>
@@ -10144,7 +10143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>33</v>
       </c>
@@ -10179,7 +10178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>108</v>
       </c>
@@ -10214,7 +10213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>116</v>
       </c>
@@ -10249,7 +10248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>45</v>
       </c>
@@ -10284,7 +10283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>27</v>
       </c>
@@ -10319,7 +10318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>49</v>
       </c>
@@ -10354,7 +10353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>28</v>
       </c>
@@ -10389,7 +10388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>34</v>
       </c>
@@ -10424,7 +10423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>20</v>
       </c>
@@ -10459,7 +10458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>5</v>
       </c>
@@ -10494,7 +10493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>43</v>
       </c>
@@ -10529,7 +10528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>21</v>
       </c>
@@ -10564,7 +10563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>4</v>
       </c>
@@ -10634,7 +10633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>1</v>
       </c>
@@ -10669,7 +10668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>2</v>
       </c>
@@ -10704,7 +10703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>30</v>
       </c>
@@ -10739,7 +10738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>63</v>
       </c>
@@ -10774,7 +10773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>39</v>
       </c>
@@ -10809,7 +10808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>29</v>
       </c>
@@ -10844,7 +10843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>6</v>
       </c>
@@ -10879,7 +10878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>3</v>
       </c>
@@ -10914,7 +10913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>25</v>
       </c>
@@ -10949,7 +10948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>32</v>
       </c>
@@ -10984,7 +10983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>113</v>
       </c>
@@ -11019,7 +11018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>45</v>
       </c>
@@ -11054,7 +11053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>37</v>
       </c>
@@ -11089,7 +11088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>2</v>
       </c>
@@ -11124,7 +11123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>4</v>
       </c>
@@ -11159,7 +11158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>50</v>
       </c>
@@ -11194,7 +11193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>28</v>
       </c>
@@ -11229,7 +11228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>30</v>
       </c>
@@ -11264,7 +11263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>34</v>
       </c>
@@ -11299,7 +11298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>57</v>
       </c>
@@ -11334,7 +11333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>59</v>
       </c>
@@ -11369,7 +11368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>21</v>
       </c>
@@ -11404,7 +11403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>20</v>
       </c>
@@ -11439,7 +11438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>43</v>
       </c>
@@ -11474,7 +11473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>27</v>
       </c>
@@ -11509,7 +11508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>3</v>
       </c>
@@ -11544,7 +11543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>1</v>
       </c>
@@ -11579,7 +11578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>110</v>
       </c>
@@ -11614,7 +11613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>32</v>
       </c>
@@ -11649,7 +11648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>23</v>
       </c>
@@ -11684,7 +11683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>5</v>
       </c>
@@ -11719,7 +11718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>25</v>
       </c>
@@ -11754,7 +11753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>17</v>
       </c>
@@ -11789,7 +11788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>45</v>
       </c>
@@ -11824,7 +11823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>96</v>
       </c>
@@ -11859,7 +11858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>30</v>
       </c>
@@ -11894,7 +11893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>32</v>
       </c>
@@ -11929,7 +11928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>5</v>
       </c>
@@ -11964,7 +11963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>84</v>
       </c>
@@ -11999,7 +11998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>59</v>
       </c>
@@ -12034,7 +12033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>2</v>
       </c>
@@ -12069,7 +12068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>110</v>
       </c>
@@ -12104,7 +12103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>29</v>
       </c>
@@ -12174,7 +12173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>36</v>
       </c>
@@ -12209,7 +12208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>3</v>
       </c>
@@ -12244,7 +12243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>27</v>
       </c>
@@ -12279,7 +12278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>43</v>
       </c>
@@ -12314,7 +12313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>25</v>
       </c>
@@ -12349,7 +12348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>20</v>
       </c>
@@ -12384,7 +12383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>21</v>
       </c>
@@ -12419,7 +12418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>117</v>
       </c>
@@ -12454,7 +12453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>1</v>
       </c>
@@ -12489,7 +12488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>4</v>
       </c>
@@ -12524,7 +12523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>6</v>
       </c>
@@ -12559,7 +12558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>108</v>
       </c>
@@ -12594,7 +12593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>96</v>
       </c>
@@ -12629,7 +12628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>118</v>
       </c>
@@ -12664,7 +12663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>119</v>
       </c>
@@ -12699,7 +12698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>29</v>
       </c>
@@ -12734,7 +12733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>30</v>
       </c>
@@ -12769,7 +12768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>84</v>
       </c>
@@ -12804,7 +12803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>25</v>
       </c>
@@ -12839,7 +12838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>120</v>
       </c>
@@ -12874,7 +12873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>20</v>
       </c>
@@ -12909,7 +12908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>3</v>
       </c>
@@ -12944,7 +12943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>34</v>
       </c>
@@ -12979,7 +12978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>36</v>
       </c>
@@ -13014,7 +13013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>27</v>
       </c>
@@ -13049,7 +13048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>4</v>
       </c>
@@ -13084,7 +13083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>32</v>
       </c>
@@ -13119,7 +13118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>28</v>
       </c>
@@ -13154,7 +13153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>121</v>
       </c>
@@ -13224,7 +13223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>6</v>
       </c>
@@ -13259,7 +13258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>57</v>
       </c>
@@ -13294,7 +13293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>110</v>
       </c>
@@ -13329,7 +13328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>21</v>
       </c>
@@ -13364,7 +13363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>25</v>
       </c>
@@ -13399,7 +13398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>45</v>
       </c>
@@ -13434,143 +13433,848 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
+        <v>80</v>
+      </c>
+      <c r="C363">
+        <v>4</v>
+      </c>
+      <c r="D363">
+        <v>2</v>
+      </c>
+      <c r="E363">
+        <v>3</v>
+      </c>
+      <c r="F363">
+        <v>0</v>
+      </c>
+      <c r="G363">
+        <v>1</v>
+      </c>
+      <c r="H363">
+        <v>1</v>
+      </c>
+      <c r="I363">
+        <v>0</v>
+      </c>
+      <c r="J363">
+        <v>0</v>
+      </c>
+      <c r="K363">
+        <v>3</v>
+      </c>
+      <c r="L363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>29</v>
+      </c>
+      <c r="C364">
+        <v>5</v>
+      </c>
+      <c r="D364">
+        <v>2</v>
+      </c>
+      <c r="E364">
+        <v>2</v>
+      </c>
+      <c r="F364">
+        <v>2</v>
+      </c>
+      <c r="G364">
+        <v>1</v>
+      </c>
+      <c r="H364">
+        <v>1</v>
+      </c>
+      <c r="I364">
+        <v>0</v>
+      </c>
+      <c r="J364">
+        <v>0</v>
+      </c>
+      <c r="K364">
+        <v>0</v>
+      </c>
+      <c r="L364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>5</v>
+      </c>
+      <c r="D365">
+        <v>2</v>
+      </c>
+      <c r="E365">
+        <v>2</v>
+      </c>
+      <c r="F365">
+        <v>4</v>
+      </c>
+      <c r="G365">
+        <v>1</v>
+      </c>
+      <c r="H365">
+        <v>1</v>
+      </c>
+      <c r="I365">
+        <v>0</v>
+      </c>
+      <c r="J365">
+        <v>0</v>
+      </c>
+      <c r="K365">
+        <v>0</v>
+      </c>
+      <c r="L365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>43</v>
+      </c>
+      <c r="C366">
+        <v>5</v>
+      </c>
+      <c r="D366">
+        <v>2</v>
+      </c>
+      <c r="E366">
+        <v>2</v>
+      </c>
+      <c r="F366">
+        <v>2</v>
+      </c>
+      <c r="G366">
+        <v>1</v>
+      </c>
+      <c r="H366">
+        <v>1</v>
+      </c>
+      <c r="I366">
+        <v>0</v>
+      </c>
+      <c r="J366">
+        <v>0</v>
+      </c>
+      <c r="K366">
+        <v>0</v>
+      </c>
+      <c r="L366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>3</v>
+      </c>
+      <c r="C367">
+        <v>5</v>
+      </c>
+      <c r="D367">
+        <v>2</v>
+      </c>
+      <c r="E367">
+        <v>2</v>
+      </c>
+      <c r="F367">
+        <v>1</v>
+      </c>
+      <c r="G367">
+        <v>1</v>
+      </c>
+      <c r="H367">
+        <v>1</v>
+      </c>
+      <c r="I367">
+        <v>0</v>
+      </c>
+      <c r="J367">
+        <v>0</v>
+      </c>
+      <c r="K367">
+        <v>0</v>
+      </c>
+      <c r="L367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>32</v>
+      </c>
+      <c r="C368">
+        <v>5</v>
+      </c>
+      <c r="D368">
+        <v>2</v>
+      </c>
+      <c r="E368">
+        <v>2</v>
+      </c>
+      <c r="F368">
+        <v>0</v>
+      </c>
+      <c r="G368">
+        <v>1</v>
+      </c>
+      <c r="H368">
+        <v>1</v>
+      </c>
+      <c r="I368">
+        <v>0</v>
+      </c>
+      <c r="J368">
+        <v>0</v>
+      </c>
+      <c r="K368">
+        <v>0</v>
+      </c>
+      <c r="L368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>57</v>
+      </c>
+      <c r="C369">
+        <v>3</v>
+      </c>
+      <c r="D369">
+        <v>1</v>
+      </c>
+      <c r="E369">
+        <v>4</v>
+      </c>
+      <c r="F369">
+        <v>5</v>
+      </c>
+      <c r="G369">
+        <v>1</v>
+      </c>
+      <c r="H369">
+        <v>0</v>
+      </c>
+      <c r="I369">
+        <v>0</v>
+      </c>
+      <c r="J369">
+        <v>0</v>
+      </c>
+      <c r="K369">
+        <v>0</v>
+      </c>
+      <c r="L369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>117</v>
+      </c>
+      <c r="C370">
+        <v>3</v>
+      </c>
+      <c r="D370">
+        <v>1</v>
+      </c>
+      <c r="E370">
+        <v>4</v>
+      </c>
+      <c r="F370">
+        <v>1</v>
+      </c>
+      <c r="G370">
+        <v>1</v>
+      </c>
+      <c r="H370">
+        <v>0</v>
+      </c>
+      <c r="I370">
+        <v>0</v>
+      </c>
+      <c r="J370">
+        <v>0</v>
+      </c>
+      <c r="K370">
+        <v>0</v>
+      </c>
+      <c r="L370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>59</v>
+      </c>
+      <c r="C371">
+        <v>3</v>
+      </c>
+      <c r="D371">
+        <v>1</v>
+      </c>
+      <c r="E371">
+        <v>4</v>
+      </c>
+      <c r="F371">
+        <v>0</v>
+      </c>
+      <c r="G371">
+        <v>1</v>
+      </c>
+      <c r="H371">
+        <v>0</v>
+      </c>
+      <c r="I371">
+        <v>0</v>
+      </c>
+      <c r="J371">
+        <v>0</v>
+      </c>
+      <c r="K371">
+        <v>0</v>
+      </c>
+      <c r="L371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>21</v>
+      </c>
+      <c r="C372">
+        <v>3</v>
+      </c>
+      <c r="D372">
+        <v>1</v>
+      </c>
+      <c r="E372">
+        <v>4</v>
+      </c>
+      <c r="F372">
+        <v>0</v>
+      </c>
+      <c r="G372">
+        <v>1</v>
+      </c>
+      <c r="H372">
+        <v>0</v>
+      </c>
+      <c r="I372">
+        <v>0</v>
+      </c>
+      <c r="J372">
+        <v>0</v>
+      </c>
+      <c r="K372">
+        <v>0</v>
+      </c>
+      <c r="L372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>1</v>
+      </c>
+      <c r="C373">
+        <v>3</v>
+      </c>
+      <c r="D373">
+        <v>1</v>
+      </c>
+      <c r="E373">
+        <v>4</v>
+      </c>
+      <c r="F373">
+        <v>1</v>
+      </c>
+      <c r="G373">
+        <v>1</v>
+      </c>
+      <c r="H373">
+        <v>0</v>
+      </c>
+      <c r="I373">
+        <v>0</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373">
+        <v>0</v>
+      </c>
+      <c r="L373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>2</v>
+      </c>
+      <c r="C374">
+        <v>3</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>4</v>
+      </c>
+      <c r="F374">
+        <v>1</v>
+      </c>
+      <c r="G374">
+        <v>1</v>
+      </c>
+      <c r="H374">
+        <v>0</v>
+      </c>
+      <c r="I374">
+        <v>1</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374">
+        <v>0</v>
+      </c>
+      <c r="L374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>30</v>
+      </c>
+      <c r="C375">
+        <v>3</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>4</v>
+      </c>
+      <c r="F375">
+        <v>0</v>
+      </c>
+      <c r="G375">
+        <v>1</v>
+      </c>
+      <c r="H375">
+        <v>0</v>
+      </c>
+      <c r="I375">
+        <v>1</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375">
+        <v>0</v>
+      </c>
+      <c r="L375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>114</v>
+      </c>
+      <c r="C376">
+        <v>3</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>4</v>
+      </c>
+      <c r="F376">
+        <v>4</v>
+      </c>
+      <c r="G376">
+        <v>1</v>
+      </c>
+      <c r="H376">
+        <v>0</v>
+      </c>
+      <c r="I376">
+        <v>1</v>
+      </c>
+      <c r="J376">
+        <v>0</v>
+      </c>
+      <c r="K376">
+        <v>0</v>
+      </c>
+      <c r="L376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>49</v>
+      </c>
+      <c r="C377">
+        <v>3</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>4</v>
+      </c>
+      <c r="F377">
+        <v>0</v>
+      </c>
+      <c r="G377">
+        <v>1</v>
+      </c>
+      <c r="H377">
+        <v>0</v>
+      </c>
+      <c r="I377">
+        <v>1</v>
+      </c>
+      <c r="J377">
+        <v>0</v>
+      </c>
+      <c r="K377">
+        <v>0</v>
+      </c>
+      <c r="L377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>5</v>
+      </c>
+      <c r="C378">
+        <v>3</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>4</v>
+      </c>
+      <c r="F378">
+        <v>1</v>
+      </c>
+      <c r="G378">
+        <v>1</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+      <c r="I378">
+        <v>1</v>
+      </c>
+      <c r="J378">
+        <v>0</v>
+      </c>
+      <c r="K378">
+        <v>0</v>
+      </c>
+      <c r="L378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>27</v>
+      </c>
+      <c r="C379">
+        <v>3</v>
+      </c>
+      <c r="D379">
+        <v>1</v>
+      </c>
+      <c r="E379">
+        <v>3</v>
+      </c>
+      <c r="F379">
+        <v>2</v>
+      </c>
+      <c r="G379">
+        <v>1</v>
+      </c>
+      <c r="H379">
+        <v>0</v>
+      </c>
+      <c r="I379">
+        <v>0</v>
+      </c>
+      <c r="J379">
+        <v>0</v>
+      </c>
+      <c r="K379">
+        <v>0</v>
+      </c>
+      <c r="L379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>28</v>
+      </c>
+      <c r="C380">
+        <v>3</v>
+      </c>
+      <c r="D380">
+        <v>1</v>
+      </c>
+      <c r="E380">
+        <v>3</v>
+      </c>
+      <c r="F380">
+        <v>0</v>
+      </c>
+      <c r="G380">
+        <v>1</v>
+      </c>
+      <c r="H380">
+        <v>0</v>
+      </c>
+      <c r="I380">
+        <v>0</v>
+      </c>
+      <c r="J380">
+        <v>0</v>
+      </c>
+      <c r="K380">
+        <v>0</v>
+      </c>
+      <c r="L380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>36</v>
+      </c>
+      <c r="C381">
+        <v>3</v>
+      </c>
+      <c r="D381">
+        <v>1</v>
+      </c>
+      <c r="E381">
+        <v>3</v>
+      </c>
+      <c r="F381">
+        <v>2</v>
+      </c>
+      <c r="G381">
+        <v>1</v>
+      </c>
+      <c r="H381">
+        <v>0</v>
+      </c>
+      <c r="I381">
+        <v>0</v>
+      </c>
+      <c r="J381">
+        <v>0</v>
+      </c>
+      <c r="K381">
+        <v>0</v>
+      </c>
+      <c r="L381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>34</v>
+      </c>
+      <c r="C382">
+        <v>3</v>
+      </c>
+      <c r="D382">
+        <v>1</v>
+      </c>
+      <c r="E382">
+        <v>3</v>
+      </c>
+      <c r="F382">
+        <v>0</v>
+      </c>
+      <c r="G382">
+        <v>1</v>
+      </c>
+      <c r="H382">
+        <v>0</v>
+      </c>
+      <c r="I382">
+        <v>0</v>
+      </c>
+      <c r="J382">
+        <v>0</v>
+      </c>
+      <c r="K382">
+        <v>0</v>
+      </c>
+      <c r="L382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>20</v>
+      </c>
+      <c r="C383">
+        <v>3</v>
+      </c>
+      <c r="D383">
+        <v>1</v>
+      </c>
+      <c r="E383">
+        <v>3</v>
+      </c>
+      <c r="F383">
+        <v>2</v>
+      </c>
+      <c r="G383">
+        <v>1</v>
+      </c>
+      <c r="H383">
+        <v>0</v>
+      </c>
+      <c r="I383">
+        <v>0</v>
+      </c>
+      <c r="J383">
+        <v>0</v>
+      </c>
+      <c r="K383">
+        <v>0</v>
+      </c>
+      <c r="L383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>17</v>
+      </c>
+      <c r="C384">
+        <v>6</v>
+      </c>
+      <c r="D384">
+        <v>2</v>
+      </c>
+      <c r="E384">
+        <v>5</v>
+      </c>
+      <c r="F384">
+        <v>0</v>
+      </c>
+      <c r="G384">
+        <v>1</v>
+      </c>
+      <c r="H384">
+        <v>1</v>
+      </c>
+      <c r="I384">
+        <v>0</v>
+      </c>
+      <c r="J384">
+        <v>0</v>
+      </c>
+      <c r="K384">
+        <v>9</v>
+      </c>
+      <c r="L384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>118</v>
+      </c>
+      <c r="C385">
+        <v>4</v>
+      </c>
+      <c r="D385">
+        <v>2</v>
+      </c>
+      <c r="E385">
+        <v>4</v>
+      </c>
+      <c r="F385">
+        <v>0</v>
+      </c>
+      <c r="G385">
+        <v>1</v>
+      </c>
+      <c r="H385">
+        <v>0</v>
+      </c>
+      <c r="I385">
+        <v>0</v>
+      </c>
+      <c r="J385">
+        <v>0</v>
+      </c>
+      <c r="K385">
+        <v>9</v>
+      </c>
+      <c r="L385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
         <v>122</v>
       </c>
-      <c r="C363">
-        <v>4</v>
-      </c>
-      <c r="D363">
-        <v>2</v>
-      </c>
-      <c r="E363">
-        <v>3</v>
-      </c>
-      <c r="F363">
-        <v>0</v>
-      </c>
-      <c r="G363">
-        <v>1</v>
-      </c>
-      <c r="H363">
-        <v>1</v>
-      </c>
-      <c r="I363">
-        <v>0</v>
-      </c>
-      <c r="J363">
-        <v>0</v>
-      </c>
-      <c r="K363">
-        <v>3</v>
-      </c>
-      <c r="L363">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="365" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="368" spans="1:12" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="369" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="370" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="371" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="372" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="373" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="374" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="375" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="376" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="377" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="378" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="379" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="380" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="381" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="382" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="383" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="384" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="385" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="386" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="387" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="388" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="389" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="390" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="391" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="392" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="393" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="394" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="395" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="396" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="397" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="398" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="399" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="400" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="401" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="402" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="403" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="404" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="405" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="406" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="407" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="408" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="409" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="410" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="411" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="412" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="413" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="414" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="415" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="416" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="417" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="418" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="419" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="420" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="421" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="422" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="423" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="424" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="425" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="426" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="427" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="428" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="429" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="430" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="431" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="432" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="433" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="434" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="435" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="436" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="437" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="438" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="439" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="440" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="441" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="442" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="443" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="444" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="445" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="446" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="447" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="448" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="449" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="450" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="451" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="452" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="453" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="454" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="455" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="456" hidden="1" x14ac:dyDescent="0.35"/>
+      <c r="C386">
+        <v>3</v>
+      </c>
+      <c r="D386">
+        <v>2</v>
+      </c>
+      <c r="E386">
+        <v>4</v>
+      </c>
+      <c r="F386">
+        <v>0</v>
+      </c>
+      <c r="G386">
+        <v>1</v>
+      </c>
+      <c r="H386">
+        <v>0</v>
+      </c>
+      <c r="I386">
+        <v>1</v>
+      </c>
+      <c r="J386">
+        <v>0</v>
+      </c>
+      <c r="K386">
+        <v>9</v>
+      </c>
+      <c r="L386">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="David"/>
-        <filter val="Davidson"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1799" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1A24EF-D718-4355-9A32-5745A238FECA}"/>
+  <xr:revisionPtr revIDLastSave="1913" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DD74499-5493-4DDE-A2C4-690B7E8D3684}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="123">
   <si>
     <t>Boneco</t>
   </si>
@@ -734,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O386"/>
+  <dimension ref="A1:O408"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -14273,6 +14273,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>59</v>
+      </c>
+      <c r="C387">
+        <v>6</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387">
+        <v>2</v>
+      </c>
+      <c r="F387">
+        <v>2</v>
+      </c>
+      <c r="G387">
+        <v>1</v>
+      </c>
+      <c r="H387">
+        <v>1</v>
+      </c>
+      <c r="I387">
+        <v>0</v>
+      </c>
+      <c r="J387">
+        <v>0</v>
+      </c>
+      <c r="K387">
+        <v>0</v>
+      </c>
+      <c r="L387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>29</v>
+      </c>
+      <c r="C388">
+        <v>6</v>
+      </c>
+      <c r="D388">
+        <v>2</v>
+      </c>
+      <c r="E388">
+        <v>2</v>
+      </c>
+      <c r="F388">
+        <v>0</v>
+      </c>
+      <c r="G388">
+        <v>1</v>
+      </c>
+      <c r="H388">
+        <v>1</v>
+      </c>
+      <c r="I388">
+        <v>0</v>
+      </c>
+      <c r="J388">
+        <v>0</v>
+      </c>
+      <c r="K388">
+        <v>0</v>
+      </c>
+      <c r="L388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>6</v>
+      </c>
+      <c r="C389">
+        <v>6</v>
+      </c>
+      <c r="D389">
+        <v>2</v>
+      </c>
+      <c r="E389">
+        <v>2</v>
+      </c>
+      <c r="F389">
+        <v>1</v>
+      </c>
+      <c r="G389">
+        <v>1</v>
+      </c>
+      <c r="H389">
+        <v>1</v>
+      </c>
+      <c r="I389">
+        <v>0</v>
+      </c>
+      <c r="J389">
+        <v>0</v>
+      </c>
+      <c r="K389">
+        <v>0</v>
+      </c>
+      <c r="L389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>2</v>
+      </c>
+      <c r="C390">
+        <v>6</v>
+      </c>
+      <c r="D390">
+        <v>2</v>
+      </c>
+      <c r="E390">
+        <v>2</v>
+      </c>
+      <c r="F390">
+        <v>4</v>
+      </c>
+      <c r="G390">
+        <v>1</v>
+      </c>
+      <c r="H390">
+        <v>1</v>
+      </c>
+      <c r="I390">
+        <v>0</v>
+      </c>
+      <c r="J390">
+        <v>0</v>
+      </c>
+      <c r="K390">
+        <v>0</v>
+      </c>
+      <c r="L390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>3</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391">
+        <v>2</v>
+      </c>
+      <c r="E391">
+        <v>2</v>
+      </c>
+      <c r="F391">
+        <v>2</v>
+      </c>
+      <c r="G391">
+        <v>1</v>
+      </c>
+      <c r="H391">
+        <v>1</v>
+      </c>
+      <c r="I391">
+        <v>0</v>
+      </c>
+      <c r="J391">
+        <v>0</v>
+      </c>
+      <c r="K391">
+        <v>0</v>
+      </c>
+      <c r="L391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>39</v>
+      </c>
+      <c r="C392">
+        <v>2</v>
+      </c>
+      <c r="D392">
+        <v>0</v>
+      </c>
+      <c r="E392">
+        <v>5</v>
+      </c>
+      <c r="F392">
+        <v>1</v>
+      </c>
+      <c r="G392">
+        <v>1</v>
+      </c>
+      <c r="H392">
+        <v>0</v>
+      </c>
+      <c r="I392">
+        <v>1</v>
+      </c>
+      <c r="J392">
+        <v>0</v>
+      </c>
+      <c r="K392">
+        <v>0</v>
+      </c>
+      <c r="L392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>121</v>
+      </c>
+      <c r="C393">
+        <v>2</v>
+      </c>
+      <c r="D393">
+        <v>0</v>
+      </c>
+      <c r="E393">
+        <v>5</v>
+      </c>
+      <c r="F393">
+        <v>1</v>
+      </c>
+      <c r="G393">
+        <v>1</v>
+      </c>
+      <c r="H393">
+        <v>0</v>
+      </c>
+      <c r="I393">
+        <v>1</v>
+      </c>
+      <c r="J393">
+        <v>0</v>
+      </c>
+      <c r="K393">
+        <v>0</v>
+      </c>
+      <c r="L393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>5</v>
+      </c>
+      <c r="C394">
+        <v>2</v>
+      </c>
+      <c r="D394">
+        <v>0</v>
+      </c>
+      <c r="E394">
+        <v>5</v>
+      </c>
+      <c r="F394">
+        <v>0</v>
+      </c>
+      <c r="G394">
+        <v>1</v>
+      </c>
+      <c r="H394">
+        <v>0</v>
+      </c>
+      <c r="I394">
+        <v>1</v>
+      </c>
+      <c r="J394">
+        <v>0</v>
+      </c>
+      <c r="K394">
+        <v>0</v>
+      </c>
+      <c r="L394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>1</v>
+      </c>
+      <c r="C395">
+        <v>2</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+      <c r="E395">
+        <v>5</v>
+      </c>
+      <c r="F395">
+        <v>4</v>
+      </c>
+      <c r="G395">
+        <v>1</v>
+      </c>
+      <c r="H395">
+        <v>0</v>
+      </c>
+      <c r="I395">
+        <v>1</v>
+      </c>
+      <c r="J395">
+        <v>0</v>
+      </c>
+      <c r="K395">
+        <v>0</v>
+      </c>
+      <c r="L395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>117</v>
+      </c>
+      <c r="C396">
+        <v>2</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+      <c r="E396">
+        <v>5</v>
+      </c>
+      <c r="F396">
+        <v>0</v>
+      </c>
+      <c r="G396">
+        <v>1</v>
+      </c>
+      <c r="H396">
+        <v>0</v>
+      </c>
+      <c r="I396">
+        <v>1</v>
+      </c>
+      <c r="J396">
+        <v>0</v>
+      </c>
+      <c r="K396">
+        <v>0</v>
+      </c>
+      <c r="L396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>27</v>
+      </c>
+      <c r="C397">
+        <v>4</v>
+      </c>
+      <c r="D397">
+        <v>2</v>
+      </c>
+      <c r="E397">
+        <v>2</v>
+      </c>
+      <c r="F397">
+        <v>2</v>
+      </c>
+      <c r="G397">
+        <v>1</v>
+      </c>
+      <c r="H397">
+        <v>0</v>
+      </c>
+      <c r="I397">
+        <v>0</v>
+      </c>
+      <c r="J397">
+        <v>0</v>
+      </c>
+      <c r="K397">
+        <v>0</v>
+      </c>
+      <c r="L397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>28</v>
+      </c>
+      <c r="C398">
+        <v>4</v>
+      </c>
+      <c r="D398">
+        <v>2</v>
+      </c>
+      <c r="E398">
+        <v>2</v>
+      </c>
+      <c r="F398">
+        <v>4</v>
+      </c>
+      <c r="G398">
+        <v>1</v>
+      </c>
+      <c r="H398">
+        <v>0</v>
+      </c>
+      <c r="I398">
+        <v>0</v>
+      </c>
+      <c r="J398">
+        <v>0</v>
+      </c>
+      <c r="K398">
+        <v>0</v>
+      </c>
+      <c r="L398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>32</v>
+      </c>
+      <c r="C399">
+        <v>4</v>
+      </c>
+      <c r="D399">
+        <v>2</v>
+      </c>
+      <c r="E399">
+        <v>2</v>
+      </c>
+      <c r="F399">
+        <v>1</v>
+      </c>
+      <c r="G399">
+        <v>1</v>
+      </c>
+      <c r="H399">
+        <v>0</v>
+      </c>
+      <c r="I399">
+        <v>0</v>
+      </c>
+      <c r="J399">
+        <v>0</v>
+      </c>
+      <c r="K399">
+        <v>0</v>
+      </c>
+      <c r="L399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>20</v>
+      </c>
+      <c r="C400">
+        <v>4</v>
+      </c>
+      <c r="D400">
+        <v>2</v>
+      </c>
+      <c r="E400">
+        <v>2</v>
+      </c>
+      <c r="F400">
+        <v>0</v>
+      </c>
+      <c r="G400">
+        <v>1</v>
+      </c>
+      <c r="H400">
+        <v>0</v>
+      </c>
+      <c r="I400">
+        <v>0</v>
+      </c>
+      <c r="J400">
+        <v>0</v>
+      </c>
+      <c r="K400">
+        <v>0</v>
+      </c>
+      <c r="L400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>34</v>
+      </c>
+      <c r="C401">
+        <v>4</v>
+      </c>
+      <c r="D401">
+        <v>2</v>
+      </c>
+      <c r="E401">
+        <v>2</v>
+      </c>
+      <c r="F401">
+        <v>4</v>
+      </c>
+      <c r="G401">
+        <v>1</v>
+      </c>
+      <c r="H401">
+        <v>0</v>
+      </c>
+      <c r="I401">
+        <v>0</v>
+      </c>
+      <c r="J401">
+        <v>0</v>
+      </c>
+      <c r="K401">
+        <v>0</v>
+      </c>
+      <c r="L401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>30</v>
+      </c>
+      <c r="C402">
+        <v>2</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+      <c r="E402">
+        <v>5</v>
+      </c>
+      <c r="F402">
+        <v>1</v>
+      </c>
+      <c r="G402">
+        <v>1</v>
+      </c>
+      <c r="H402">
+        <v>0</v>
+      </c>
+      <c r="I402">
+        <v>0</v>
+      </c>
+      <c r="J402">
+        <v>0</v>
+      </c>
+      <c r="K402">
+        <v>0</v>
+      </c>
+      <c r="L402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>26</v>
+      </c>
+      <c r="C403">
+        <v>2</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+      <c r="E403">
+        <v>5</v>
+      </c>
+      <c r="F403">
+        <v>0</v>
+      </c>
+      <c r="G403">
+        <v>1</v>
+      </c>
+      <c r="H403">
+        <v>0</v>
+      </c>
+      <c r="I403">
+        <v>0</v>
+      </c>
+      <c r="J403">
+        <v>0</v>
+      </c>
+      <c r="K403">
+        <v>0</v>
+      </c>
+      <c r="L403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>119</v>
+      </c>
+      <c r="C404">
+        <v>2</v>
+      </c>
+      <c r="D404">
+        <v>0</v>
+      </c>
+      <c r="E404">
+        <v>5</v>
+      </c>
+      <c r="F404">
+        <v>1</v>
+      </c>
+      <c r="G404">
+        <v>1</v>
+      </c>
+      <c r="H404">
+        <v>0</v>
+      </c>
+      <c r="I404">
+        <v>0</v>
+      </c>
+      <c r="J404">
+        <v>0</v>
+      </c>
+      <c r="K404">
+        <v>0</v>
+      </c>
+      <c r="L404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>57</v>
+      </c>
+      <c r="C405">
+        <v>2</v>
+      </c>
+      <c r="D405">
+        <v>0</v>
+      </c>
+      <c r="E405">
+        <v>5</v>
+      </c>
+      <c r="F405">
+        <v>0</v>
+      </c>
+      <c r="G405">
+        <v>1</v>
+      </c>
+      <c r="H405">
+        <v>0</v>
+      </c>
+      <c r="I405">
+        <v>0</v>
+      </c>
+      <c r="J405">
+        <v>0</v>
+      </c>
+      <c r="K405">
+        <v>0</v>
+      </c>
+      <c r="L405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>4</v>
+      </c>
+      <c r="C406">
+        <v>2</v>
+      </c>
+      <c r="D406">
+        <v>0</v>
+      </c>
+      <c r="E406">
+        <v>5</v>
+      </c>
+      <c r="F406">
+        <v>4</v>
+      </c>
+      <c r="G406">
+        <v>1</v>
+      </c>
+      <c r="H406">
+        <v>0</v>
+      </c>
+      <c r="I406">
+        <v>0</v>
+      </c>
+      <c r="J406">
+        <v>0</v>
+      </c>
+      <c r="K406">
+        <v>0</v>
+      </c>
+      <c r="L406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>45</v>
+      </c>
+      <c r="C407">
+        <v>8</v>
+      </c>
+      <c r="D407">
+        <v>1</v>
+      </c>
+      <c r="E407">
+        <v>6</v>
+      </c>
+      <c r="F407">
+        <v>0</v>
+      </c>
+      <c r="G407">
+        <v>1</v>
+      </c>
+      <c r="H407">
+        <v>1</v>
+      </c>
+      <c r="I407">
+        <v>0</v>
+      </c>
+      <c r="J407">
+        <v>0</v>
+      </c>
+      <c r="K407">
+        <v>13</v>
+      </c>
+      <c r="L407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>118</v>
+      </c>
+      <c r="C408">
+        <v>6</v>
+      </c>
+      <c r="D408">
+        <v>1</v>
+      </c>
+      <c r="E408">
+        <v>8</v>
+      </c>
+      <c r="F408">
+        <v>0</v>
+      </c>
+      <c r="G408">
+        <v>1</v>
+      </c>
+      <c r="H408">
+        <v>0</v>
+      </c>
+      <c r="I408">
+        <v>1</v>
+      </c>
+      <c r="J408">
+        <v>0</v>
+      </c>
+      <c r="K408">
+        <v>17</v>
+      </c>
+      <c r="L408">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1913" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DD74499-5493-4DDE-A2C4-690B7E8D3684}"/>
+  <xr:revisionPtr revIDLastSave="2032" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22638623-1062-49EA-B99C-D3900764FCF3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="123">
   <si>
     <t>Boneco</t>
   </si>
@@ -734,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O408"/>
+  <dimension ref="A1:O431"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -15043,6 +15043,811 @@
         <v>0</v>
       </c>
     </row>
+    <row r="409" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>24</v>
+      </c>
+      <c r="C409">
+        <v>4</v>
+      </c>
+      <c r="D409">
+        <v>1</v>
+      </c>
+      <c r="E409">
+        <v>4</v>
+      </c>
+      <c r="F409">
+        <v>1</v>
+      </c>
+      <c r="G409">
+        <v>1</v>
+      </c>
+      <c r="H409">
+        <v>0</v>
+      </c>
+      <c r="I409">
+        <v>0</v>
+      </c>
+      <c r="J409">
+        <v>0</v>
+      </c>
+      <c r="K409">
+        <v>0</v>
+      </c>
+      <c r="L409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>29</v>
+      </c>
+      <c r="C410">
+        <v>4</v>
+      </c>
+      <c r="D410">
+        <v>1</v>
+      </c>
+      <c r="E410">
+        <v>4</v>
+      </c>
+      <c r="F410">
+        <v>1</v>
+      </c>
+      <c r="G410">
+        <v>1</v>
+      </c>
+      <c r="H410">
+        <v>0</v>
+      </c>
+      <c r="I410">
+        <v>0</v>
+      </c>
+      <c r="J410">
+        <v>0</v>
+      </c>
+      <c r="K410">
+        <v>0</v>
+      </c>
+      <c r="L410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>20</v>
+      </c>
+      <c r="C411">
+        <v>4</v>
+      </c>
+      <c r="D411">
+        <v>1</v>
+      </c>
+      <c r="E411">
+        <v>4</v>
+      </c>
+      <c r="F411">
+        <v>1</v>
+      </c>
+      <c r="G411">
+        <v>1</v>
+      </c>
+      <c r="H411">
+        <v>0</v>
+      </c>
+      <c r="I411">
+        <v>0</v>
+      </c>
+      <c r="J411">
+        <v>0</v>
+      </c>
+      <c r="K411">
+        <v>0</v>
+      </c>
+      <c r="L411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>23</v>
+      </c>
+      <c r="C412">
+        <v>4</v>
+      </c>
+      <c r="D412">
+        <v>1</v>
+      </c>
+      <c r="E412">
+        <v>4</v>
+      </c>
+      <c r="F412">
+        <v>2</v>
+      </c>
+      <c r="G412">
+        <v>1</v>
+      </c>
+      <c r="H412">
+        <v>0</v>
+      </c>
+      <c r="I412">
+        <v>0</v>
+      </c>
+      <c r="J412">
+        <v>0</v>
+      </c>
+      <c r="K412">
+        <v>0</v>
+      </c>
+      <c r="L412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>36</v>
+      </c>
+      <c r="C413">
+        <v>4</v>
+      </c>
+      <c r="D413">
+        <v>1</v>
+      </c>
+      <c r="E413">
+        <v>4</v>
+      </c>
+      <c r="F413">
+        <v>1</v>
+      </c>
+      <c r="G413">
+        <v>1</v>
+      </c>
+      <c r="H413">
+        <v>0</v>
+      </c>
+      <c r="I413">
+        <v>0</v>
+      </c>
+      <c r="J413">
+        <v>0</v>
+      </c>
+      <c r="K413">
+        <v>0</v>
+      </c>
+      <c r="L413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>27</v>
+      </c>
+      <c r="C414">
+        <v>5</v>
+      </c>
+      <c r="D414">
+        <v>1</v>
+      </c>
+      <c r="E414">
+        <v>3</v>
+      </c>
+      <c r="F414">
+        <v>3</v>
+      </c>
+      <c r="G414">
+        <v>1</v>
+      </c>
+      <c r="H414">
+        <v>1</v>
+      </c>
+      <c r="I414">
+        <v>0</v>
+      </c>
+      <c r="J414">
+        <v>0</v>
+      </c>
+      <c r="K414">
+        <v>0</v>
+      </c>
+      <c r="L414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>48</v>
+      </c>
+      <c r="C415">
+        <v>5</v>
+      </c>
+      <c r="D415">
+        <v>1</v>
+      </c>
+      <c r="E415">
+        <v>3</v>
+      </c>
+      <c r="F415">
+        <v>1</v>
+      </c>
+      <c r="G415">
+        <v>1</v>
+      </c>
+      <c r="H415">
+        <v>1</v>
+      </c>
+      <c r="I415">
+        <v>0</v>
+      </c>
+      <c r="J415">
+        <v>0</v>
+      </c>
+      <c r="K415">
+        <v>0</v>
+      </c>
+      <c r="L415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>99</v>
+      </c>
+      <c r="C416">
+        <v>5</v>
+      </c>
+      <c r="D416">
+        <v>1</v>
+      </c>
+      <c r="E416">
+        <v>3</v>
+      </c>
+      <c r="F416">
+        <v>2</v>
+      </c>
+      <c r="G416">
+        <v>1</v>
+      </c>
+      <c r="H416">
+        <v>1</v>
+      </c>
+      <c r="I416">
+        <v>0</v>
+      </c>
+      <c r="J416">
+        <v>0</v>
+      </c>
+      <c r="K416">
+        <v>0</v>
+      </c>
+      <c r="L416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>21</v>
+      </c>
+      <c r="C417">
+        <v>5</v>
+      </c>
+      <c r="D417">
+        <v>1</v>
+      </c>
+      <c r="E417">
+        <v>3</v>
+      </c>
+      <c r="F417">
+        <v>3</v>
+      </c>
+      <c r="G417">
+        <v>1</v>
+      </c>
+      <c r="H417">
+        <v>1</v>
+      </c>
+      <c r="I417">
+        <v>0</v>
+      </c>
+      <c r="J417">
+        <v>0</v>
+      </c>
+      <c r="K417">
+        <v>0</v>
+      </c>
+      <c r="L417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>30</v>
+      </c>
+      <c r="C418">
+        <v>5</v>
+      </c>
+      <c r="D418">
+        <v>1</v>
+      </c>
+      <c r="E418">
+        <v>3</v>
+      </c>
+      <c r="F418">
+        <v>1</v>
+      </c>
+      <c r="G418">
+        <v>1</v>
+      </c>
+      <c r="H418">
+        <v>1</v>
+      </c>
+      <c r="I418">
+        <v>0</v>
+      </c>
+      <c r="J418">
+        <v>0</v>
+      </c>
+      <c r="K418">
+        <v>0</v>
+      </c>
+      <c r="L418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>34</v>
+      </c>
+      <c r="C419">
+        <v>3</v>
+      </c>
+      <c r="D419">
+        <v>0</v>
+      </c>
+      <c r="E419">
+        <v>4</v>
+      </c>
+      <c r="F419">
+        <v>1</v>
+      </c>
+      <c r="G419">
+        <v>1</v>
+      </c>
+      <c r="H419">
+        <v>0</v>
+      </c>
+      <c r="I419">
+        <v>1</v>
+      </c>
+      <c r="J419">
+        <v>0</v>
+      </c>
+      <c r="K419">
+        <v>0</v>
+      </c>
+      <c r="L419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>3</v>
+      </c>
+      <c r="C420">
+        <v>3</v>
+      </c>
+      <c r="D420">
+        <v>0</v>
+      </c>
+      <c r="E420">
+        <v>4</v>
+      </c>
+      <c r="F420">
+        <v>1</v>
+      </c>
+      <c r="G420">
+        <v>1</v>
+      </c>
+      <c r="H420">
+        <v>0</v>
+      </c>
+      <c r="I420">
+        <v>1</v>
+      </c>
+      <c r="J420">
+        <v>0</v>
+      </c>
+      <c r="K420">
+        <v>0</v>
+      </c>
+      <c r="L420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>80</v>
+      </c>
+      <c r="C421">
+        <v>3</v>
+      </c>
+      <c r="D421">
+        <v>0</v>
+      </c>
+      <c r="E421">
+        <v>4</v>
+      </c>
+      <c r="F421">
+        <v>1</v>
+      </c>
+      <c r="G421">
+        <v>1</v>
+      </c>
+      <c r="H421">
+        <v>0</v>
+      </c>
+      <c r="I421">
+        <v>1</v>
+      </c>
+      <c r="J421">
+        <v>0</v>
+      </c>
+      <c r="K421">
+        <v>0</v>
+      </c>
+      <c r="L421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>50</v>
+      </c>
+      <c r="C422">
+        <v>3</v>
+      </c>
+      <c r="D422">
+        <v>0</v>
+      </c>
+      <c r="E422">
+        <v>4</v>
+      </c>
+      <c r="F422">
+        <v>0</v>
+      </c>
+      <c r="G422">
+        <v>1</v>
+      </c>
+      <c r="H422">
+        <v>0</v>
+      </c>
+      <c r="I422">
+        <v>1</v>
+      </c>
+      <c r="J422">
+        <v>0</v>
+      </c>
+      <c r="K422">
+        <v>0</v>
+      </c>
+      <c r="L422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>59</v>
+      </c>
+      <c r="C423">
+        <v>3</v>
+      </c>
+      <c r="D423">
+        <v>0</v>
+      </c>
+      <c r="E423">
+        <v>4</v>
+      </c>
+      <c r="F423">
+        <v>2</v>
+      </c>
+      <c r="G423">
+        <v>1</v>
+      </c>
+      <c r="H423">
+        <v>0</v>
+      </c>
+      <c r="I423">
+        <v>1</v>
+      </c>
+      <c r="J423">
+        <v>0</v>
+      </c>
+      <c r="K423">
+        <v>0</v>
+      </c>
+      <c r="L423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>28</v>
+      </c>
+      <c r="C424">
+        <v>4</v>
+      </c>
+      <c r="D424">
+        <v>0</v>
+      </c>
+      <c r="E424">
+        <v>4</v>
+      </c>
+      <c r="F424">
+        <v>0</v>
+      </c>
+      <c r="G424">
+        <v>1</v>
+      </c>
+      <c r="H424">
+        <v>0</v>
+      </c>
+      <c r="I424">
+        <v>0</v>
+      </c>
+      <c r="J424">
+        <v>0</v>
+      </c>
+      <c r="K424">
+        <v>0</v>
+      </c>
+      <c r="L424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>1</v>
+      </c>
+      <c r="C425">
+        <v>4</v>
+      </c>
+      <c r="D425">
+        <v>0</v>
+      </c>
+      <c r="E425">
+        <v>4</v>
+      </c>
+      <c r="F425">
+        <v>4</v>
+      </c>
+      <c r="G425">
+        <v>1</v>
+      </c>
+      <c r="H425">
+        <v>0</v>
+      </c>
+      <c r="I425">
+        <v>0</v>
+      </c>
+      <c r="J425">
+        <v>0</v>
+      </c>
+      <c r="K425">
+        <v>0</v>
+      </c>
+      <c r="L425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>4</v>
+      </c>
+      <c r="C426">
+        <v>4</v>
+      </c>
+      <c r="D426">
+        <v>0</v>
+      </c>
+      <c r="E426">
+        <v>4</v>
+      </c>
+      <c r="F426">
+        <v>0</v>
+      </c>
+      <c r="G426">
+        <v>1</v>
+      </c>
+      <c r="H426">
+        <v>0</v>
+      </c>
+      <c r="I426">
+        <v>0</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
+      </c>
+      <c r="K426">
+        <v>0</v>
+      </c>
+      <c r="L426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>6</v>
+      </c>
+      <c r="C427">
+        <v>4</v>
+      </c>
+      <c r="D427">
+        <v>0</v>
+      </c>
+      <c r="E427">
+        <v>4</v>
+      </c>
+      <c r="F427">
+        <v>0</v>
+      </c>
+      <c r="G427">
+        <v>1</v>
+      </c>
+      <c r="H427">
+        <v>0</v>
+      </c>
+      <c r="I427">
+        <v>0</v>
+      </c>
+      <c r="J427">
+        <v>0</v>
+      </c>
+      <c r="K427">
+        <v>0</v>
+      </c>
+      <c r="L427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>2</v>
+      </c>
+      <c r="C428">
+        <v>4</v>
+      </c>
+      <c r="D428">
+        <v>0</v>
+      </c>
+      <c r="E428">
+        <v>4</v>
+      </c>
+      <c r="F428">
+        <v>1</v>
+      </c>
+      <c r="G428">
+        <v>1</v>
+      </c>
+      <c r="H428">
+        <v>0</v>
+      </c>
+      <c r="I428">
+        <v>0</v>
+      </c>
+      <c r="J428">
+        <v>0</v>
+      </c>
+      <c r="K428">
+        <v>0</v>
+      </c>
+      <c r="L428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>17</v>
+      </c>
+      <c r="C429">
+        <v>5</v>
+      </c>
+      <c r="D429">
+        <v>0</v>
+      </c>
+      <c r="E429">
+        <v>5</v>
+      </c>
+      <c r="F429">
+        <v>2</v>
+      </c>
+      <c r="G429">
+        <v>1</v>
+      </c>
+      <c r="H429">
+        <v>0</v>
+      </c>
+      <c r="I429">
+        <v>0</v>
+      </c>
+      <c r="J429">
+        <v>0</v>
+      </c>
+      <c r="K429">
+        <v>9</v>
+      </c>
+      <c r="L429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>45</v>
+      </c>
+      <c r="C430">
+        <v>6</v>
+      </c>
+      <c r="D430">
+        <v>1</v>
+      </c>
+      <c r="E430">
+        <v>3</v>
+      </c>
+      <c r="F430">
+        <v>0</v>
+      </c>
+      <c r="G430">
+        <v>1</v>
+      </c>
+      <c r="H430">
+        <v>1</v>
+      </c>
+      <c r="I430">
+        <v>0</v>
+      </c>
+      <c r="J430">
+        <v>0</v>
+      </c>
+      <c r="K430">
+        <v>5</v>
+      </c>
+      <c r="L430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>96</v>
+      </c>
+      <c r="C431">
+        <v>3</v>
+      </c>
+      <c r="D431">
+        <v>1</v>
+      </c>
+      <c r="E431">
+        <v>4</v>
+      </c>
+      <c r="F431">
+        <v>0</v>
+      </c>
+      <c r="G431">
+        <v>1</v>
+      </c>
+      <c r="H431">
+        <v>0</v>
+      </c>
+      <c r="I431">
+        <v>1</v>
+      </c>
+      <c r="J431">
+        <v>0</v>
+      </c>
+      <c r="K431">
+        <v>13</v>
+      </c>
+      <c r="L431">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2032" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22638623-1062-49EA-B99C-D3900764FCF3}"/>
+  <xr:revisionPtr revIDLastSave="2150" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{980B6B72-390A-48DA-B29A-CBD1565A2F31}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="124">
   <si>
     <t>Boneco</t>
   </si>
@@ -409,6 +409,9 @@
   <si>
     <t>Luiz</t>
   </si>
+  <si>
+    <t>Samuel</t>
+  </si>
 </sst>
 </file>
 
@@ -734,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O431"/>
+  <dimension ref="A1:O453"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -15848,6 +15851,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="432" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>30</v>
+      </c>
+      <c r="C432">
+        <v>1</v>
+      </c>
+      <c r="D432">
+        <v>3</v>
+      </c>
+      <c r="E432">
+        <v>2</v>
+      </c>
+      <c r="F432">
+        <v>1</v>
+      </c>
+      <c r="G432">
+        <v>1</v>
+      </c>
+      <c r="H432">
+        <v>0</v>
+      </c>
+      <c r="I432">
+        <v>0</v>
+      </c>
+      <c r="J432">
+        <v>0</v>
+      </c>
+      <c r="K432">
+        <v>0</v>
+      </c>
+      <c r="L432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>2</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+      <c r="D433">
+        <v>3</v>
+      </c>
+      <c r="E433">
+        <v>2</v>
+      </c>
+      <c r="F433">
+        <v>3</v>
+      </c>
+      <c r="G433">
+        <v>1</v>
+      </c>
+      <c r="H433">
+        <v>0</v>
+      </c>
+      <c r="I433">
+        <v>0</v>
+      </c>
+      <c r="J433">
+        <v>0</v>
+      </c>
+      <c r="K433">
+        <v>0</v>
+      </c>
+      <c r="L433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>59</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+      <c r="D434">
+        <v>3</v>
+      </c>
+      <c r="E434">
+        <v>2</v>
+      </c>
+      <c r="F434">
+        <v>0</v>
+      </c>
+      <c r="G434">
+        <v>1</v>
+      </c>
+      <c r="H434">
+        <v>0</v>
+      </c>
+      <c r="I434">
+        <v>0</v>
+      </c>
+      <c r="J434">
+        <v>0</v>
+      </c>
+      <c r="K434">
+        <v>0</v>
+      </c>
+      <c r="L434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>29</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+      <c r="D435">
+        <v>3</v>
+      </c>
+      <c r="E435">
+        <v>2</v>
+      </c>
+      <c r="F435">
+        <v>0</v>
+      </c>
+      <c r="G435">
+        <v>1</v>
+      </c>
+      <c r="H435">
+        <v>0</v>
+      </c>
+      <c r="I435">
+        <v>0</v>
+      </c>
+      <c r="J435">
+        <v>0</v>
+      </c>
+      <c r="K435">
+        <v>0</v>
+      </c>
+      <c r="L435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>21</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+      <c r="D436">
+        <v>3</v>
+      </c>
+      <c r="E436">
+        <v>2</v>
+      </c>
+      <c r="F436">
+        <v>0</v>
+      </c>
+      <c r="G436">
+        <v>1</v>
+      </c>
+      <c r="H436">
+        <v>0</v>
+      </c>
+      <c r="I436">
+        <v>0</v>
+      </c>
+      <c r="J436">
+        <v>0</v>
+      </c>
+      <c r="K436">
+        <v>0</v>
+      </c>
+      <c r="L436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>1</v>
+      </c>
+      <c r="C437">
+        <v>5</v>
+      </c>
+      <c r="D437">
+        <v>2</v>
+      </c>
+      <c r="E437">
+        <v>2</v>
+      </c>
+      <c r="F437">
+        <v>1</v>
+      </c>
+      <c r="G437">
+        <v>1</v>
+      </c>
+      <c r="H437">
+        <v>1</v>
+      </c>
+      <c r="I437">
+        <v>0</v>
+      </c>
+      <c r="J437">
+        <v>0</v>
+      </c>
+      <c r="K437">
+        <v>0</v>
+      </c>
+      <c r="L437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>32</v>
+      </c>
+      <c r="C438">
+        <v>5</v>
+      </c>
+      <c r="D438">
+        <v>2</v>
+      </c>
+      <c r="E438">
+        <v>2</v>
+      </c>
+      <c r="F438">
+        <v>0</v>
+      </c>
+      <c r="G438">
+        <v>1</v>
+      </c>
+      <c r="H438">
+        <v>1</v>
+      </c>
+      <c r="I438">
+        <v>0</v>
+      </c>
+      <c r="J438">
+        <v>0</v>
+      </c>
+      <c r="K438">
+        <v>0</v>
+      </c>
+      <c r="L438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>36</v>
+      </c>
+      <c r="C439">
+        <v>5</v>
+      </c>
+      <c r="D439">
+        <v>2</v>
+      </c>
+      <c r="E439">
+        <v>2</v>
+      </c>
+      <c r="F439">
+        <v>4</v>
+      </c>
+      <c r="G439">
+        <v>1</v>
+      </c>
+      <c r="H439">
+        <v>1</v>
+      </c>
+      <c r="I439">
+        <v>0</v>
+      </c>
+      <c r="J439">
+        <v>0</v>
+      </c>
+      <c r="K439">
+        <v>0</v>
+      </c>
+      <c r="L439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>34</v>
+      </c>
+      <c r="C440">
+        <v>5</v>
+      </c>
+      <c r="D440">
+        <v>2</v>
+      </c>
+      <c r="E440">
+        <v>2</v>
+      </c>
+      <c r="F440">
+        <v>0</v>
+      </c>
+      <c r="G440">
+        <v>1</v>
+      </c>
+      <c r="H440">
+        <v>1</v>
+      </c>
+      <c r="I440">
+        <v>0</v>
+      </c>
+      <c r="J440">
+        <v>0</v>
+      </c>
+      <c r="K440">
+        <v>0</v>
+      </c>
+      <c r="L440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>28</v>
+      </c>
+      <c r="C441">
+        <v>5</v>
+      </c>
+      <c r="D441">
+        <v>2</v>
+      </c>
+      <c r="E441">
+        <v>2</v>
+      </c>
+      <c r="F441">
+        <v>2</v>
+      </c>
+      <c r="G441">
+        <v>1</v>
+      </c>
+      <c r="H441">
+        <v>1</v>
+      </c>
+      <c r="I441">
+        <v>0</v>
+      </c>
+      <c r="J441">
+        <v>0</v>
+      </c>
+      <c r="K441">
+        <v>0</v>
+      </c>
+      <c r="L441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>24</v>
+      </c>
+      <c r="C442">
+        <v>2</v>
+      </c>
+      <c r="D442">
+        <v>3</v>
+      </c>
+      <c r="E442">
+        <v>2</v>
+      </c>
+      <c r="F442">
+        <v>2</v>
+      </c>
+      <c r="G442">
+        <v>1</v>
+      </c>
+      <c r="H442">
+        <v>0</v>
+      </c>
+      <c r="I442">
+        <v>0</v>
+      </c>
+      <c r="J442">
+        <v>0</v>
+      </c>
+      <c r="K442">
+        <v>0</v>
+      </c>
+      <c r="L442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>20</v>
+      </c>
+      <c r="C443">
+        <v>2</v>
+      </c>
+      <c r="D443">
+        <v>3</v>
+      </c>
+      <c r="E443">
+        <v>2</v>
+      </c>
+      <c r="F443">
+        <v>0</v>
+      </c>
+      <c r="G443">
+        <v>1</v>
+      </c>
+      <c r="H443">
+        <v>0</v>
+      </c>
+      <c r="I443">
+        <v>0</v>
+      </c>
+      <c r="J443">
+        <v>0</v>
+      </c>
+      <c r="K443">
+        <v>0</v>
+      </c>
+      <c r="L443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>4</v>
+      </c>
+      <c r="C444">
+        <v>2</v>
+      </c>
+      <c r="D444">
+        <v>3</v>
+      </c>
+      <c r="E444">
+        <v>2</v>
+      </c>
+      <c r="F444">
+        <v>1</v>
+      </c>
+      <c r="G444">
+        <v>1</v>
+      </c>
+      <c r="H444">
+        <v>0</v>
+      </c>
+      <c r="I444">
+        <v>0</v>
+      </c>
+      <c r="J444">
+        <v>0</v>
+      </c>
+      <c r="K444">
+        <v>0</v>
+      </c>
+      <c r="L444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>7</v>
+      </c>
+      <c r="C445">
+        <v>2</v>
+      </c>
+      <c r="D445">
+        <v>3</v>
+      </c>
+      <c r="E445">
+        <v>2</v>
+      </c>
+      <c r="F445">
+        <v>0</v>
+      </c>
+      <c r="G445">
+        <v>1</v>
+      </c>
+      <c r="H445">
+        <v>0</v>
+      </c>
+      <c r="I445">
+        <v>0</v>
+      </c>
+      <c r="J445">
+        <v>0</v>
+      </c>
+      <c r="K445">
+        <v>0</v>
+      </c>
+      <c r="L445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>27</v>
+      </c>
+      <c r="C446">
+        <v>2</v>
+      </c>
+      <c r="D446">
+        <v>3</v>
+      </c>
+      <c r="E446">
+        <v>2</v>
+      </c>
+      <c r="F446">
+        <v>1</v>
+      </c>
+      <c r="G446">
+        <v>1</v>
+      </c>
+      <c r="H446">
+        <v>0</v>
+      </c>
+      <c r="I446">
+        <v>0</v>
+      </c>
+      <c r="J446">
+        <v>0</v>
+      </c>
+      <c r="K446">
+        <v>0</v>
+      </c>
+      <c r="L446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>6</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+      <c r="D447">
+        <v>2</v>
+      </c>
+      <c r="E447">
+        <v>3</v>
+      </c>
+      <c r="F447">
+        <v>1</v>
+      </c>
+      <c r="G447">
+        <v>1</v>
+      </c>
+      <c r="H447">
+        <v>0</v>
+      </c>
+      <c r="I447">
+        <v>1</v>
+      </c>
+      <c r="J447">
+        <v>0</v>
+      </c>
+      <c r="K447">
+        <v>0</v>
+      </c>
+      <c r="L447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>123</v>
+      </c>
+      <c r="C448">
+        <v>1</v>
+      </c>
+      <c r="D448">
+        <v>2</v>
+      </c>
+      <c r="E448">
+        <v>3</v>
+      </c>
+      <c r="F448">
+        <v>0</v>
+      </c>
+      <c r="G448">
+        <v>1</v>
+      </c>
+      <c r="H448">
+        <v>0</v>
+      </c>
+      <c r="I448">
+        <v>1</v>
+      </c>
+      <c r="J448">
+        <v>0</v>
+      </c>
+      <c r="K448">
+        <v>0</v>
+      </c>
+      <c r="L448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>49</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+      <c r="D449">
+        <v>2</v>
+      </c>
+      <c r="E449">
+        <v>3</v>
+      </c>
+      <c r="F449">
+        <v>0</v>
+      </c>
+      <c r="G449">
+        <v>1</v>
+      </c>
+      <c r="H449">
+        <v>0</v>
+      </c>
+      <c r="I449">
+        <v>1</v>
+      </c>
+      <c r="J449">
+        <v>0</v>
+      </c>
+      <c r="K449">
+        <v>0</v>
+      </c>
+      <c r="L449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>37</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+      <c r="D450">
+        <v>2</v>
+      </c>
+      <c r="E450">
+        <v>3</v>
+      </c>
+      <c r="F450">
+        <v>0</v>
+      </c>
+      <c r="G450">
+        <v>1</v>
+      </c>
+      <c r="H450">
+        <v>0</v>
+      </c>
+      <c r="I450">
+        <v>1</v>
+      </c>
+      <c r="J450">
+        <v>0</v>
+      </c>
+      <c r="K450">
+        <v>0</v>
+      </c>
+      <c r="L450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>3</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+      <c r="D451">
+        <v>2</v>
+      </c>
+      <c r="E451">
+        <v>3</v>
+      </c>
+      <c r="F451">
+        <v>1</v>
+      </c>
+      <c r="G451">
+        <v>1</v>
+      </c>
+      <c r="H451">
+        <v>0</v>
+      </c>
+      <c r="I451">
+        <v>1</v>
+      </c>
+      <c r="J451">
+        <v>0</v>
+      </c>
+      <c r="K451">
+        <v>0</v>
+      </c>
+      <c r="L451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>108</v>
+      </c>
+      <c r="C452">
+        <v>4</v>
+      </c>
+      <c r="D452">
+        <v>5</v>
+      </c>
+      <c r="E452">
+        <v>4</v>
+      </c>
+      <c r="F452">
+        <v>0</v>
+      </c>
+      <c r="G452">
+        <v>1</v>
+      </c>
+      <c r="H452">
+        <v>0</v>
+      </c>
+      <c r="I452">
+        <v>1</v>
+      </c>
+      <c r="J452">
+        <v>0</v>
+      </c>
+      <c r="K452">
+        <v>11</v>
+      </c>
+      <c r="L452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>45</v>
+      </c>
+      <c r="C453">
+        <v>4</v>
+      </c>
+      <c r="D453">
+        <v>5</v>
+      </c>
+      <c r="E453">
+        <v>4</v>
+      </c>
+      <c r="F453">
+        <v>1</v>
+      </c>
+      <c r="G453">
+        <v>1</v>
+      </c>
+      <c r="H453">
+        <v>1</v>
+      </c>
+      <c r="I453">
+        <v>0</v>
+      </c>
+      <c r="J453">
+        <v>0</v>
+      </c>
+      <c r="K453">
+        <v>6</v>
+      </c>
+      <c r="L453">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2150" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{980B6B72-390A-48DA-B29A-CBD1565A2F31}"/>
+  <xr:revisionPtr revIDLastSave="2264" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6FCF602-8C22-46CD-BC9B-417ED913866C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Jogadores!$A$1:$L$456</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Jogadores!$A$1:$L$475</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="125">
   <si>
     <t>Boneco</t>
   </si>
@@ -412,6 +412,9 @@
   <si>
     <t>Samuel</t>
   </si>
+  <si>
+    <t>Jonathan</t>
+  </si>
 </sst>
 </file>
 
@@ -737,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O453"/>
+  <dimension ref="A1:O475"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -16621,8 +16624,778 @@
         <v>0</v>
       </c>
     </row>
+    <row r="454" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>21</v>
+      </c>
+      <c r="C454">
+        <v>4</v>
+      </c>
+      <c r="D454">
+        <v>4</v>
+      </c>
+      <c r="E454">
+        <v>1</v>
+      </c>
+      <c r="F454">
+        <v>2</v>
+      </c>
+      <c r="G454">
+        <v>1</v>
+      </c>
+      <c r="H454">
+        <v>1</v>
+      </c>
+      <c r="I454">
+        <v>0</v>
+      </c>
+      <c r="J454">
+        <v>0</v>
+      </c>
+      <c r="K454">
+        <v>0</v>
+      </c>
+      <c r="L454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>124</v>
+      </c>
+      <c r="C455">
+        <v>4</v>
+      </c>
+      <c r="D455">
+        <v>4</v>
+      </c>
+      <c r="E455">
+        <v>1</v>
+      </c>
+      <c r="F455">
+        <v>3</v>
+      </c>
+      <c r="G455">
+        <v>1</v>
+      </c>
+      <c r="H455">
+        <v>1</v>
+      </c>
+      <c r="I455">
+        <v>0</v>
+      </c>
+      <c r="J455">
+        <v>0</v>
+      </c>
+      <c r="K455">
+        <v>0</v>
+      </c>
+      <c r="L455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>32</v>
+      </c>
+      <c r="C456">
+        <v>4</v>
+      </c>
+      <c r="D456">
+        <v>4</v>
+      </c>
+      <c r="E456">
+        <v>1</v>
+      </c>
+      <c r="F456">
+        <v>0</v>
+      </c>
+      <c r="G456">
+        <v>1</v>
+      </c>
+      <c r="H456">
+        <v>1</v>
+      </c>
+      <c r="I456">
+        <v>0</v>
+      </c>
+      <c r="J456">
+        <v>0</v>
+      </c>
+      <c r="K456">
+        <v>0</v>
+      </c>
+      <c r="L456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
+        <v>84</v>
+      </c>
+      <c r="C457">
+        <v>4</v>
+      </c>
+      <c r="D457">
+        <v>4</v>
+      </c>
+      <c r="E457">
+        <v>1</v>
+      </c>
+      <c r="F457">
+        <v>1</v>
+      </c>
+      <c r="G457">
+        <v>1</v>
+      </c>
+      <c r="H457">
+        <v>1</v>
+      </c>
+      <c r="I457">
+        <v>0</v>
+      </c>
+      <c r="J457">
+        <v>0</v>
+      </c>
+      <c r="K457">
+        <v>0</v>
+      </c>
+      <c r="L457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
+        <v>37</v>
+      </c>
+      <c r="C458">
+        <v>4</v>
+      </c>
+      <c r="D458">
+        <v>4</v>
+      </c>
+      <c r="E458">
+        <v>1</v>
+      </c>
+      <c r="F458">
+        <v>2</v>
+      </c>
+      <c r="G458">
+        <v>1</v>
+      </c>
+      <c r="H458">
+        <v>1</v>
+      </c>
+      <c r="I458">
+        <v>0</v>
+      </c>
+      <c r="J458">
+        <v>0</v>
+      </c>
+      <c r="K458">
+        <v>0</v>
+      </c>
+      <c r="L458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
+        <v>4</v>
+      </c>
+      <c r="C459">
+        <v>2</v>
+      </c>
+      <c r="D459">
+        <v>3</v>
+      </c>
+      <c r="E459">
+        <v>2</v>
+      </c>
+      <c r="F459">
+        <v>3</v>
+      </c>
+      <c r="G459">
+        <v>1</v>
+      </c>
+      <c r="H459">
+        <v>0</v>
+      </c>
+      <c r="I459">
+        <v>0</v>
+      </c>
+      <c r="J459">
+        <v>0</v>
+      </c>
+      <c r="K459">
+        <v>0</v>
+      </c>
+      <c r="L459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
+        <v>117</v>
+      </c>
+      <c r="C460">
+        <v>2</v>
+      </c>
+      <c r="D460">
+        <v>3</v>
+      </c>
+      <c r="E460">
+        <v>2</v>
+      </c>
+      <c r="F460">
+        <v>0</v>
+      </c>
+      <c r="G460">
+        <v>1</v>
+      </c>
+      <c r="H460">
+        <v>0</v>
+      </c>
+      <c r="I460">
+        <v>0</v>
+      </c>
+      <c r="J460">
+        <v>0</v>
+      </c>
+      <c r="K460">
+        <v>0</v>
+      </c>
+      <c r="L460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
+        <v>27</v>
+      </c>
+      <c r="C461">
+        <v>2</v>
+      </c>
+      <c r="D461">
+        <v>3</v>
+      </c>
+      <c r="E461">
+        <v>2</v>
+      </c>
+      <c r="F461">
+        <v>0</v>
+      </c>
+      <c r="G461">
+        <v>1</v>
+      </c>
+      <c r="H461">
+        <v>0</v>
+      </c>
+      <c r="I461">
+        <v>0</v>
+      </c>
+      <c r="J461">
+        <v>0</v>
+      </c>
+      <c r="K461">
+        <v>0</v>
+      </c>
+      <c r="L461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
+        <v>49</v>
+      </c>
+      <c r="C462">
+        <v>2</v>
+      </c>
+      <c r="D462">
+        <v>3</v>
+      </c>
+      <c r="E462">
+        <v>2</v>
+      </c>
+      <c r="F462">
+        <v>0</v>
+      </c>
+      <c r="G462">
+        <v>1</v>
+      </c>
+      <c r="H462">
+        <v>0</v>
+      </c>
+      <c r="I462">
+        <v>0</v>
+      </c>
+      <c r="J462">
+        <v>0</v>
+      </c>
+      <c r="K462">
+        <v>0</v>
+      </c>
+      <c r="L462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
+        <v>1</v>
+      </c>
+      <c r="C463">
+        <v>2</v>
+      </c>
+      <c r="D463">
+        <v>3</v>
+      </c>
+      <c r="E463">
+        <v>2</v>
+      </c>
+      <c r="F463">
+        <v>1</v>
+      </c>
+      <c r="G463">
+        <v>1</v>
+      </c>
+      <c r="H463">
+        <v>0</v>
+      </c>
+      <c r="I463">
+        <v>0</v>
+      </c>
+      <c r="J463">
+        <v>0</v>
+      </c>
+      <c r="K463">
+        <v>0</v>
+      </c>
+      <c r="L463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
+        <v>3</v>
+      </c>
+      <c r="C464">
+        <v>4</v>
+      </c>
+      <c r="D464">
+        <v>1</v>
+      </c>
+      <c r="E464">
+        <v>3</v>
+      </c>
+      <c r="F464">
+        <v>1</v>
+      </c>
+      <c r="G464">
+        <v>1</v>
+      </c>
+      <c r="H464">
+        <v>0</v>
+      </c>
+      <c r="I464">
+        <v>0</v>
+      </c>
+      <c r="J464">
+        <v>0</v>
+      </c>
+      <c r="K464">
+        <v>0</v>
+      </c>
+      <c r="L464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>29</v>
+      </c>
+      <c r="C465">
+        <v>4</v>
+      </c>
+      <c r="D465">
+        <v>1</v>
+      </c>
+      <c r="E465">
+        <v>3</v>
+      </c>
+      <c r="F465">
+        <v>3</v>
+      </c>
+      <c r="G465">
+        <v>1</v>
+      </c>
+      <c r="H465">
+        <v>0</v>
+      </c>
+      <c r="I465">
+        <v>0</v>
+      </c>
+      <c r="J465">
+        <v>0</v>
+      </c>
+      <c r="K465">
+        <v>0</v>
+      </c>
+      <c r="L465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>6</v>
+      </c>
+      <c r="C466">
+        <v>4</v>
+      </c>
+      <c r="D466">
+        <v>1</v>
+      </c>
+      <c r="E466">
+        <v>3</v>
+      </c>
+      <c r="F466">
+        <v>1</v>
+      </c>
+      <c r="G466">
+        <v>1</v>
+      </c>
+      <c r="H466">
+        <v>0</v>
+      </c>
+      <c r="I466">
+        <v>0</v>
+      </c>
+      <c r="J466">
+        <v>0</v>
+      </c>
+      <c r="K466">
+        <v>0</v>
+      </c>
+      <c r="L466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>2</v>
+      </c>
+      <c r="C467">
+        <v>4</v>
+      </c>
+      <c r="D467">
+        <v>1</v>
+      </c>
+      <c r="E467">
+        <v>3</v>
+      </c>
+      <c r="F467">
+        <v>2</v>
+      </c>
+      <c r="G467">
+        <v>1</v>
+      </c>
+      <c r="H467">
+        <v>0</v>
+      </c>
+      <c r="I467">
+        <v>0</v>
+      </c>
+      <c r="J467">
+        <v>0</v>
+      </c>
+      <c r="K467">
+        <v>0</v>
+      </c>
+      <c r="L467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>20</v>
+      </c>
+      <c r="C468">
+        <v>4</v>
+      </c>
+      <c r="D468">
+        <v>1</v>
+      </c>
+      <c r="E468">
+        <v>3</v>
+      </c>
+      <c r="F468">
+        <v>2</v>
+      </c>
+      <c r="G468">
+        <v>1</v>
+      </c>
+      <c r="H468">
+        <v>0</v>
+      </c>
+      <c r="I468">
+        <v>0</v>
+      </c>
+      <c r="J468">
+        <v>0</v>
+      </c>
+      <c r="K468">
+        <v>0</v>
+      </c>
+      <c r="L468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>0</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+      <c r="D469">
+        <v>0</v>
+      </c>
+      <c r="E469">
+        <v>5</v>
+      </c>
+      <c r="F469">
+        <v>0</v>
+      </c>
+      <c r="G469">
+        <v>1</v>
+      </c>
+      <c r="H469">
+        <v>0</v>
+      </c>
+      <c r="I469">
+        <v>1</v>
+      </c>
+      <c r="J469">
+        <v>0</v>
+      </c>
+      <c r="K469">
+        <v>0</v>
+      </c>
+      <c r="L469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
+        <v>7</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+      <c r="D470">
+        <v>0</v>
+      </c>
+      <c r="E470">
+        <v>5</v>
+      </c>
+      <c r="F470">
+        <v>1</v>
+      </c>
+      <c r="G470">
+        <v>1</v>
+      </c>
+      <c r="H470">
+        <v>0</v>
+      </c>
+      <c r="I470">
+        <v>1</v>
+      </c>
+      <c r="J470">
+        <v>0</v>
+      </c>
+      <c r="K470">
+        <v>0</v>
+      </c>
+      <c r="L470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
+        <v>24</v>
+      </c>
+      <c r="C471">
+        <v>1</v>
+      </c>
+      <c r="D471">
+        <v>0</v>
+      </c>
+      <c r="E471">
+        <v>5</v>
+      </c>
+      <c r="F471">
+        <v>0</v>
+      </c>
+      <c r="G471">
+        <v>1</v>
+      </c>
+      <c r="H471">
+        <v>0</v>
+      </c>
+      <c r="I471">
+        <v>1</v>
+      </c>
+      <c r="J471">
+        <v>0</v>
+      </c>
+      <c r="K471">
+        <v>0</v>
+      </c>
+      <c r="L471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
+        <v>59</v>
+      </c>
+      <c r="C472">
+        <v>1</v>
+      </c>
+      <c r="D472">
+        <v>0</v>
+      </c>
+      <c r="E472">
+        <v>5</v>
+      </c>
+      <c r="F472">
+        <v>1</v>
+      </c>
+      <c r="G472">
+        <v>1</v>
+      </c>
+      <c r="H472">
+        <v>0</v>
+      </c>
+      <c r="I472">
+        <v>1</v>
+      </c>
+      <c r="J472">
+        <v>0</v>
+      </c>
+      <c r="K472">
+        <v>0</v>
+      </c>
+      <c r="L472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
+        <v>36</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+      <c r="D473">
+        <v>0</v>
+      </c>
+      <c r="E473">
+        <v>5</v>
+      </c>
+      <c r="F473">
+        <v>0</v>
+      </c>
+      <c r="G473">
+        <v>1</v>
+      </c>
+      <c r="H473">
+        <v>0</v>
+      </c>
+      <c r="I473">
+        <v>1</v>
+      </c>
+      <c r="J473">
+        <v>0</v>
+      </c>
+      <c r="K473">
+        <v>0</v>
+      </c>
+      <c r="L473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
+        <v>80</v>
+      </c>
+      <c r="C474">
+        <v>8</v>
+      </c>
+      <c r="D474">
+        <v>4</v>
+      </c>
+      <c r="E474">
+        <v>4</v>
+      </c>
+      <c r="F474">
+        <v>0</v>
+      </c>
+      <c r="G474">
+        <v>1</v>
+      </c>
+      <c r="H474">
+        <v>1</v>
+      </c>
+      <c r="I474">
+        <v>0</v>
+      </c>
+      <c r="J474">
+        <v>0</v>
+      </c>
+      <c r="K474">
+        <v>6</v>
+      </c>
+      <c r="L474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
+        <v>45</v>
+      </c>
+      <c r="C475">
+        <v>4</v>
+      </c>
+      <c r="D475">
+        <v>4</v>
+      </c>
+      <c r="E475">
+        <v>8</v>
+      </c>
+      <c r="F475">
+        <v>0</v>
+      </c>
+      <c r="G475">
+        <v>1</v>
+      </c>
+      <c r="H475">
+        <v>0</v>
+      </c>
+      <c r="I475">
+        <v>1</v>
+      </c>
+      <c r="J475">
+        <v>0</v>
+      </c>
+      <c r="K475">
+        <v>16</v>
+      </c>
+      <c r="L475">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L456" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L475" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2264" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6FCF602-8C22-46CD-BC9B-417ED913866C}"/>
+  <xr:revisionPtr revIDLastSave="2385" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12FF7A98-B6F7-4D35-9033-CA313C1C0F09}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="127">
   <si>
     <t>Boneco</t>
   </si>
@@ -415,6 +415,12 @@
   <si>
     <t>Jonathan</t>
   </si>
+  <si>
+    <t>Davison</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
 </sst>
 </file>
 
@@ -740,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O475"/>
+  <dimension ref="A1:O498"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -17394,6 +17400,811 @@
         <v>0</v>
       </c>
     </row>
+    <row r="476" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
+        <v>30</v>
+      </c>
+      <c r="C476">
+        <v>3</v>
+      </c>
+      <c r="D476">
+        <v>3</v>
+      </c>
+      <c r="E476">
+        <v>2</v>
+      </c>
+      <c r="F476">
+        <v>3</v>
+      </c>
+      <c r="G476">
+        <v>1</v>
+      </c>
+      <c r="H476">
+        <v>0</v>
+      </c>
+      <c r="I476">
+        <v>0</v>
+      </c>
+      <c r="J476">
+        <v>0</v>
+      </c>
+      <c r="K476">
+        <v>0</v>
+      </c>
+      <c r="L476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
+        <v>27</v>
+      </c>
+      <c r="C477">
+        <v>3</v>
+      </c>
+      <c r="D477">
+        <v>3</v>
+      </c>
+      <c r="E477">
+        <v>2</v>
+      </c>
+      <c r="F477">
+        <v>0</v>
+      </c>
+      <c r="G477">
+        <v>1</v>
+      </c>
+      <c r="H477">
+        <v>0</v>
+      </c>
+      <c r="I477">
+        <v>0</v>
+      </c>
+      <c r="J477">
+        <v>0</v>
+      </c>
+      <c r="K477">
+        <v>0</v>
+      </c>
+      <c r="L477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A478" t="s">
+        <v>20</v>
+      </c>
+      <c r="C478">
+        <v>3</v>
+      </c>
+      <c r="D478">
+        <v>3</v>
+      </c>
+      <c r="E478">
+        <v>2</v>
+      </c>
+      <c r="F478">
+        <v>1</v>
+      </c>
+      <c r="G478">
+        <v>1</v>
+      </c>
+      <c r="H478">
+        <v>0</v>
+      </c>
+      <c r="I478">
+        <v>0</v>
+      </c>
+      <c r="J478">
+        <v>0</v>
+      </c>
+      <c r="K478">
+        <v>0</v>
+      </c>
+      <c r="L478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A479" t="s">
+        <v>125</v>
+      </c>
+      <c r="C479">
+        <v>3</v>
+      </c>
+      <c r="D479">
+        <v>3</v>
+      </c>
+      <c r="E479">
+        <v>2</v>
+      </c>
+      <c r="F479">
+        <v>3</v>
+      </c>
+      <c r="G479">
+        <v>1</v>
+      </c>
+      <c r="H479">
+        <v>0</v>
+      </c>
+      <c r="I479">
+        <v>0</v>
+      </c>
+      <c r="J479">
+        <v>0</v>
+      </c>
+      <c r="K479">
+        <v>0</v>
+      </c>
+      <c r="L479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A480" t="s">
+        <v>34</v>
+      </c>
+      <c r="C480">
+        <v>3</v>
+      </c>
+      <c r="D480">
+        <v>3</v>
+      </c>
+      <c r="E480">
+        <v>2</v>
+      </c>
+      <c r="F480">
+        <v>0</v>
+      </c>
+      <c r="G480">
+        <v>1</v>
+      </c>
+      <c r="H480">
+        <v>0</v>
+      </c>
+      <c r="I480">
+        <v>0</v>
+      </c>
+      <c r="J480">
+        <v>0</v>
+      </c>
+      <c r="K480">
+        <v>0</v>
+      </c>
+      <c r="L480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A481" t="s">
+        <v>36</v>
+      </c>
+      <c r="C481">
+        <v>2</v>
+      </c>
+      <c r="D481">
+        <v>1</v>
+      </c>
+      <c r="E481">
+        <v>4</v>
+      </c>
+      <c r="F481">
+        <v>1</v>
+      </c>
+      <c r="G481">
+        <v>1</v>
+      </c>
+      <c r="H481">
+        <v>0</v>
+      </c>
+      <c r="I481">
+        <v>1</v>
+      </c>
+      <c r="J481">
+        <v>0</v>
+      </c>
+      <c r="K481">
+        <v>0</v>
+      </c>
+      <c r="L481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A482" t="s">
+        <v>29</v>
+      </c>
+      <c r="C482">
+        <v>2</v>
+      </c>
+      <c r="D482">
+        <v>1</v>
+      </c>
+      <c r="E482">
+        <v>4</v>
+      </c>
+      <c r="F482">
+        <v>1</v>
+      </c>
+      <c r="G482">
+        <v>1</v>
+      </c>
+      <c r="H482">
+        <v>0</v>
+      </c>
+      <c r="I482">
+        <v>1</v>
+      </c>
+      <c r="J482">
+        <v>0</v>
+      </c>
+      <c r="K482">
+        <v>0</v>
+      </c>
+      <c r="L482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A483" t="s">
+        <v>2</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+      <c r="D483">
+        <v>1</v>
+      </c>
+      <c r="E483">
+        <v>4</v>
+      </c>
+      <c r="F483">
+        <v>2</v>
+      </c>
+      <c r="G483">
+        <v>1</v>
+      </c>
+      <c r="H483">
+        <v>0</v>
+      </c>
+      <c r="I483">
+        <v>1</v>
+      </c>
+      <c r="J483">
+        <v>0</v>
+      </c>
+      <c r="K483">
+        <v>0</v>
+      </c>
+      <c r="L483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A484" t="s">
+        <v>28</v>
+      </c>
+      <c r="C484">
+        <v>2</v>
+      </c>
+      <c r="D484">
+        <v>1</v>
+      </c>
+      <c r="E484">
+        <v>4</v>
+      </c>
+      <c r="F484">
+        <v>1</v>
+      </c>
+      <c r="G484">
+        <v>1</v>
+      </c>
+      <c r="H484">
+        <v>0</v>
+      </c>
+      <c r="I484">
+        <v>1</v>
+      </c>
+      <c r="J484">
+        <v>0</v>
+      </c>
+      <c r="K484">
+        <v>0</v>
+      </c>
+      <c r="L484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
+        <v>119</v>
+      </c>
+      <c r="C485">
+        <v>2</v>
+      </c>
+      <c r="D485">
+        <v>1</v>
+      </c>
+      <c r="E485">
+        <v>4</v>
+      </c>
+      <c r="F485">
+        <v>0</v>
+      </c>
+      <c r="G485">
+        <v>1</v>
+      </c>
+      <c r="H485">
+        <v>0</v>
+      </c>
+      <c r="I485">
+        <v>1</v>
+      </c>
+      <c r="J485">
+        <v>0</v>
+      </c>
+      <c r="K485">
+        <v>0</v>
+      </c>
+      <c r="L485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
+        <v>0</v>
+      </c>
+      <c r="C486">
+        <v>4</v>
+      </c>
+      <c r="D486">
+        <v>2</v>
+      </c>
+      <c r="E486">
+        <v>3</v>
+      </c>
+      <c r="F486">
+        <v>2</v>
+      </c>
+      <c r="G486">
+        <v>1</v>
+      </c>
+      <c r="H486">
+        <v>1</v>
+      </c>
+      <c r="I486">
+        <v>0</v>
+      </c>
+      <c r="J486">
+        <v>0</v>
+      </c>
+      <c r="K486">
+        <v>0</v>
+      </c>
+      <c r="L486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
+        <v>3</v>
+      </c>
+      <c r="C487">
+        <v>4</v>
+      </c>
+      <c r="D487">
+        <v>2</v>
+      </c>
+      <c r="E487">
+        <v>3</v>
+      </c>
+      <c r="F487">
+        <v>1</v>
+      </c>
+      <c r="G487">
+        <v>1</v>
+      </c>
+      <c r="H487">
+        <v>1</v>
+      </c>
+      <c r="I487">
+        <v>0</v>
+      </c>
+      <c r="J487">
+        <v>0</v>
+      </c>
+      <c r="K487">
+        <v>0</v>
+      </c>
+      <c r="L487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
+        <v>4</v>
+      </c>
+      <c r="C488">
+        <v>4</v>
+      </c>
+      <c r="D488">
+        <v>2</v>
+      </c>
+      <c r="E488">
+        <v>3</v>
+      </c>
+      <c r="F488">
+        <v>0</v>
+      </c>
+      <c r="G488">
+        <v>1</v>
+      </c>
+      <c r="H488">
+        <v>1</v>
+      </c>
+      <c r="I488">
+        <v>0</v>
+      </c>
+      <c r="J488">
+        <v>0</v>
+      </c>
+      <c r="K488">
+        <v>0</v>
+      </c>
+      <c r="L488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
+        <v>99</v>
+      </c>
+      <c r="C489">
+        <v>4</v>
+      </c>
+      <c r="D489">
+        <v>2</v>
+      </c>
+      <c r="E489">
+        <v>3</v>
+      </c>
+      <c r="F489">
+        <v>2</v>
+      </c>
+      <c r="G489">
+        <v>1</v>
+      </c>
+      <c r="H489">
+        <v>1</v>
+      </c>
+      <c r="I489">
+        <v>0</v>
+      </c>
+      <c r="J489">
+        <v>0</v>
+      </c>
+      <c r="K489">
+        <v>0</v>
+      </c>
+      <c r="L489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>23</v>
+      </c>
+      <c r="C490">
+        <v>4</v>
+      </c>
+      <c r="D490">
+        <v>2</v>
+      </c>
+      <c r="E490">
+        <v>3</v>
+      </c>
+      <c r="F490">
+        <v>0</v>
+      </c>
+      <c r="G490">
+        <v>1</v>
+      </c>
+      <c r="H490">
+        <v>1</v>
+      </c>
+      <c r="I490">
+        <v>0</v>
+      </c>
+      <c r="J490">
+        <v>0</v>
+      </c>
+      <c r="K490">
+        <v>0</v>
+      </c>
+      <c r="L490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
+        <v>6</v>
+      </c>
+      <c r="C491">
+        <v>1</v>
+      </c>
+      <c r="D491">
+        <v>4</v>
+      </c>
+      <c r="E491">
+        <v>1</v>
+      </c>
+      <c r="F491">
+        <v>0</v>
+      </c>
+      <c r="G491">
+        <v>1</v>
+      </c>
+      <c r="H491">
+        <v>0</v>
+      </c>
+      <c r="I491">
+        <v>0</v>
+      </c>
+      <c r="J491">
+        <v>0</v>
+      </c>
+      <c r="K491">
+        <v>0</v>
+      </c>
+      <c r="L491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
+        <v>117</v>
+      </c>
+      <c r="C492">
+        <v>1</v>
+      </c>
+      <c r="D492">
+        <v>4</v>
+      </c>
+      <c r="E492">
+        <v>1</v>
+      </c>
+      <c r="F492">
+        <v>0</v>
+      </c>
+      <c r="G492">
+        <v>1</v>
+      </c>
+      <c r="H492">
+        <v>0</v>
+      </c>
+      <c r="I492">
+        <v>0</v>
+      </c>
+      <c r="J492">
+        <v>0</v>
+      </c>
+      <c r="K492">
+        <v>0</v>
+      </c>
+      <c r="L492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
+        <v>1</v>
+      </c>
+      <c r="C493">
+        <v>1</v>
+      </c>
+      <c r="D493">
+        <v>4</v>
+      </c>
+      <c r="E493">
+        <v>1</v>
+      </c>
+      <c r="F493">
+        <v>3</v>
+      </c>
+      <c r="G493">
+        <v>1</v>
+      </c>
+      <c r="H493">
+        <v>0</v>
+      </c>
+      <c r="I493">
+        <v>0</v>
+      </c>
+      <c r="J493">
+        <v>0</v>
+      </c>
+      <c r="K493">
+        <v>0</v>
+      </c>
+      <c r="L493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
+        <v>57</v>
+      </c>
+      <c r="C494">
+        <v>1</v>
+      </c>
+      <c r="D494">
+        <v>4</v>
+      </c>
+      <c r="E494">
+        <v>1</v>
+      </c>
+      <c r="F494">
+        <v>1</v>
+      </c>
+      <c r="G494">
+        <v>1</v>
+      </c>
+      <c r="H494">
+        <v>0</v>
+      </c>
+      <c r="I494">
+        <v>0</v>
+      </c>
+      <c r="J494">
+        <v>0</v>
+      </c>
+      <c r="K494">
+        <v>0</v>
+      </c>
+      <c r="L494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>37</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+      <c r="D495">
+        <v>4</v>
+      </c>
+      <c r="E495">
+        <v>1</v>
+      </c>
+      <c r="F495">
+        <v>1</v>
+      </c>
+      <c r="G495">
+        <v>1</v>
+      </c>
+      <c r="H495">
+        <v>0</v>
+      </c>
+      <c r="I495">
+        <v>0</v>
+      </c>
+      <c r="J495">
+        <v>0</v>
+      </c>
+      <c r="K495">
+        <v>0</v>
+      </c>
+      <c r="L495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
+        <v>17</v>
+      </c>
+      <c r="C496">
+        <v>6</v>
+      </c>
+      <c r="D496">
+        <v>2</v>
+      </c>
+      <c r="E496">
+        <v>3</v>
+      </c>
+      <c r="F496">
+        <v>0</v>
+      </c>
+      <c r="G496">
+        <v>1</v>
+      </c>
+      <c r="H496">
+        <v>1</v>
+      </c>
+      <c r="I496">
+        <v>0</v>
+      </c>
+      <c r="J496">
+        <v>0</v>
+      </c>
+      <c r="K496">
+        <v>3</v>
+      </c>
+      <c r="L496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A497" t="s">
+        <v>45</v>
+      </c>
+      <c r="C497">
+        <v>3</v>
+      </c>
+      <c r="D497">
+        <v>2</v>
+      </c>
+      <c r="E497">
+        <v>5</v>
+      </c>
+      <c r="F497">
+        <v>0</v>
+      </c>
+      <c r="G497">
+        <v>1</v>
+      </c>
+      <c r="H497">
+        <v>0</v>
+      </c>
+      <c r="I497">
+        <v>1</v>
+      </c>
+      <c r="J497">
+        <v>0</v>
+      </c>
+      <c r="K497">
+        <v>9</v>
+      </c>
+      <c r="L497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
+        <v>126</v>
+      </c>
+      <c r="C498">
+        <v>3</v>
+      </c>
+      <c r="D498">
+        <v>4</v>
+      </c>
+      <c r="E498">
+        <v>3</v>
+      </c>
+      <c r="F498">
+        <v>0</v>
+      </c>
+      <c r="G498">
+        <v>1</v>
+      </c>
+      <c r="H498">
+        <v>0</v>
+      </c>
+      <c r="I498">
+        <v>0</v>
+      </c>
+      <c r="J498">
+        <v>0</v>
+      </c>
+      <c r="K498">
+        <v>5</v>
+      </c>
+      <c r="L498">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L475" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2385" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12FF7A98-B6F7-4D35-9033-CA313C1C0F09}"/>
+  <xr:revisionPtr revIDLastSave="2494" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9771B86-123E-4134-8471-157DE73C586B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="131">
   <si>
     <t>Boneco</t>
   </si>
@@ -421,6 +421,18 @@
   <si>
     <t>Pedro</t>
   </si>
+  <si>
+    <t>Enzo</t>
+  </si>
+  <si>
+    <t>leandrão</t>
+  </si>
+  <si>
+    <t>Loirinho</t>
+  </si>
+  <si>
+    <t>Renan</t>
+  </si>
 </sst>
 </file>
 
@@ -746,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O498"/>
+  <dimension ref="A1:O520"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -18205,6 +18217,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="499" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A499" t="s">
+        <v>34</v>
+      </c>
+      <c r="C499">
+        <v>4</v>
+      </c>
+      <c r="D499">
+        <v>4</v>
+      </c>
+      <c r="E499">
+        <v>1</v>
+      </c>
+      <c r="F499">
+        <v>4</v>
+      </c>
+      <c r="G499">
+        <v>1</v>
+      </c>
+      <c r="H499">
+        <v>1</v>
+      </c>
+      <c r="I499">
+        <v>0</v>
+      </c>
+      <c r="J499">
+        <v>0</v>
+      </c>
+      <c r="K499">
+        <v>0</v>
+      </c>
+      <c r="L499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
+        <v>20</v>
+      </c>
+      <c r="C500">
+        <v>4</v>
+      </c>
+      <c r="D500">
+        <v>4</v>
+      </c>
+      <c r="E500">
+        <v>1</v>
+      </c>
+      <c r="F500">
+        <v>0</v>
+      </c>
+      <c r="G500">
+        <v>1</v>
+      </c>
+      <c r="H500">
+        <v>1</v>
+      </c>
+      <c r="I500">
+        <v>0</v>
+      </c>
+      <c r="J500">
+        <v>0</v>
+      </c>
+      <c r="K500">
+        <v>0</v>
+      </c>
+      <c r="L500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A501" t="s">
+        <v>127</v>
+      </c>
+      <c r="C501">
+        <v>4</v>
+      </c>
+      <c r="D501">
+        <v>4</v>
+      </c>
+      <c r="E501">
+        <v>1</v>
+      </c>
+      <c r="F501">
+        <v>0</v>
+      </c>
+      <c r="G501">
+        <v>1</v>
+      </c>
+      <c r="H501">
+        <v>1</v>
+      </c>
+      <c r="I501">
+        <v>0</v>
+      </c>
+      <c r="J501">
+        <v>0</v>
+      </c>
+      <c r="K501">
+        <v>0</v>
+      </c>
+      <c r="L501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
+        <v>57</v>
+      </c>
+      <c r="C502">
+        <v>4</v>
+      </c>
+      <c r="D502">
+        <v>4</v>
+      </c>
+      <c r="E502">
+        <v>1</v>
+      </c>
+      <c r="F502">
+        <v>4</v>
+      </c>
+      <c r="G502">
+        <v>1</v>
+      </c>
+      <c r="H502">
+        <v>1</v>
+      </c>
+      <c r="I502">
+        <v>0</v>
+      </c>
+      <c r="J502">
+        <v>0</v>
+      </c>
+      <c r="K502">
+        <v>0</v>
+      </c>
+      <c r="L502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A503" t="s">
+        <v>21</v>
+      </c>
+      <c r="C503">
+        <v>4</v>
+      </c>
+      <c r="D503">
+        <v>4</v>
+      </c>
+      <c r="E503">
+        <v>1</v>
+      </c>
+      <c r="F503">
+        <v>2</v>
+      </c>
+      <c r="G503">
+        <v>1</v>
+      </c>
+      <c r="H503">
+        <v>1</v>
+      </c>
+      <c r="I503">
+        <v>0</v>
+      </c>
+      <c r="J503">
+        <v>0</v>
+      </c>
+      <c r="K503">
+        <v>0</v>
+      </c>
+      <c r="L503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
+        <v>29</v>
+      </c>
+      <c r="C504">
+        <v>2</v>
+      </c>
+      <c r="D504">
+        <v>2</v>
+      </c>
+      <c r="E504">
+        <v>4</v>
+      </c>
+      <c r="F504">
+        <v>1</v>
+      </c>
+      <c r="G504">
+        <v>1</v>
+      </c>
+      <c r="H504">
+        <v>0</v>
+      </c>
+      <c r="I504">
+        <v>0</v>
+      </c>
+      <c r="J504">
+        <v>0</v>
+      </c>
+      <c r="K504">
+        <v>0</v>
+      </c>
+      <c r="L504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A505" t="s">
+        <v>128</v>
+      </c>
+      <c r="C505">
+        <v>2</v>
+      </c>
+      <c r="D505">
+        <v>2</v>
+      </c>
+      <c r="E505">
+        <v>4</v>
+      </c>
+      <c r="F505">
+        <v>0</v>
+      </c>
+      <c r="G505">
+        <v>1</v>
+      </c>
+      <c r="H505">
+        <v>0</v>
+      </c>
+      <c r="I505">
+        <v>0</v>
+      </c>
+      <c r="J505">
+        <v>0</v>
+      </c>
+      <c r="K505">
+        <v>0</v>
+      </c>
+      <c r="L505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
+        <v>48</v>
+      </c>
+      <c r="C506">
+        <v>2</v>
+      </c>
+      <c r="D506">
+        <v>2</v>
+      </c>
+      <c r="E506">
+        <v>4</v>
+      </c>
+      <c r="F506">
+        <v>1</v>
+      </c>
+      <c r="G506">
+        <v>1</v>
+      </c>
+      <c r="H506">
+        <v>0</v>
+      </c>
+      <c r="I506">
+        <v>0</v>
+      </c>
+      <c r="J506">
+        <v>0</v>
+      </c>
+      <c r="K506">
+        <v>0</v>
+      </c>
+      <c r="L506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A507" t="s">
+        <v>3</v>
+      </c>
+      <c r="C507">
+        <v>2</v>
+      </c>
+      <c r="D507">
+        <v>2</v>
+      </c>
+      <c r="E507">
+        <v>4</v>
+      </c>
+      <c r="F507">
+        <v>1</v>
+      </c>
+      <c r="G507">
+        <v>1</v>
+      </c>
+      <c r="H507">
+        <v>0</v>
+      </c>
+      <c r="I507">
+        <v>0</v>
+      </c>
+      <c r="J507">
+        <v>0</v>
+      </c>
+      <c r="K507">
+        <v>0</v>
+      </c>
+      <c r="L507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
+        <v>6</v>
+      </c>
+      <c r="C508">
+        <v>2</v>
+      </c>
+      <c r="D508">
+        <v>2</v>
+      </c>
+      <c r="E508">
+        <v>4</v>
+      </c>
+      <c r="F508">
+        <v>3</v>
+      </c>
+      <c r="G508">
+        <v>1</v>
+      </c>
+      <c r="H508">
+        <v>0</v>
+      </c>
+      <c r="I508">
+        <v>0</v>
+      </c>
+      <c r="J508">
+        <v>0</v>
+      </c>
+      <c r="K508">
+        <v>0</v>
+      </c>
+      <c r="L508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
+        <v>110</v>
+      </c>
+      <c r="C509">
+        <v>1</v>
+      </c>
+      <c r="D509">
+        <v>1</v>
+      </c>
+      <c r="E509">
+        <v>4</v>
+      </c>
+      <c r="F509">
+        <v>0</v>
+      </c>
+      <c r="G509">
+        <v>1</v>
+      </c>
+      <c r="H509">
+        <v>0</v>
+      </c>
+      <c r="I509">
+        <v>1</v>
+      </c>
+      <c r="J509">
+        <v>0</v>
+      </c>
+      <c r="K509">
+        <v>0</v>
+      </c>
+      <c r="L509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
+        <v>32</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+      <c r="D510">
+        <v>1</v>
+      </c>
+      <c r="E510">
+        <v>4</v>
+      </c>
+      <c r="F510">
+        <v>0</v>
+      </c>
+      <c r="G510">
+        <v>1</v>
+      </c>
+      <c r="H510">
+        <v>0</v>
+      </c>
+      <c r="I510">
+        <v>1</v>
+      </c>
+      <c r="J510">
+        <v>0</v>
+      </c>
+      <c r="K510">
+        <v>0</v>
+      </c>
+      <c r="L510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
+        <v>4</v>
+      </c>
+      <c r="C511">
+        <v>1</v>
+      </c>
+      <c r="D511">
+        <v>1</v>
+      </c>
+      <c r="E511">
+        <v>4</v>
+      </c>
+      <c r="F511">
+        <v>1</v>
+      </c>
+      <c r="G511">
+        <v>1</v>
+      </c>
+      <c r="H511">
+        <v>0</v>
+      </c>
+      <c r="I511">
+        <v>1</v>
+      </c>
+      <c r="J511">
+        <v>0</v>
+      </c>
+      <c r="K511">
+        <v>0</v>
+      </c>
+      <c r="L511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>37</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+      <c r="D512">
+        <v>1</v>
+      </c>
+      <c r="E512">
+        <v>4</v>
+      </c>
+      <c r="F512">
+        <v>0</v>
+      </c>
+      <c r="G512">
+        <v>1</v>
+      </c>
+      <c r="H512">
+        <v>0</v>
+      </c>
+      <c r="I512">
+        <v>1</v>
+      </c>
+      <c r="J512">
+        <v>0</v>
+      </c>
+      <c r="K512">
+        <v>0</v>
+      </c>
+      <c r="L512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
+        <v>1</v>
+      </c>
+      <c r="C513">
+        <v>1</v>
+      </c>
+      <c r="D513">
+        <v>1</v>
+      </c>
+      <c r="E513">
+        <v>4</v>
+      </c>
+      <c r="F513">
+        <v>1</v>
+      </c>
+      <c r="G513">
+        <v>1</v>
+      </c>
+      <c r="H513">
+        <v>0</v>
+      </c>
+      <c r="I513">
+        <v>1</v>
+      </c>
+      <c r="J513">
+        <v>0</v>
+      </c>
+      <c r="K513">
+        <v>0</v>
+      </c>
+      <c r="L513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
+        <v>59</v>
+      </c>
+      <c r="C514">
+        <v>5</v>
+      </c>
+      <c r="D514">
+        <v>1</v>
+      </c>
+      <c r="E514">
+        <v>3</v>
+      </c>
+      <c r="F514">
+        <v>3</v>
+      </c>
+      <c r="G514">
+        <v>1</v>
+      </c>
+      <c r="H514">
+        <v>0</v>
+      </c>
+      <c r="I514">
+        <v>0</v>
+      </c>
+      <c r="J514">
+        <v>0</v>
+      </c>
+      <c r="K514">
+        <v>0</v>
+      </c>
+      <c r="L514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
+        <v>2</v>
+      </c>
+      <c r="C515">
+        <v>5</v>
+      </c>
+      <c r="D515">
+        <v>1</v>
+      </c>
+      <c r="E515">
+        <v>3</v>
+      </c>
+      <c r="F515">
+        <v>3</v>
+      </c>
+      <c r="G515">
+        <v>1</v>
+      </c>
+      <c r="H515">
+        <v>0</v>
+      </c>
+      <c r="I515">
+        <v>0</v>
+      </c>
+      <c r="J515">
+        <v>0</v>
+      </c>
+      <c r="K515">
+        <v>0</v>
+      </c>
+      <c r="L515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
+        <v>26</v>
+      </c>
+      <c r="C516">
+        <v>5</v>
+      </c>
+      <c r="D516">
+        <v>1</v>
+      </c>
+      <c r="E516">
+        <v>3</v>
+      </c>
+      <c r="F516">
+        <v>0</v>
+      </c>
+      <c r="G516">
+        <v>1</v>
+      </c>
+      <c r="H516">
+        <v>0</v>
+      </c>
+      <c r="I516">
+        <v>0</v>
+      </c>
+      <c r="J516">
+        <v>0</v>
+      </c>
+      <c r="K516">
+        <v>0</v>
+      </c>
+      <c r="L516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
+        <v>84</v>
+      </c>
+      <c r="C517">
+        <v>5</v>
+      </c>
+      <c r="D517">
+        <v>1</v>
+      </c>
+      <c r="E517">
+        <v>3</v>
+      </c>
+      <c r="F517">
+        <v>2</v>
+      </c>
+      <c r="G517">
+        <v>1</v>
+      </c>
+      <c r="H517">
+        <v>0</v>
+      </c>
+      <c r="I517">
+        <v>0</v>
+      </c>
+      <c r="J517">
+        <v>0</v>
+      </c>
+      <c r="K517">
+        <v>0</v>
+      </c>
+      <c r="L517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
+        <v>129</v>
+      </c>
+      <c r="C518">
+        <v>5</v>
+      </c>
+      <c r="D518">
+        <v>1</v>
+      </c>
+      <c r="E518">
+        <v>3</v>
+      </c>
+      <c r="F518">
+        <v>2</v>
+      </c>
+      <c r="G518">
+        <v>1</v>
+      </c>
+      <c r="H518">
+        <v>0</v>
+      </c>
+      <c r="I518">
+        <v>0</v>
+      </c>
+      <c r="J518">
+        <v>0</v>
+      </c>
+      <c r="K518">
+        <v>0</v>
+      </c>
+      <c r="L518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
+        <v>108</v>
+      </c>
+      <c r="C519">
+        <v>8</v>
+      </c>
+      <c r="D519">
+        <v>4</v>
+      </c>
+      <c r="E519">
+        <v>5</v>
+      </c>
+      <c r="F519">
+        <v>0</v>
+      </c>
+      <c r="G519">
+        <v>1</v>
+      </c>
+      <c r="H519">
+        <v>1</v>
+      </c>
+      <c r="I519">
+        <v>0</v>
+      </c>
+      <c r="J519">
+        <v>0</v>
+      </c>
+      <c r="K519">
+        <v>9</v>
+      </c>
+      <c r="L519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
+        <v>130</v>
+      </c>
+      <c r="C520">
+        <v>5</v>
+      </c>
+      <c r="D520">
+        <v>4</v>
+      </c>
+      <c r="E520">
+        <v>8</v>
+      </c>
+      <c r="F520">
+        <v>0</v>
+      </c>
+      <c r="G520">
+        <v>1</v>
+      </c>
+      <c r="H520">
+        <v>0</v>
+      </c>
+      <c r="I520">
+        <v>1</v>
+      </c>
+      <c r="J520">
+        <v>0</v>
+      </c>
+      <c r="K520">
+        <v>14</v>
+      </c>
+      <c r="L520">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L475" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2494" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9771B86-123E-4134-8471-157DE73C586B}"/>
+  <xr:revisionPtr revIDLastSave="2602" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53BDC2D9-9837-4906-BB5F-B620717BAFD8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="133">
   <si>
     <t>Boneco</t>
   </si>
@@ -433,6 +433,12 @@
   <si>
     <t>Renan</t>
   </si>
+  <si>
+    <t>Presley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro </t>
+  </si>
 </sst>
 </file>
 
@@ -758,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O520"/>
+  <dimension ref="A1:O541"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -18987,6 +18993,741 @@
         <v>0</v>
       </c>
     </row>
+    <row r="521" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A521" t="s">
+        <v>34</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+      <c r="D521">
+        <v>3</v>
+      </c>
+      <c r="E521">
+        <v>3</v>
+      </c>
+      <c r="F521">
+        <v>1</v>
+      </c>
+      <c r="G521">
+        <v>1</v>
+      </c>
+      <c r="H521">
+        <v>0</v>
+      </c>
+      <c r="I521">
+        <v>0</v>
+      </c>
+      <c r="J521">
+        <v>0</v>
+      </c>
+      <c r="K521">
+        <v>0</v>
+      </c>
+      <c r="L521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
+        <v>129</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
+      <c r="D522">
+        <v>3</v>
+      </c>
+      <c r="E522">
+        <v>3</v>
+      </c>
+      <c r="F522">
+        <v>0</v>
+      </c>
+      <c r="G522">
+        <v>1</v>
+      </c>
+      <c r="H522">
+        <v>0</v>
+      </c>
+      <c r="I522">
+        <v>0</v>
+      </c>
+      <c r="J522">
+        <v>0</v>
+      </c>
+      <c r="K522">
+        <v>0</v>
+      </c>
+      <c r="L522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A523" t="s">
+        <v>21</v>
+      </c>
+      <c r="C523">
+        <v>1</v>
+      </c>
+      <c r="D523">
+        <v>3</v>
+      </c>
+      <c r="E523">
+        <v>3</v>
+      </c>
+      <c r="F523">
+        <v>2</v>
+      </c>
+      <c r="G523">
+        <v>1</v>
+      </c>
+      <c r="H523">
+        <v>0</v>
+      </c>
+      <c r="I523">
+        <v>0</v>
+      </c>
+      <c r="J523">
+        <v>0</v>
+      </c>
+      <c r="K523">
+        <v>0</v>
+      </c>
+      <c r="L523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
+        <v>25</v>
+      </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
+      <c r="D524">
+        <v>3</v>
+      </c>
+      <c r="E524">
+        <v>3</v>
+      </c>
+      <c r="F524">
+        <v>0</v>
+      </c>
+      <c r="G524">
+        <v>1</v>
+      </c>
+      <c r="H524">
+        <v>0</v>
+      </c>
+      <c r="I524">
+        <v>0</v>
+      </c>
+      <c r="J524">
+        <v>0</v>
+      </c>
+      <c r="K524">
+        <v>0</v>
+      </c>
+      <c r="L524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A525" t="s">
+        <v>32</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+      <c r="D525">
+        <v>3</v>
+      </c>
+      <c r="E525">
+        <v>3</v>
+      </c>
+      <c r="F525">
+        <v>1</v>
+      </c>
+      <c r="G525">
+        <v>1</v>
+      </c>
+      <c r="H525">
+        <v>0</v>
+      </c>
+      <c r="I525">
+        <v>0</v>
+      </c>
+      <c r="J525">
+        <v>0</v>
+      </c>
+      <c r="K525">
+        <v>0</v>
+      </c>
+      <c r="L525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
+        <v>29</v>
+      </c>
+      <c r="C526">
+        <v>4</v>
+      </c>
+      <c r="D526">
+        <v>3</v>
+      </c>
+      <c r="E526">
+        <v>2</v>
+      </c>
+      <c r="F526">
+        <v>2</v>
+      </c>
+      <c r="G526">
+        <v>1</v>
+      </c>
+      <c r="H526">
+        <v>1</v>
+      </c>
+      <c r="I526">
+        <v>0</v>
+      </c>
+      <c r="J526">
+        <v>0</v>
+      </c>
+      <c r="K526">
+        <v>0</v>
+      </c>
+      <c r="L526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
+        <v>4</v>
+      </c>
+      <c r="C527">
+        <v>4</v>
+      </c>
+      <c r="D527">
+        <v>3</v>
+      </c>
+      <c r="E527">
+        <v>2</v>
+      </c>
+      <c r="F527">
+        <v>4</v>
+      </c>
+      <c r="G527">
+        <v>1</v>
+      </c>
+      <c r="H527">
+        <v>1</v>
+      </c>
+      <c r="I527">
+        <v>0</v>
+      </c>
+      <c r="J527">
+        <v>0</v>
+      </c>
+      <c r="K527">
+        <v>0</v>
+      </c>
+      <c r="L527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
+        <v>3</v>
+      </c>
+      <c r="C528">
+        <v>4</v>
+      </c>
+      <c r="D528">
+        <v>3</v>
+      </c>
+      <c r="E528">
+        <v>2</v>
+      </c>
+      <c r="F528">
+        <v>1</v>
+      </c>
+      <c r="G528">
+        <v>1</v>
+      </c>
+      <c r="H528">
+        <v>1</v>
+      </c>
+      <c r="I528">
+        <v>0</v>
+      </c>
+      <c r="J528">
+        <v>0</v>
+      </c>
+      <c r="K528">
+        <v>0</v>
+      </c>
+      <c r="L528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
+        <v>67</v>
+      </c>
+      <c r="C529">
+        <v>4</v>
+      </c>
+      <c r="D529">
+        <v>3</v>
+      </c>
+      <c r="E529">
+        <v>2</v>
+      </c>
+      <c r="F529">
+        <v>1</v>
+      </c>
+      <c r="G529">
+        <v>1</v>
+      </c>
+      <c r="H529">
+        <v>1</v>
+      </c>
+      <c r="I529">
+        <v>0</v>
+      </c>
+      <c r="J529">
+        <v>0</v>
+      </c>
+      <c r="K529">
+        <v>0</v>
+      </c>
+      <c r="L529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
+        <v>128</v>
+      </c>
+      <c r="C530">
+        <v>1</v>
+      </c>
+      <c r="D530">
+        <v>2</v>
+      </c>
+      <c r="E530">
+        <v>3</v>
+      </c>
+      <c r="F530">
+        <v>0</v>
+      </c>
+      <c r="G530">
+        <v>1</v>
+      </c>
+      <c r="H530">
+        <v>0</v>
+      </c>
+      <c r="I530">
+        <v>1</v>
+      </c>
+      <c r="J530">
+        <v>0</v>
+      </c>
+      <c r="K530">
+        <v>0</v>
+      </c>
+      <c r="L530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A531" t="s">
+        <v>27</v>
+      </c>
+      <c r="C531">
+        <v>1</v>
+      </c>
+      <c r="D531">
+        <v>2</v>
+      </c>
+      <c r="E531">
+        <v>3</v>
+      </c>
+      <c r="F531">
+        <v>1</v>
+      </c>
+      <c r="G531">
+        <v>1</v>
+      </c>
+      <c r="H531">
+        <v>0</v>
+      </c>
+      <c r="I531">
+        <v>1</v>
+      </c>
+      <c r="J531">
+        <v>0</v>
+      </c>
+      <c r="K531">
+        <v>0</v>
+      </c>
+      <c r="L531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
+        <v>2</v>
+      </c>
+      <c r="C532">
+        <v>1</v>
+      </c>
+      <c r="D532">
+        <v>2</v>
+      </c>
+      <c r="E532">
+        <v>3</v>
+      </c>
+      <c r="F532">
+        <v>2</v>
+      </c>
+      <c r="G532">
+        <v>1</v>
+      </c>
+      <c r="H532">
+        <v>0</v>
+      </c>
+      <c r="I532">
+        <v>1</v>
+      </c>
+      <c r="J532">
+        <v>0</v>
+      </c>
+      <c r="K532">
+        <v>0</v>
+      </c>
+      <c r="L532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A533" t="s">
+        <v>110</v>
+      </c>
+      <c r="C533">
+        <v>1</v>
+      </c>
+      <c r="D533">
+        <v>2</v>
+      </c>
+      <c r="E533">
+        <v>3</v>
+      </c>
+      <c r="F533">
+        <v>1</v>
+      </c>
+      <c r="G533">
+        <v>1</v>
+      </c>
+      <c r="H533">
+        <v>0</v>
+      </c>
+      <c r="I533">
+        <v>1</v>
+      </c>
+      <c r="J533">
+        <v>0</v>
+      </c>
+      <c r="K533">
+        <v>0</v>
+      </c>
+      <c r="L533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
+        <v>57</v>
+      </c>
+      <c r="C534">
+        <v>1</v>
+      </c>
+      <c r="D534">
+        <v>2</v>
+      </c>
+      <c r="E534">
+        <v>3</v>
+      </c>
+      <c r="F534">
+        <v>0</v>
+      </c>
+      <c r="G534">
+        <v>1</v>
+      </c>
+      <c r="H534">
+        <v>0</v>
+      </c>
+      <c r="I534">
+        <v>1</v>
+      </c>
+      <c r="J534">
+        <v>0</v>
+      </c>
+      <c r="K534">
+        <v>0</v>
+      </c>
+      <c r="L534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A535" t="s">
+        <v>20</v>
+      </c>
+      <c r="C535">
+        <v>4</v>
+      </c>
+      <c r="D535">
+        <v>2</v>
+      </c>
+      <c r="E535">
+        <v>2</v>
+      </c>
+      <c r="F535">
+        <v>1</v>
+      </c>
+      <c r="G535">
+        <v>1</v>
+      </c>
+      <c r="H535">
+        <v>0</v>
+      </c>
+      <c r="I535">
+        <v>0</v>
+      </c>
+      <c r="J535">
+        <v>0</v>
+      </c>
+      <c r="K535">
+        <v>0</v>
+      </c>
+      <c r="L535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
+        <v>131</v>
+      </c>
+      <c r="C536">
+        <v>4</v>
+      </c>
+      <c r="D536">
+        <v>2</v>
+      </c>
+      <c r="E536">
+        <v>2</v>
+      </c>
+      <c r="F536">
+        <v>3</v>
+      </c>
+      <c r="G536">
+        <v>1</v>
+      </c>
+      <c r="H536">
+        <v>0</v>
+      </c>
+      <c r="I536">
+        <v>0</v>
+      </c>
+      <c r="J536">
+        <v>0</v>
+      </c>
+      <c r="K536">
+        <v>0</v>
+      </c>
+      <c r="L536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A537" t="s">
+        <v>43</v>
+      </c>
+      <c r="C537">
+        <v>4</v>
+      </c>
+      <c r="D537">
+        <v>2</v>
+      </c>
+      <c r="E537">
+        <v>2</v>
+      </c>
+      <c r="F537">
+        <v>1</v>
+      </c>
+      <c r="G537">
+        <v>1</v>
+      </c>
+      <c r="H537">
+        <v>0</v>
+      </c>
+      <c r="I537">
+        <v>0</v>
+      </c>
+      <c r="J537">
+        <v>0</v>
+      </c>
+      <c r="K537">
+        <v>0</v>
+      </c>
+      <c r="L537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
+        <v>37</v>
+      </c>
+      <c r="C538">
+        <v>4</v>
+      </c>
+      <c r="D538">
+        <v>2</v>
+      </c>
+      <c r="E538">
+        <v>2</v>
+      </c>
+      <c r="F538">
+        <v>1</v>
+      </c>
+      <c r="G538">
+        <v>1</v>
+      </c>
+      <c r="H538">
+        <v>0</v>
+      </c>
+      <c r="I538">
+        <v>0</v>
+      </c>
+      <c r="J538">
+        <v>0</v>
+      </c>
+      <c r="K538">
+        <v>0</v>
+      </c>
+      <c r="L538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A539" t="s">
+        <v>6</v>
+      </c>
+      <c r="C539">
+        <v>4</v>
+      </c>
+      <c r="D539">
+        <v>2</v>
+      </c>
+      <c r="E539">
+        <v>2</v>
+      </c>
+      <c r="F539">
+        <v>0</v>
+      </c>
+      <c r="G539">
+        <v>1</v>
+      </c>
+      <c r="H539">
+        <v>0</v>
+      </c>
+      <c r="I539">
+        <v>0</v>
+      </c>
+      <c r="J539">
+        <v>0</v>
+      </c>
+      <c r="K539">
+        <v>0</v>
+      </c>
+      <c r="L539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>132</v>
+      </c>
+      <c r="C540">
+        <v>4</v>
+      </c>
+      <c r="D540">
+        <v>4</v>
+      </c>
+      <c r="E540">
+        <v>5</v>
+      </c>
+      <c r="F540">
+        <v>0</v>
+      </c>
+      <c r="G540">
+        <v>1</v>
+      </c>
+      <c r="H540">
+        <v>0</v>
+      </c>
+      <c r="I540">
+        <v>1</v>
+      </c>
+      <c r="J540">
+        <v>0</v>
+      </c>
+      <c r="K540">
+        <v>12</v>
+      </c>
+      <c r="L540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>45</v>
+      </c>
+      <c r="C541">
+        <v>5</v>
+      </c>
+      <c r="D541">
+        <v>4</v>
+      </c>
+      <c r="E541">
+        <v>4</v>
+      </c>
+      <c r="F541">
+        <v>0</v>
+      </c>
+      <c r="G541">
+        <v>1</v>
+      </c>
+      <c r="H541">
+        <v>1</v>
+      </c>
+      <c r="I541">
+        <v>0</v>
+      </c>
+      <c r="J541">
+        <v>0</v>
+      </c>
+      <c r="K541">
+        <v>10</v>
+      </c>
+      <c r="L541">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L475" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2602" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53BDC2D9-9837-4906-BB5F-B620717BAFD8}"/>
+  <xr:revisionPtr revIDLastSave="2711" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D44DEC07-391A-4F61-B868-520DEEB0EA5E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="133">
   <si>
     <t>Boneco</t>
   </si>
@@ -764,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O541"/>
+  <dimension ref="A1:O563"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -19728,6 +19728,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="542" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>29</v>
+      </c>
+      <c r="C542">
+        <v>2</v>
+      </c>
+      <c r="D542">
+        <v>3</v>
+      </c>
+      <c r="E542">
+        <v>3</v>
+      </c>
+      <c r="F542">
+        <v>0</v>
+      </c>
+      <c r="G542">
+        <v>1</v>
+      </c>
+      <c r="H542">
+        <v>0</v>
+      </c>
+      <c r="I542">
+        <v>0</v>
+      </c>
+      <c r="J542">
+        <v>0</v>
+      </c>
+      <c r="K542">
+        <v>0</v>
+      </c>
+      <c r="L542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>1</v>
+      </c>
+      <c r="C543">
+        <v>2</v>
+      </c>
+      <c r="D543">
+        <v>3</v>
+      </c>
+      <c r="E543">
+        <v>3</v>
+      </c>
+      <c r="F543">
+        <v>1</v>
+      </c>
+      <c r="G543">
+        <v>1</v>
+      </c>
+      <c r="H543">
+        <v>0</v>
+      </c>
+      <c r="I543">
+        <v>0</v>
+      </c>
+      <c r="J543">
+        <v>0</v>
+      </c>
+      <c r="K543">
+        <v>0</v>
+      </c>
+      <c r="L543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>20</v>
+      </c>
+      <c r="C544">
+        <v>2</v>
+      </c>
+      <c r="D544">
+        <v>3</v>
+      </c>
+      <c r="E544">
+        <v>3</v>
+      </c>
+      <c r="F544">
+        <v>0</v>
+      </c>
+      <c r="G544">
+        <v>1</v>
+      </c>
+      <c r="H544">
+        <v>0</v>
+      </c>
+      <c r="I544">
+        <v>0</v>
+      </c>
+      <c r="J544">
+        <v>0</v>
+      </c>
+      <c r="K544">
+        <v>0</v>
+      </c>
+      <c r="L544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>6</v>
+      </c>
+      <c r="C545">
+        <v>2</v>
+      </c>
+      <c r="D545">
+        <v>3</v>
+      </c>
+      <c r="E545">
+        <v>3</v>
+      </c>
+      <c r="F545">
+        <v>2</v>
+      </c>
+      <c r="G545">
+        <v>1</v>
+      </c>
+      <c r="H545">
+        <v>0</v>
+      </c>
+      <c r="I545">
+        <v>0</v>
+      </c>
+      <c r="J545">
+        <v>0</v>
+      </c>
+      <c r="K545">
+        <v>0</v>
+      </c>
+      <c r="L545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>5</v>
+      </c>
+      <c r="C546">
+        <v>2</v>
+      </c>
+      <c r="D546">
+        <v>3</v>
+      </c>
+      <c r="E546">
+        <v>3</v>
+      </c>
+      <c r="F546">
+        <v>1</v>
+      </c>
+      <c r="G546">
+        <v>1</v>
+      </c>
+      <c r="H546">
+        <v>0</v>
+      </c>
+      <c r="I546">
+        <v>0</v>
+      </c>
+      <c r="J546">
+        <v>0</v>
+      </c>
+      <c r="K546">
+        <v>0</v>
+      </c>
+      <c r="L546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>2</v>
+      </c>
+      <c r="C547">
+        <v>1</v>
+      </c>
+      <c r="D547">
+        <v>4</v>
+      </c>
+      <c r="E547">
+        <v>2</v>
+      </c>
+      <c r="F547">
+        <v>2</v>
+      </c>
+      <c r="G547">
+        <v>1</v>
+      </c>
+      <c r="H547">
+        <v>0</v>
+      </c>
+      <c r="I547">
+        <v>1</v>
+      </c>
+      <c r="J547">
+        <v>0</v>
+      </c>
+      <c r="K547">
+        <v>0</v>
+      </c>
+      <c r="L547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>27</v>
+      </c>
+      <c r="C548">
+        <v>1</v>
+      </c>
+      <c r="D548">
+        <v>4</v>
+      </c>
+      <c r="E548">
+        <v>2</v>
+      </c>
+      <c r="F548">
+        <v>1</v>
+      </c>
+      <c r="G548">
+        <v>1</v>
+      </c>
+      <c r="H548">
+        <v>0</v>
+      </c>
+      <c r="I548">
+        <v>1</v>
+      </c>
+      <c r="J548">
+        <v>0</v>
+      </c>
+      <c r="K548">
+        <v>0</v>
+      </c>
+      <c r="L548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>84</v>
+      </c>
+      <c r="C549">
+        <v>1</v>
+      </c>
+      <c r="D549">
+        <v>4</v>
+      </c>
+      <c r="E549">
+        <v>2</v>
+      </c>
+      <c r="F549">
+        <v>0</v>
+      </c>
+      <c r="G549">
+        <v>1</v>
+      </c>
+      <c r="H549">
+        <v>0</v>
+      </c>
+      <c r="I549">
+        <v>1</v>
+      </c>
+      <c r="J549">
+        <v>0</v>
+      </c>
+      <c r="K549">
+        <v>0</v>
+      </c>
+      <c r="L549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>28</v>
+      </c>
+      <c r="C550">
+        <v>1</v>
+      </c>
+      <c r="D550">
+        <v>4</v>
+      </c>
+      <c r="E550">
+        <v>2</v>
+      </c>
+      <c r="F550">
+        <v>1</v>
+      </c>
+      <c r="G550">
+        <v>1</v>
+      </c>
+      <c r="H550">
+        <v>0</v>
+      </c>
+      <c r="I550">
+        <v>1</v>
+      </c>
+      <c r="J550">
+        <v>0</v>
+      </c>
+      <c r="K550">
+        <v>0</v>
+      </c>
+      <c r="L550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>117</v>
+      </c>
+      <c r="C551">
+        <v>1</v>
+      </c>
+      <c r="D551">
+        <v>4</v>
+      </c>
+      <c r="E551">
+        <v>2</v>
+      </c>
+      <c r="F551">
+        <v>2</v>
+      </c>
+      <c r="G551">
+        <v>1</v>
+      </c>
+      <c r="H551">
+        <v>0</v>
+      </c>
+      <c r="I551">
+        <v>1</v>
+      </c>
+      <c r="J551">
+        <v>0</v>
+      </c>
+      <c r="K551">
+        <v>0</v>
+      </c>
+      <c r="L551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>34</v>
+      </c>
+      <c r="C552">
+        <v>3</v>
+      </c>
+      <c r="D552">
+        <v>1</v>
+      </c>
+      <c r="E552">
+        <v>3</v>
+      </c>
+      <c r="F552">
+        <v>1</v>
+      </c>
+      <c r="G552">
+        <v>1</v>
+      </c>
+      <c r="H552">
+        <v>0</v>
+      </c>
+      <c r="I552">
+        <v>0</v>
+      </c>
+      <c r="J552">
+        <v>0</v>
+      </c>
+      <c r="K552">
+        <v>0</v>
+      </c>
+      <c r="L552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A553" t="s">
+        <v>25</v>
+      </c>
+      <c r="C553">
+        <v>3</v>
+      </c>
+      <c r="D553">
+        <v>1</v>
+      </c>
+      <c r="E553">
+        <v>3</v>
+      </c>
+      <c r="F553">
+        <v>0</v>
+      </c>
+      <c r="G553">
+        <v>1</v>
+      </c>
+      <c r="H553">
+        <v>0</v>
+      </c>
+      <c r="I553">
+        <v>0</v>
+      </c>
+      <c r="J553">
+        <v>0</v>
+      </c>
+      <c r="K553">
+        <v>0</v>
+      </c>
+      <c r="L553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A554" t="s">
+        <v>37</v>
+      </c>
+      <c r="C554">
+        <v>3</v>
+      </c>
+      <c r="D554">
+        <v>1</v>
+      </c>
+      <c r="E554">
+        <v>3</v>
+      </c>
+      <c r="F554">
+        <v>3</v>
+      </c>
+      <c r="G554">
+        <v>1</v>
+      </c>
+      <c r="H554">
+        <v>0</v>
+      </c>
+      <c r="I554">
+        <v>0</v>
+      </c>
+      <c r="J554">
+        <v>0</v>
+      </c>
+      <c r="K554">
+        <v>0</v>
+      </c>
+      <c r="L554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A555" t="s">
+        <v>3</v>
+      </c>
+      <c r="C555">
+        <v>3</v>
+      </c>
+      <c r="D555">
+        <v>1</v>
+      </c>
+      <c r="E555">
+        <v>3</v>
+      </c>
+      <c r="F555">
+        <v>1</v>
+      </c>
+      <c r="G555">
+        <v>1</v>
+      </c>
+      <c r="H555">
+        <v>0</v>
+      </c>
+      <c r="I555">
+        <v>0</v>
+      </c>
+      <c r="J555">
+        <v>0</v>
+      </c>
+      <c r="K555">
+        <v>0</v>
+      </c>
+      <c r="L555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A556" t="s">
+        <v>67</v>
+      </c>
+      <c r="C556">
+        <v>3</v>
+      </c>
+      <c r="D556">
+        <v>1</v>
+      </c>
+      <c r="E556">
+        <v>3</v>
+      </c>
+      <c r="F556">
+        <v>1</v>
+      </c>
+      <c r="G556">
+        <v>1</v>
+      </c>
+      <c r="H556">
+        <v>0</v>
+      </c>
+      <c r="I556">
+        <v>0</v>
+      </c>
+      <c r="J556">
+        <v>0</v>
+      </c>
+      <c r="K556">
+        <v>0</v>
+      </c>
+      <c r="L556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A557" t="s">
+        <v>59</v>
+      </c>
+      <c r="C557">
+        <v>3</v>
+      </c>
+      <c r="D557">
+        <v>2</v>
+      </c>
+      <c r="E557">
+        <v>1</v>
+      </c>
+      <c r="F557">
+        <v>1</v>
+      </c>
+      <c r="G557">
+        <v>1</v>
+      </c>
+      <c r="H557">
+        <v>1</v>
+      </c>
+      <c r="I557">
+        <v>0</v>
+      </c>
+      <c r="J557">
+        <v>0</v>
+      </c>
+      <c r="K557">
+        <v>0</v>
+      </c>
+      <c r="L557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
+        <v>43</v>
+      </c>
+      <c r="C558">
+        <v>3</v>
+      </c>
+      <c r="D558">
+        <v>2</v>
+      </c>
+      <c r="E558">
+        <v>1</v>
+      </c>
+      <c r="F558">
+        <v>2</v>
+      </c>
+      <c r="G558">
+        <v>1</v>
+      </c>
+      <c r="H558">
+        <v>1</v>
+      </c>
+      <c r="I558">
+        <v>0</v>
+      </c>
+      <c r="J558">
+        <v>0</v>
+      </c>
+      <c r="K558">
+        <v>0</v>
+      </c>
+      <c r="L558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
+        <v>30</v>
+      </c>
+      <c r="C559">
+        <v>3</v>
+      </c>
+      <c r="D559">
+        <v>2</v>
+      </c>
+      <c r="E559">
+        <v>1</v>
+      </c>
+      <c r="F559">
+        <v>3</v>
+      </c>
+      <c r="G559">
+        <v>1</v>
+      </c>
+      <c r="H559">
+        <v>1</v>
+      </c>
+      <c r="I559">
+        <v>0</v>
+      </c>
+      <c r="J559">
+        <v>0</v>
+      </c>
+      <c r="K559">
+        <v>0</v>
+      </c>
+      <c r="L559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A560" t="s">
+        <v>4</v>
+      </c>
+      <c r="C560">
+        <v>3</v>
+      </c>
+      <c r="D560">
+        <v>2</v>
+      </c>
+      <c r="E560">
+        <v>1</v>
+      </c>
+      <c r="F560">
+        <v>1</v>
+      </c>
+      <c r="G560">
+        <v>1</v>
+      </c>
+      <c r="H560">
+        <v>1</v>
+      </c>
+      <c r="I560">
+        <v>0</v>
+      </c>
+      <c r="J560">
+        <v>0</v>
+      </c>
+      <c r="K560">
+        <v>0</v>
+      </c>
+      <c r="L560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A561" t="s">
+        <v>32</v>
+      </c>
+      <c r="C561">
+        <v>3</v>
+      </c>
+      <c r="D561">
+        <v>2</v>
+      </c>
+      <c r="E561">
+        <v>1</v>
+      </c>
+      <c r="F561">
+        <v>0</v>
+      </c>
+      <c r="G561">
+        <v>1</v>
+      </c>
+      <c r="H561">
+        <v>1</v>
+      </c>
+      <c r="I561">
+        <v>0</v>
+      </c>
+      <c r="J561">
+        <v>0</v>
+      </c>
+      <c r="K561">
+        <v>0</v>
+      </c>
+      <c r="L561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A562" t="s">
+        <v>45</v>
+      </c>
+      <c r="C562">
+        <v>3</v>
+      </c>
+      <c r="D562">
+        <v>4</v>
+      </c>
+      <c r="E562">
+        <v>6</v>
+      </c>
+      <c r="F562">
+        <v>0</v>
+      </c>
+      <c r="G562">
+        <v>1</v>
+      </c>
+      <c r="H562">
+        <v>0</v>
+      </c>
+      <c r="I562">
+        <v>1</v>
+      </c>
+      <c r="J562">
+        <v>0</v>
+      </c>
+      <c r="K562">
+        <v>12</v>
+      </c>
+      <c r="L562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A563" t="s">
+        <v>126</v>
+      </c>
+      <c r="C563">
+        <v>6</v>
+      </c>
+      <c r="D563">
+        <v>4</v>
+      </c>
+      <c r="E563">
+        <v>3</v>
+      </c>
+      <c r="F563">
+        <v>0</v>
+      </c>
+      <c r="G563">
+        <v>1</v>
+      </c>
+      <c r="H563">
+        <v>1</v>
+      </c>
+      <c r="I563">
+        <v>0</v>
+      </c>
+      <c r="J563">
+        <v>0</v>
+      </c>
+      <c r="K563">
+        <v>10</v>
+      </c>
+      <c r="L563">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L475" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_01.xlsx
+++ b/pelada_sabado_2026_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2711" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D44DEC07-391A-4F61-B868-520DEEB0EA5E}"/>
+  <xr:revisionPtr revIDLastSave="2826" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60009F10-6A52-4370-8DCD-D6D1AD5F673A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Jogadores!$A$1:$L$475</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Jogadores!$A$1:$L$579</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="136">
   <si>
     <t>Boneco</t>
   </si>
@@ -439,6 +439,15 @@
   <si>
     <t xml:space="preserve">Pedro </t>
   </si>
+  <si>
+    <t>Zebinho</t>
+  </si>
+  <si>
+    <t>Leandro</t>
+  </si>
+  <si>
+    <t>Betim</t>
+  </si>
 </sst>
 </file>
 
@@ -764,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O563"/>
+  <dimension ref="A1:O585"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -10175,7 +10184,7 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C269">
         <v>2</v>
@@ -20498,8 +20507,778 @@
         <v>0</v>
       </c>
     </row>
+    <row r="564" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A564" t="s">
+        <v>119</v>
+      </c>
+      <c r="C564">
+        <v>5</v>
+      </c>
+      <c r="D564">
+        <v>2</v>
+      </c>
+      <c r="E564">
+        <v>3</v>
+      </c>
+      <c r="F564">
+        <v>2</v>
+      </c>
+      <c r="G564">
+        <v>1</v>
+      </c>
+      <c r="H564">
+        <v>1</v>
+      </c>
+      <c r="I564">
+        <v>0</v>
+      </c>
+      <c r="J564">
+        <v>0</v>
+      </c>
+      <c r="K564">
+        <v>0</v>
+      </c>
+      <c r="L564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A565" t="s">
+        <v>128</v>
+      </c>
+      <c r="C565">
+        <v>5</v>
+      </c>
+      <c r="D565">
+        <v>2</v>
+      </c>
+      <c r="E565">
+        <v>3</v>
+      </c>
+      <c r="F565">
+        <v>1</v>
+      </c>
+      <c r="G565">
+        <v>1</v>
+      </c>
+      <c r="H565">
+        <v>1</v>
+      </c>
+      <c r="I565">
+        <v>0</v>
+      </c>
+      <c r="J565">
+        <v>0</v>
+      </c>
+      <c r="K565">
+        <v>0</v>
+      </c>
+      <c r="L565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A566" t="s">
+        <v>117</v>
+      </c>
+      <c r="C566">
+        <v>5</v>
+      </c>
+      <c r="D566">
+        <v>2</v>
+      </c>
+      <c r="E566">
+        <v>3</v>
+      </c>
+      <c r="F566">
+        <v>0</v>
+      </c>
+      <c r="G566">
+        <v>1</v>
+      </c>
+      <c r="H566">
+        <v>1</v>
+      </c>
+      <c r="I566">
+        <v>0</v>
+      </c>
+      <c r="J566">
+        <v>0</v>
+      </c>
+      <c r="K566">
+        <v>0</v>
+      </c>
+      <c r="L566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A567" t="s">
+        <v>57</v>
+      </c>
+      <c r="C567">
+        <v>5</v>
+      </c>
+      <c r="D567">
+        <v>2</v>
+      </c>
+      <c r="E567">
+        <v>3</v>
+      </c>
+      <c r="F567">
+        <v>5</v>
+      </c>
+      <c r="G567">
+        <v>1</v>
+      </c>
+      <c r="H567">
+        <v>1</v>
+      </c>
+      <c r="I567">
+        <v>0</v>
+      </c>
+      <c r="J567">
+        <v>0</v>
+      </c>
+      <c r="K567">
+        <v>0</v>
+      </c>
+      <c r="L567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A568" t="s">
+        <v>133</v>
+      </c>
+      <c r="C568">
+        <v>5</v>
+      </c>
+      <c r="D568">
+        <v>2</v>
+      </c>
+      <c r="E568">
+        <v>3</v>
+      </c>
+      <c r="F568">
+        <v>3</v>
+      </c>
+      <c r="G568">
+        <v>1</v>
+      </c>
+      <c r="H568">
+        <v>1</v>
+      </c>
+      <c r="I568">
+        <v>0</v>
+      </c>
+      <c r="J568">
+        <v>0</v>
+      </c>
+      <c r="K568">
+        <v>0</v>
+      </c>
+      <c r="L568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A569" t="s">
+        <v>59</v>
+      </c>
+      <c r="C569">
+        <v>1</v>
+      </c>
+      <c r="D569">
+        <v>1</v>
+      </c>
+      <c r="E569">
+        <v>4</v>
+      </c>
+      <c r="F569">
+        <v>1</v>
+      </c>
+      <c r="G569">
+        <v>1</v>
+      </c>
+      <c r="H569">
+        <v>0</v>
+      </c>
+      <c r="I569">
+        <v>1</v>
+      </c>
+      <c r="J569">
+        <v>0</v>
+      </c>
+      <c r="K569">
+        <v>0</v>
+      </c>
+      <c r="L569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A570" t="s">
+        <v>26</v>
+      </c>
+      <c r="C570">
+        <v>1</v>
+      </c>
+      <c r="D570">
+        <v>1</v>
+      </c>
+      <c r="E570">
+        <v>4</v>
+      </c>
+      <c r="F570">
+        <v>0</v>
+      </c>
+      <c r="G570">
+        <v>1</v>
+      </c>
+      <c r="H570">
+        <v>0</v>
+      </c>
+      <c r="I570">
+        <v>1</v>
+      </c>
+      <c r="J570">
+        <v>0</v>
+      </c>
+      <c r="K570">
+        <v>0</v>
+      </c>
+      <c r="L570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A571" t="s">
+        <v>6</v>
+      </c>
+      <c r="C571">
+        <v>1</v>
+      </c>
+      <c r="D571">
+        <v>1</v>
+      </c>
+      <c r="E571">
+        <v>4</v>
+      </c>
+      <c r="F571">
+        <v>0</v>
+      </c>
+      <c r="G571">
+        <v>1</v>
+      </c>
+      <c r="H571">
+        <v>0</v>
+      </c>
+      <c r="I571">
+        <v>1</v>
+      </c>
+      <c r="J571">
+        <v>0</v>
+      </c>
+      <c r="K571">
+        <v>0</v>
+      </c>
+      <c r="L571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A572" t="s">
+        <v>3</v>
+      </c>
+      <c r="C572">
+        <v>1</v>
+      </c>
+      <c r="D572">
+        <v>1</v>
+      </c>
+      <c r="E572">
+        <v>4</v>
+      </c>
+      <c r="F572">
+        <v>1</v>
+      </c>
+      <c r="G572">
+        <v>1</v>
+      </c>
+      <c r="H572">
+        <v>0</v>
+      </c>
+      <c r="I572">
+        <v>1</v>
+      </c>
+      <c r="J572">
+        <v>0</v>
+      </c>
+      <c r="K572">
+        <v>0</v>
+      </c>
+      <c r="L572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A573" t="s">
+        <v>27</v>
+      </c>
+      <c r="C573">
+        <v>1</v>
+      </c>
+      <c r="D573">
+        <v>1</v>
+      </c>
+      <c r="E573">
+        <v>4</v>
+      </c>
+      <c r="F573">
+        <v>0</v>
+      </c>
+      <c r="G573">
+        <v>1</v>
+      </c>
+      <c r="H573">
+        <v>0</v>
+      </c>
+      <c r="I573">
+        <v>1</v>
+      </c>
+      <c r="J573">
+        <v>0</v>
+      </c>
+      <c r="K573">
+        <v>0</v>
+      </c>
+      <c r="L573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A574" t="s">
+        <v>30</v>
+      </c>
+      <c r="C574">
+        <v>2</v>
+      </c>
+      <c r="D574">
+        <v>4</v>
+      </c>
+      <c r="E574">
+        <v>1</v>
+      </c>
+      <c r="F574">
+        <v>0</v>
+      </c>
+      <c r="G574">
+        <v>1</v>
+      </c>
+      <c r="H574">
+        <v>0</v>
+      </c>
+      <c r="I574">
+        <v>0</v>
+      </c>
+      <c r="J574">
+        <v>0</v>
+      </c>
+      <c r="K574">
+        <v>0</v>
+      </c>
+      <c r="L574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A575" t="s">
+        <v>134</v>
+      </c>
+      <c r="C575">
+        <v>2</v>
+      </c>
+      <c r="D575">
+        <v>4</v>
+      </c>
+      <c r="E575">
+        <v>1</v>
+      </c>
+      <c r="F575">
+        <v>0</v>
+      </c>
+      <c r="G575">
+        <v>1</v>
+      </c>
+      <c r="H575">
+        <v>0</v>
+      </c>
+      <c r="I575">
+        <v>0</v>
+      </c>
+      <c r="J575">
+        <v>0</v>
+      </c>
+      <c r="K575">
+        <v>0</v>
+      </c>
+      <c r="L575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A576" t="s">
+        <v>129</v>
+      </c>
+      <c r="C576">
+        <v>2</v>
+      </c>
+      <c r="D576">
+        <v>4</v>
+      </c>
+      <c r="E576">
+        <v>1</v>
+      </c>
+      <c r="F576">
+        <v>0</v>
+      </c>
+      <c r="G576">
+        <v>1</v>
+      </c>
+      <c r="H576">
+        <v>0</v>
+      </c>
+      <c r="I576">
+        <v>0</v>
+      </c>
+      <c r="J576">
+        <v>0</v>
+      </c>
+      <c r="K576">
+        <v>0</v>
+      </c>
+      <c r="L576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A577" t="s">
+        <v>29</v>
+      </c>
+      <c r="C577">
+        <v>2</v>
+      </c>
+      <c r="D577">
+        <v>4</v>
+      </c>
+      <c r="E577">
+        <v>1</v>
+      </c>
+      <c r="F577">
+        <v>3</v>
+      </c>
+      <c r="G577">
+        <v>1</v>
+      </c>
+      <c r="H577">
+        <v>0</v>
+      </c>
+      <c r="I577">
+        <v>0</v>
+      </c>
+      <c r="J577">
+        <v>0</v>
+      </c>
+      <c r="K577">
+        <v>0</v>
+      </c>
+      <c r="L577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A578" t="s">
+        <v>25</v>
+      </c>
+      <c r="C578">
+        <v>2</v>
+      </c>
+      <c r="D578">
+        <v>4</v>
+      </c>
+      <c r="E578">
+        <v>1</v>
+      </c>
+      <c r="F578">
+        <v>2</v>
+      </c>
+      <c r="G578">
+        <v>1</v>
+      </c>
+      <c r="H578">
+        <v>0</v>
+      </c>
+      <c r="I578">
+        <v>0</v>
+      </c>
+      <c r="J578">
+        <v>0</v>
+      </c>
+      <c r="K578">
+        <v>0</v>
+      </c>
+      <c r="L578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A579" t="s">
+        <v>36</v>
+      </c>
+      <c r="C579">
+        <v>3</v>
+      </c>
+      <c r="D579">
+        <v>5</v>
+      </c>
+      <c r="E579">
+        <v>0</v>
+      </c>
+      <c r="F579">
+        <v>2</v>
+      </c>
+      <c r="G579">
+        <v>1</v>
+      </c>
+      <c r="H579">
+        <v>0</v>
+      </c>
+      <c r="I579">
+        <v>0</v>
+      </c>
+      <c r="J579">
+        <v>0</v>
+      </c>
+      <c r="K579">
+        <v>0</v>
+      </c>
+      <c r="L579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A580" t="s">
+        <v>135</v>
+      </c>
+      <c r="C580">
+        <v>3</v>
+      </c>
+      <c r="D580">
+        <v>5</v>
+      </c>
+      <c r="E580">
+        <v>0</v>
+      </c>
+      <c r="F580">
+        <v>0</v>
+      </c>
+      <c r="G580">
+        <v>1</v>
+      </c>
+      <c r="H580">
+        <v>0</v>
+      </c>
+      <c r="I580">
+        <v>0</v>
+      </c>
+      <c r="J580">
+        <v>0</v>
+      </c>
+      <c r="K580">
+        <v>0</v>
+      </c>
+      <c r="L580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A581" t="s">
+        <v>82</v>
+      </c>
+      <c r="C581">
+        <v>3</v>
+      </c>
+      <c r="D581">
+        <v>5</v>
+      </c>
+      <c r="E581">
+        <v>0</v>
+      </c>
+      <c r="F581">
+        <v>1</v>
+      </c>
+      <c r="G581">
+        <v>1</v>
+      </c>
+      <c r="H581">
+        <v>0</v>
+      </c>
+      <c r="I581">
+        <v>0</v>
+      </c>
+      <c r="J581">
+        <v>0</v>
+      </c>
+      <c r="K581">
+        <v>0</v>
+      </c>
+      <c r="L581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A582" t="s">
+        <v>1</v>
+      </c>
+      <c r="C582">
+        <v>3</v>
+      </c>
+      <c r="D582">
+        <v>5</v>
+      </c>
+      <c r="E582">
+        <v>0</v>
+      </c>
+      <c r="F582">
+        <v>2</v>
+      </c>
+      <c r="G582">
+        <v>1</v>
+      </c>
+      <c r="H582">
+        <v>0</v>
+      </c>
+      <c r="I582">
+        <v>0</v>
+      </c>
+      <c r="J582">
+        <v>0</v>
+      </c>
+      <c r="K582">
+        <v>0</v>
+      </c>
+      <c r="L582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A583" t="s">
+        <v>121</v>
+      </c>
+      <c r="C583">
+        <v>3</v>
+      </c>
+      <c r="D583">
+        <v>5</v>
+      </c>
+      <c r="E583">
+        <v>0</v>
+      </c>
+      <c r="F583">
+        <v>1</v>
+      </c>
+      <c r="G583">
+        <v>1</v>
+      </c>
+      <c r="H583">
+        <v>0</v>
+      </c>
+      <c r="I583">
+        <v>0</v>
+      </c>
+      <c r="J583">
+        <v>0</v>
+      </c>
+      <c r="K583">
+        <v>0</v>
+      </c>
+      <c r="L583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A584" t="s">
+        <v>108</v>
+      </c>
+      <c r="C584">
+        <v>4</v>
+      </c>
+      <c r="D584">
+        <v>5</v>
+      </c>
+      <c r="E584">
+        <v>4</v>
+      </c>
+      <c r="F584">
+        <v>0</v>
+      </c>
+      <c r="G584">
+        <v>1</v>
+      </c>
+      <c r="H584">
+        <v>1</v>
+      </c>
+      <c r="I584">
+        <v>0</v>
+      </c>
+      <c r="J584">
+        <v>0</v>
+      </c>
+      <c r="K584">
+        <v>11</v>
+      </c>
+      <c r="L584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A585" t="s">
+        <v>80</v>
+      </c>
+      <c r="C585">
+        <v>4</v>
+      </c>
+      <c r="D585">
+        <v>5</v>
+      </c>
+      <c r="E585">
+        <v>4</v>
+      </c>
+      <c r="F585">
+        <v>1</v>
+      </c>
+      <c r="G585">
+        <v>1</v>
+      </c>
+      <c r="H585">
+        <v>0</v>
+      </c>
+      <c r="I585">
+        <v>1</v>
+      </c>
+      <c r="J585">
+        <v>0</v>
+      </c>
+      <c r="K585">
+        <v>12</v>
+      </c>
+      <c r="L585">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L475" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
